--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P103"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,7 +509,6 @@
           <t>Afghanistan</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>4</v>
       </c>
@@ -533,17 +532,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -561,7 +554,6 @@
           <t>Albania</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>8</v>
       </c>
@@ -585,17 +577,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -613,7 +599,6 @@
           <t>Armenia</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>51</v>
       </c>
@@ -637,17 +622,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -665,7 +644,6 @@
           <t>Australia</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>36</v>
       </c>
@@ -689,17 +667,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -717,7 +689,6 @@
           <t>Austria</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>40</v>
       </c>
@@ -741,17 +712,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -769,7 +734,6 @@
           <t>Azerbaijan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>31</v>
       </c>
@@ -793,17 +757,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -821,7 +779,6 @@
           <t>Bangladesh</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
         <v>50</v>
       </c>
@@ -845,17 +802,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -873,7 +824,6 @@
           <t>Belarus</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>112</v>
       </c>
@@ -897,17 +847,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -925,7 +869,6 @@
           <t>Belgium</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>56</v>
       </c>
@@ -949,17 +892,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -977,7 +914,6 @@
           <t>Bhutan</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>64</v>
       </c>
@@ -1001,17 +937,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1029,7 +959,6 @@
           <t>Bulgaria</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>100</v>
       </c>
@@ -1053,17 +982,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1081,7 +1004,6 @@
           <t>Burundi</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>108</v>
       </c>
@@ -1105,17 +1027,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1133,7 +1049,6 @@
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>120</v>
       </c>
@@ -1157,17 +1072,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1185,7 +1094,6 @@
           <t>Costa Rica</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>188</v>
       </c>
@@ -1209,17 +1117,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1237,7 +1139,6 @@
           <t>Croatia</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
         <v>191</v>
       </c>
@@ -1261,17 +1162,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1289,7 +1184,6 @@
           <t>Cuba</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
         <v>192</v>
       </c>
@@ -1313,17 +1207,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1341,7 +1229,6 @@
           <t>Cyprus</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>196</v>
       </c>
@@ -1365,17 +1252,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1393,7 +1274,6 @@
           <t>Czechia</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
         <v>203</v>
       </c>
@@ -1417,17 +1297,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1445,7 +1319,6 @@
           <t>Denmark</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
         <v>208</v>
       </c>
@@ -1469,17 +1342,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -1502,7 +1369,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>atlanticcouncil.org</t>
@@ -1528,16 +1394,11 @@
           <t>Mohamed Morsi</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1560,7 +1421,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>bbc.com</t>
@@ -1586,16 +1446,11 @@
           <t>Hosni Mubarak</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1618,7 +1473,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>c-span.org</t>
@@ -1644,16 +1498,11 @@
           <t>Mohamed Morsi</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1676,7 +1525,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>cdm15795.contentdm.oclc.org</t>
@@ -1702,16 +1550,11 @@
           <t>Hosni Mubarak</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1734,7 +1577,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>ilsoncenter.org</t>
@@ -1760,16 +1602,11 @@
           <t>Mohamed Morsi</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1792,7 +1629,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>leftvoice.org</t>
@@ -1818,16 +1654,11 @@
           <t>Hosni Mubarak</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1850,7 +1681,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>sadat.umd.edu</t>
@@ -1876,16 +1706,11 @@
           <t>Sadat (old speeches)</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1908,7 +1733,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>sis.gov.eg</t>
@@ -1919,7 +1743,6 @@
           <t>http://sis.gov.eg</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -1930,16 +1753,11 @@
           <t>Pres Sisi</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -1962,7 +1780,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>theguardian.com</t>
@@ -1988,16 +1805,11 @@
           <t>Hosni Mubarak</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -2020,7 +1832,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>youtube.com</t>
@@ -2046,16 +1857,11 @@
           <t>Amadou Toumani Touré; Dioncounda Traoré ; Hosni Mubarak; Mahamadou Issoufou; Mohamed Morsi; Moncef Marzouki</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (6 link(s))</t>
@@ -2073,7 +1879,6 @@
           <t>Estonia</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>233</v>
       </c>
@@ -2097,17 +1902,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2125,7 +1924,6 @@
           <t>Ethiopia</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
         <v>231</v>
       </c>
@@ -2149,17 +1947,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2182,7 +1974,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>pmo.gov.et</t>
@@ -2208,16 +1999,11 @@
           <t>Prime Minister Abiy Ahmed</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (2 link(s))</t>
@@ -2235,7 +2021,6 @@
           <t>Fiji</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>242</v>
       </c>
@@ -2259,17 +2044,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2287,7 +2066,6 @@
           <t>Finland</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
         <v>246</v>
       </c>
@@ -2311,17 +2089,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2339,7 +2111,6 @@
           <t>Gambia</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>270</v>
       </c>
@@ -2363,17 +2134,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2391,7 +2156,6 @@
           <t>Georgia</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>268</v>
       </c>
@@ -2415,17 +2179,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2443,7 +2201,6 @@
           <t>Germany</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>276</v>
       </c>
@@ -2467,17 +2224,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2495,7 +2246,6 @@
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>288</v>
       </c>
@@ -2519,17 +2269,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2547,7 +2291,6 @@
           <t>Greece</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>300</v>
       </c>
@@ -2571,17 +2314,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2599,7 +2336,6 @@
           <t>Guyana</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>328</v>
       </c>
@@ -2623,17 +2359,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2651,7 +2381,6 @@
           <t>Hungary</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
         <v>348</v>
       </c>
@@ -2675,17 +2404,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2703,7 +2426,6 @@
           <t>Iceland</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
         <v>352</v>
       </c>
@@ -2727,17 +2449,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2755,7 +2471,6 @@
           <t>India</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
         <v>356</v>
       </c>
@@ -2779,17 +2494,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2807,7 +2516,6 @@
           <t>Iran, Islamic Republic of</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
         <v>364</v>
       </c>
@@ -2831,17 +2539,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2859,7 +2561,6 @@
           <t>Ireland</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
         <v>372</v>
       </c>
@@ -2883,17 +2584,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2911,7 +2606,6 @@
           <t>Israel</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>376</v>
       </c>
@@ -2935,17 +2629,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -2963,7 +2651,6 @@
           <t>Italy</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
         <v>380</v>
       </c>
@@ -2987,17 +2674,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3015,7 +2696,6 @@
           <t>Japan</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
         <v>392</v>
       </c>
@@ -3039,17 +2719,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3067,7 +2741,6 @@
           <t>Jordan</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
         <v>400</v>
       </c>
@@ -3091,17 +2764,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3119,7 +2786,6 @@
           <t>Kazakhstan</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>398</v>
       </c>
@@ -3143,17 +2809,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3171,7 +2831,6 @@
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>404</v>
       </c>
@@ -3195,17 +2854,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3223,7 +2876,6 @@
           <t>Kuwait</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>414</v>
       </c>
@@ -3247,17 +2899,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3275,7 +2921,6 @@
           <t>Kyrgyzstan</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
         <v>417</v>
       </c>
@@ -3299,17 +2944,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3327,7 +2966,6 @@
           <t>Latvia</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
         <v>428</v>
       </c>
@@ -3351,17 +2989,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3379,7 +3011,6 @@
           <t>Lebanon</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>422</v>
       </c>
@@ -3403,17 +3034,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3431,7 +3056,6 @@
           <t>Lesotho</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
         <v>426</v>
       </c>
@@ -3455,17 +3079,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3483,7 +3101,6 @@
           <t>Lithuania</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
         <v>440</v>
       </c>
@@ -3507,17 +3124,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3535,7 +3146,6 @@
           <t>Luxembourg</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
         <v>442</v>
       </c>
@@ -3559,17 +3169,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3587,7 +3191,6 @@
           <t>Madagascar</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
         <v>450</v>
       </c>
@@ -3611,17 +3214,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3639,7 +3236,6 @@
           <t>Maldives</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
         <v>462</v>
       </c>
@@ -3663,17 +3259,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3691,7 +3281,6 @@
           <t>Malta</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
         <v>470</v>
       </c>
@@ -3715,17 +3304,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3743,7 +3326,6 @@
           <t>Mexico</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
         <v>484</v>
       </c>
@@ -3767,17 +3349,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3795,7 +3371,6 @@
           <t>Moldova, Republic of</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
         <v>498</v>
       </c>
@@ -3819,17 +3394,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3847,7 +3416,6 @@
           <t>Morocco</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
         <v>504</v>
       </c>
@@ -3871,17 +3439,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3899,7 +3461,6 @@
           <t>Netherlands</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
         <v>528</v>
       </c>
@@ -3923,17 +3484,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -3951,7 +3506,6 @@
           <t>New Zealand</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
         <v>554</v>
       </c>
@@ -3975,17 +3529,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4008,7 +3556,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>books.google.com</t>
@@ -4034,16 +3581,11 @@
           <t>Olusegun Obasanjo</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -4066,7 +3608,6 @@
           <t>Africa</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>statehouse.gov.ng</t>
@@ -4092,16 +3633,11 @@
           <t>Bola Ahmed Tinubu</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
@@ -4119,7 +3655,6 @@
           <t>North Macedonia</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
         <v>807</v>
       </c>
@@ -4143,17 +3678,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4171,7 +3700,6 @@
           <t>Norway</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
         <v>578</v>
       </c>
@@ -4195,17 +3723,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4223,7 +3745,6 @@
           <t>Poland</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
         <v>616</v>
       </c>
@@ -4247,17 +3768,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4275,7 +3790,6 @@
           <t>Romania</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
         <v>642</v>
       </c>
@@ -4299,17 +3813,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4327,7 +3835,6 @@
           <t>Serbia</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
         <v>688</v>
       </c>
@@ -4351,17 +3858,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4379,7 +3880,6 @@
           <t>Seychelles</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
         <v>690</v>
       </c>
@@ -4403,17 +3903,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4431,7 +3925,6 @@
           <t>Sierra Leone</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
         <v>694</v>
       </c>
@@ -4455,17 +3948,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4483,7 +3970,6 @@
           <t>Singapore</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
         <v>702</v>
       </c>
@@ -4507,17 +3993,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4535,7 +4015,6 @@
           <t>Slovakia</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
         <v>703</v>
       </c>
@@ -4559,17 +4038,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4587,7 +4060,6 @@
           <t>Slovenia</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
         <v>705</v>
       </c>
@@ -4611,17 +4083,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4639,7 +4105,6 @@
           <t>Somalia</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
         <v>706</v>
       </c>
@@ -4663,17 +4128,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4691,7 +4150,6 @@
           <t>South Africa</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
         <v>710</v>
       </c>
@@ -4715,17 +4173,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4743,7 +4195,6 @@
           <t>Spain</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
         <v>724</v>
       </c>
@@ -4767,17 +4218,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4795,7 +4240,6 @@
           <t>Sri Lanka</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
         <v>144</v>
       </c>
@@ -4819,17 +4263,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4847,7 +4285,6 @@
           <t>Sudan</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
         <v>729</v>
       </c>
@@ -4871,17 +4308,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4899,7 +4330,6 @@
           <t>Sweden</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
         <v>752</v>
       </c>
@@ -4923,17 +4353,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -4951,7 +4375,6 @@
           <t>Tanzania, United Republic of</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
         <v>834</v>
       </c>
@@ -4975,17 +4398,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5003,7 +4420,6 @@
           <t>Thailand</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
         <v>764</v>
       </c>
@@ -5027,17 +4443,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5055,7 +4465,6 @@
           <t>Timor-Leste</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
         <v>626</v>
       </c>
@@ -5079,17 +4488,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5107,7 +4510,6 @@
           <t>Trinidad and Tobago</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
         <v>780</v>
       </c>
@@ -5131,17 +4533,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5159,7 +4555,6 @@
           <t>Turkmenistan</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
         <v>795</v>
       </c>
@@ -5183,17 +4578,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5211,7 +4600,6 @@
           <t>Türkiye</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
         <v>792</v>
       </c>
@@ -5235,17 +4623,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5263,7 +4645,6 @@
           <t>Uganda</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
         <v>800</v>
       </c>
@@ -5287,17 +4668,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5315,7 +4690,6 @@
           <t>Ukraine</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
         <v>804</v>
       </c>
@@ -5339,17 +4713,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5367,7 +4735,6 @@
           <t>United Arab Emirates</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
         <v>784</v>
       </c>
@@ -5391,17 +4758,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5419,7 +4780,6 @@
           <t>United Kingdom</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="n">
         <v>826</v>
       </c>
@@ -5443,17 +4803,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5471,7 +4825,6 @@
           <t>United States</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
         <v>840</v>
       </c>
@@ -5495,17 +4848,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5523,7 +4870,6 @@
           <t>Uruguay</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
         <v>858</v>
       </c>
@@ -5547,17 +4893,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5575,7 +4915,6 @@
           <t>Uzbekistan</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
         <v>860</v>
       </c>
@@ -5599,17 +4938,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5627,7 +4960,6 @@
           <t>Viet Nam</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
         <v>704</v>
       </c>
@@ -5651,17 +4983,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5679,7 +5005,6 @@
           <t>Zimbabwe</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
         <v>716</v>
       </c>
@@ -5703,17 +5028,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>auto-seeded from urls_deanscrape.txt</t>
@@ -5764,8 +5083,6 @@
           <t>Milei, Fernández, Macri, Kirchner</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>Spanish</t>
@@ -5836,8 +5153,6 @@
           <t>Macron</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>French</t>
@@ -5908,8 +5223,6 @@
           <t>Sheinbaum, López Obrador (paging back)</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
           <t>Spanish</t>
@@ -5933,6 +5246,81 @@
       <c r="P103" t="inlineStr">
         <is>
           <t>recipe: recipes/mex_presidencia.yml — validated live</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>chl_presidencia</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>152</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>prensa.presidencia.cl</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://prensa.presidencia.cl/</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Bachelet, Piñera, Boric</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2014-03-11</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>recipe: recipes/chl_presidencia.yml</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>recipe: recipes/arg_casarosada.yml — validated live</t>
+          <t>recipe: recipes/arg_casarosada.yml — Wayback-backed archive recipe</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2581,13 +2584,21 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
+          <t>validated</t>
+        </is>
+      </c>
+      <c r="O46" s="1" t="n">
+        <v>46202</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P104"/>
+  <dimension ref="A1:P105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5324,6 +5324,71 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>col_presidencia</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>170</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>presidencia.gov.co</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.presidencia.gov.co/prensa/Paginas/discursos.aspx</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Petro, Duque, Santos, Uribe</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>recipe: recipes/col_presidencia.yml — pending probe</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P105"/>
+  <dimension ref="A1:P104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5324,71 +5324,6 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>col_presidencia</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>South America</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>170</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>presidencia.gov.co</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>https://www.presidencia.gov.co/prensa/Paginas/discursos.aspx</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>official_gov</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>static</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>Petro, Duque, Santos, Uribe</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>fulltext</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>recipe: recipes/col_presidencia.yml — pending probe</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -48,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2584,21 +2581,13 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>static</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>English</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>validated</t>
-        </is>
-      </c>
-      <c r="O46" s="1" t="n">
-        <v>46202</v>
+          <t>none</t>
+        </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>validated</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>validated</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>validated</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -984,7 +984,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>validated</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -1029,7 +1029,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>none</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -984,7 +984,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>validated</t>
+          <t>none</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgsch\Dropbox (Personal)\academic_work\LeaderSpeech\github_repo\LeaderSpeech\data\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C34A03DB-E95E-4601-BBA8-145546F54572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B10C2FD-5354-4E2F-9BD9-DD46496B39D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30000" yWindow="1605" windowWidth="24060" windowHeight="13800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="993" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1123" uniqueCount="605">
   <si>
     <t>source_id</t>
   </si>
@@ -64,6 +64,9 @@
     <t>recipe_status</t>
   </si>
   <si>
+    <t>full_scrape_done</t>
+  </si>
+  <si>
     <t>last_checked</t>
   </si>
   <si>
@@ -118,6 +121,12 @@
     <t>https://www.president.am/</t>
   </si>
   <si>
+    <t>js</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
     <t>aus_gg</t>
   </si>
   <si>
@@ -166,6 +175,12 @@
     <t>http://www.bangabhaban.gov.bd/</t>
   </si>
   <si>
+    <t>static</t>
+  </si>
+  <si>
+    <t>BLOCKED: speeches are legacy-Bijoy-font PDFs (declared Helvetica, no ToUnicode) -&gt; text extraction is gibberish; date is listing-only. Not tractable without Bijoy-&gt;Unicode/OCR. REDIRECTED to bgd_bss_president (BSS state-news HTML). See recipe notes / PR #39.</t>
+  </si>
+  <si>
     <t>blr_president</t>
   </si>
   <si>
@@ -190,6 +205,12 @@
     <t>https://www.monarchie.be/</t>
   </si>
   <si>
+    <t>2026-07-08</t>
+  </si>
+  <si>
+    <t>btn_royalkidu_wayback</t>
+  </si>
+  <si>
     <t>Bhutan</t>
   </si>
   <si>
@@ -232,7 +253,7 @@
     <t>prc.cm</t>
   </si>
   <si>
-    <t>https://www.prc.cm/</t>
+    <t>https://www.prc.cm/en/news/speeches-of-the-president</t>
   </si>
   <si>
     <t>cri_presidencia</t>
@@ -724,6 +745,9 @@
     <t>https://www.president.go.ke/</t>
   </si>
   <si>
+    <t>President (Ruto)</t>
+  </si>
+  <si>
     <t>kwt_e</t>
   </si>
   <si>
@@ -961,6 +985,18 @@
     <t>http://www.kongehuset.no/</t>
   </si>
   <si>
+    <t>phl_pco</t>
+  </si>
+  <si>
+    <t>Philippines</t>
+  </si>
+  <si>
+    <t>officialgazette.gov.ph (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t>static (wayback)</t>
+  </si>
+  <si>
     <t>pol_president</t>
   </si>
   <si>
@@ -1324,9 +1360,6 @@
     <t>https://www.casarosada.gob.ar/</t>
   </si>
   <si>
-    <t>static</t>
-  </si>
-  <si>
     <t>Milei, Fernández, Macri, Kirchner</t>
   </si>
   <si>
@@ -1336,6 +1369,9 @@
     <t>fulltext</t>
   </si>
   <si>
+    <t>done</t>
+  </si>
+  <si>
     <t>2026-06-28</t>
   </si>
   <si>
@@ -1408,139 +1444,397 @@
     <t>recipe: recipes/chl_presidencia.yml</t>
   </si>
   <si>
-    <t>draft</t>
-  </si>
-  <si>
-    <t>phl_pco</t>
-  </si>
-  <si>
-    <t>Philippines</t>
-  </si>
-  <si>
-    <t>static (wayback)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">draft </t>
-  </si>
-  <si>
-    <t>btn_royalkidu_wayback</t>
-  </si>
-  <si>
-    <t>very limited coverage. Needs more sources.</t>
-  </si>
-  <si>
-    <t>full_scrape_done</t>
-  </si>
-  <si>
-    <t>done</t>
-  </si>
-  <si>
     <t>arg_casarosada_wayback</t>
   </si>
   <si>
+    <t>casarosada.gob.ar (Wayback)</t>
+  </si>
+  <si>
+    <t>https://www.casarosada.gob.ar/informacion/discursos (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t>official_gov (archived)</t>
+  </si>
+  <si>
+    <t>Kirchner-era (CFK, N. Kirchner)</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>NEW master row needed | country=Argentina; source_url=https://www.casarosada.gob.ar/informacion/discursos (Wayback/CDX); source_name=casarosada.gob.ar (Wayback); source_type=official_gov (archived); region=South America; iso3n=32; content_format=fulltext; leaders_covered=Kirchner-era (CFK, N. Kirchner). recipe recipes/arg_casarosada_wayback.yml on main (PR #9) â€” pagination: wayback over IA CDX, wayback_to 20151210 (complements live arg_casarosada from 2015-12-10 on); coverage ~2007â€“2015; FULL RUN underway.</t>
+  </si>
+  <si>
     <t>arm_president_wayback</t>
   </si>
   <si>
+    <t>Asia</t>
+  </si>
+  <si>
+    <t>president.am (Wayback)</t>
+  </si>
+  <si>
+    <t>president.am/en/press-release/item (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t>Sargsyan/Sarkissian/Khachaturyan</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>Companion WAYBACK recipe recipes/arm_president_wayback.yml (reliable path while the live Radware WAF + engine networkidle block live runs). pagination:wayback over president.am/en/press-release/item -&gt; 8,152 CDX snapshots 2008-2022 (Sargsyan/Sarkissian/Khachaturyan). Probe-verified title/text/date across 2008-2022 (old .news-date + new .date-cub, day-first hy). source_url=president.am/en/press-release/item (Wayback/CDX); source_name=president.am (Wayback); source_type=official_gov (archived); region=Asia; iso3n=51; content_format=fulltext. FULL RUN pending.</t>
+  </si>
+  <si>
     <t>bgd_bss_president</t>
   </si>
   <si>
+    <t>bssnews.net (BSS state news)</t>
+  </si>
+  <si>
+    <t>https://www.bssnews.net/news/president</t>
+  </si>
+  <si>
+    <t>state_news_agency</t>
+  </si>
+  <si>
+    <t>President Mohammed Shahabuddin</t>
+  </si>
+  <si>
+    <t>Reviewer-authored (redirect of the #39 Bangabhaban task). The official presidency site bangabhaban.gov.bd is intractable: every speech is a PDF using a legacy Bijoy-encoded Bangla font (declared /Helvetica, no ToUnicode) so text extraction yields gibberish, and the date is listing-only â€” even PDF-extraction + listing-date engine features would not recover usable text (would need Bijoy-&gt;Unicode conversion or Bangla OCR, out of scope). Redirected to BSS (Bangladesh Sangbad Sangstha, state news agency) English wire: recipes/bgd_bss_president.yml, pagination:none over https://www.bssnews.net/news/president. Probe-verified clean title(.headline_content_block)/text(#details_content p)/date(.entry_update) across 2026-05..2026-07 (~25 recent President-category articles; third-person official_statement reportage of President Mohammed Shahabuddin). source_url=https://www.bssnews.net/news/president; source_name=bssnews.net (BSS); source_type=state_news_agency; region=Asia; iso3n=50; content_format=fulltext. FULL RUN pending. Follow-ups: a wayback companion for older history; a Chief-Adviser category for the interim head of government.</t>
+  </si>
+  <si>
     <t>col_presidencia</t>
   </si>
   <si>
+    <t>Colombia</t>
+  </si>
+  <si>
+    <t>https://www.presidencia.gov.co/prensa/Paginas/discursos.aspx</t>
+  </si>
+  <si>
+    <t>NEW master row needed | country=Colombia; source_url=https://www.presidencia.gov.co/prensa/Paginas/discursos.aspx; source_name=presidencia.gov.co; source_type=official_gov; region=South America; iso3n=170; content_format=fulltext. recipe recipes/col_presidencia.yml on main (issue #7) â€” SharePoint CSWP via renderer:js + browser user_agent + click pager; probe-validated, FULL RUN pending (date coverage TBD).</t>
+  </si>
+  <si>
     <t>idn_setkab</t>
   </si>
   <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>https://setkab.go.id/en/category/speech-transcript/</t>
+  </si>
+  <si>
+    <t>English (+Indonesian)</t>
+  </si>
+  <si>
+    <t>NEW master row needed | country=Indonesia; source_url=https://setkab.go.id/en/category/speech-transcript/; source_name=setkab.go.id; source_type=official_gov; region=Asia; iso3n=360; content_format=fulltext. Cabinet Secretariat 'Speech Transcript' archive: ~200 pages of full presidential transcripts, WordPress-style /page/N/ pagination. SSL cert chain does not verify -&gt; likely needs verify_ssl: false. Indonesian-language originals at setkab.go.id/kategori/. GitHub issue #45 already opened - do NOT re-run create_issues_from_master.py for this row.</t>
+  </si>
+  <si>
     <t>ind_pmindia</t>
   </si>
   <si>
+    <t>https://www.pmindia.gov.in/en/</t>
+  </si>
+  <si>
+    <t>English/Hindi</t>
+  </si>
+  <si>
+    <t>NEW master row needed | country=India; source_url=https://www.pmindia.gov.in/en/; source_name=pmindia.gov.in; source_type=official_gov; region=Asia; iso3n=356; content_format=fulltext. PM Modi is India's actual national leader (the President in master is ceremonial). The /en/speeches/ section is largely video; look for text under /en/pms-speeches/ or fall back to narendramodi.in/category/text-speeches. GitHub issue #43 already opened - do NOT re-run create_issues_from_master.py for this row.</t>
+  </si>
+  <si>
     <t>tha_thaigov</t>
   </si>
   <si>
+    <t>https://www.thaigov.go.th/en/news</t>
+  </si>
+  <si>
+    <t>Thai/English</t>
+  </si>
+  <si>
     <t>proposed</t>
   </si>
   <si>
-    <t>js</t>
-  </si>
-  <si>
-    <t>static/js</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
-    <t>Bulgarian</t>
-  </si>
-  <si>
-    <t>Croatian</t>
-  </si>
-  <si>
-    <t>English (+Indonesian)</t>
-  </si>
-  <si>
-    <t>English/Hindi</t>
-  </si>
-  <si>
-    <t>English/Filipino</t>
-  </si>
-  <si>
-    <t>Thai/English</t>
-  </si>
-  <si>
-    <t>NEW master row needed | country=Argentina; source_url=https://www.casarosada.gob.ar/informacion/discursos (Wayback/CDX); source_name=casarosada.gob.ar (Wayback); source_type=official_gov (archived); region=South America; iso3n=32; content_format=fulltext; leaders_covered=Kirchner-era (CFK, N. Kirchner). recipe recipes/arg_casarosada_wayback.yml on main (PR #9) â€” pagination: wayback over IA CDX, wayback_to 20151210 (complements live arg_casarosada from 2015-12-10 on); coverage ~2007â€“2015; FULL RUN underway.</t>
-  </si>
-  <si>
-    <t>Reviewer networked-probe outcome. LIVE recipe recipes/arm_president.yml uses renderer:js + browser user_agent to clear the Radware behavioral WAF on president.am (bot UA hard-blocked; browser UA challenged after a burst). Listing renders (49 /en/press-release/item/YYYY/MM/DD/ links) and detail selectors verified (title h1, text .news-text/.static-content, date .date-cub|.news-date day-first hy). BUT full runs are UNRELIABLE: the engine js fetch waits for networkidle (fetch.py), which never settles on this WAF-beacon site -&gt; intermittent goto timeouts; plus the behavioral WAF throttles ~1300-page runs. Engine tweak needed (js wait_until domcontentloaded/selector). Use arm_president_wayback for reliable coverage now. source_url=https://www.president.am/en/press-release/; source_name=president.am; source_type=official_gov; region=Asia; iso3n=51; content_format=fulltext. FULL RUN pending (expect WAF friction).</t>
-  </si>
-  <si>
-    <t>Companion WAYBACK recipe recipes/arm_president_wayback.yml (reliable path while the live Radware WAF + engine networkidle block live runs). pagination:wayback over president.am/en/press-release/item -&gt; 8,152 CDX snapshots 2008-2022 (Sargsyan/Sarkissian/Khachaturyan). Probe-verified title/text/date across 2008-2022 (old .news-date + new .date-cub, day-first hy). source_url=president.am/en/press-release/item (Wayback/CDX); source_name=president.am (Wayback); source_type=official_gov (archived); region=Asia; iso3n=51; content_format=fulltext. FULL RUN pending.</t>
-  </si>
-  <si>
-    <t>Reviewer-authored (redirect of the #39 Bangabhaban task). The official presidency site bangabhaban.gov.bd is intractable: every speech is a PDF using a legacy Bijoy-encoded Bangla font (declared /Helvetica, no ToUnicode) so text extraction yields gibberish, and the date is listing-only â€” even PDF-extraction + listing-date engine features would not recover usable text (would need Bijoy-&gt;Unicode conversion or Bangla OCR, out of scope). Redirected to BSS (Bangladesh Sangbad Sangstha, state news agency) English wire: recipes/bgd_bss_president.yml, pagination:none over https://www.bssnews.net/news/president. Probe-verified clean title(.headline_content_block)/text(#details_content p)/date(.entry_update) across 2026-05..2026-07 (~25 recent President-category articles; third-person official_statement reportage of President Mohammed Shahabuddin). source_url=https://www.bssnews.net/news/president; source_name=bssnews.net (BSS); source_type=state_news_agency; region=Asia; iso3n=50; content_format=fulltext. FULL RUN pending. Follow-ups: a wayback companion for older history; a Chief-Adviser category for the interim head of government.</t>
-  </si>
-  <si>
-    <t>Reviewer networked-probe outcome. Recipe recipes/bgr_president.yml uses pagination:sitemap over president.bg/sitemap.xml (children sitemap_000/001.xml) â€” 4,379 clean absolute /newsNNNN/*.html permalinks, probe-verified title(h2.article-title)/text(.print-content)/date(.date) across 2012-2016 (Plevneliev era). NOTE language is Bulgarian not English (copilot had it wrong); dates are Bulgarian month names -&gt; date_languages:[bg]. The LIVE /news/page/N/ listing is NOT scrapable by the engine: the site sets &lt;base href=root&gt; and uses relative ./newsNNNN/ hrefs, so urljoin against /news/page/N/ yields non-canonical paths that soft-404 to the homepage (an engine &lt;base&gt;-tag limitation, not a recipe issue); the stale sitemap also stops at ~2016. FOLLOW-UPS (yes-and): a wayback recipe would cover the 2017-2026 Radev-era gap, and honoring &lt;base href&gt; in the engine would unlock the live listing. source_url=president.bg/sitemap.xml; source_name=president.bg; source_type=official_gov; region=Europe; iso3n=100; content_format=fulltext. FULL RUN pending.</t>
-  </si>
-  <si>
-    <t>Reviewer networked-probe outcome (supersedes the btn_pmo draft: pmo.gov.bt is DEAD â€” 503/connection-fail live, ~0 speeches in IA). Bhutan's official web presence is largely dead: royalkidu.bt does not resolve, bhutan.gov.bt fails DNS, nab.gov.bt is down and its speeches are AUDIO/VIDEO (.mp4/.mp3) not text. Only recoverable leader-speech TEXT: royalkidu.bt's archived 'Royal Address' section (His Majesty the King's COVID-era Addresses to the Nation, 2020). Recipe recipes/btn_royalkidu_wayback.yml = pagination:wayback over royalkidu.bt -&gt; probe-verified clean title(h1.entry-title)/text(.entry-content)/date(time.entry-date) on the 2020 addresses. SMALL corpus (~2 addresses) but genuine head-of-state text and the only Bhutan content available. speaker_default=Jigme Khesar Namgyel Wangchuck (King). source_url=royalkidu.bt (Wayback/CDX); source_name=royalkidu.bt (Wayback); source_type=official (archived, defunct); region=Asia; iso3n=64; content_format=fulltext. FOLLOW-UP: nab.gov.bt has ~200 archived audio/video speeches for the video_audio_scraper+Whisper; revisit if a live King's-office/PMO site returns. FULL RUN pending.</t>
-  </si>
-  <si>
-    <t>Reviewer networked-probe outcome. prc.cm/en Presidency of Cameroon (Joomla K2), speeches-of-the-president archive. FIXED copilot recipe: pagination step 10-&gt;8 (page size is 8; step 10 SKIPPED 2 speeches/page). Probe-verified title(h2)/text(article) + speaker_default Paul Biya across the full archive (~90 English speeches, ids 8251..1155, ~2012-2026; ?start offset pager, engine auto-stops). DATE: there is NO machine-readable date on the detail pages (no &lt;time&gt;/meta/created-attr) and no date in the Joomla-id URL; ~50%% of TITLES contain DD-Month-YYYY but a title date-regex is UNSAFE (engine first_match returns whole text on regex-miss -&gt; parse_date stamps TODAY as garbage). So date is intentionally None at scrape and filled downstream by clean_structure_metadata GPT date pass. ENGINE FEATURE that would date ~50%% safely at scrape: a strict date-regex option (return None on miss, do not fall through to whole-text). source_url=https://www.prc.cm/en/news/speeches-of-the-president; source_name=prc.cm; source_type=official_gov; region=Africa; iso3n=120; content_format=fulltext. FULL RUN pending.</t>
-  </si>
-  <si>
-    <t>NEW master row needed | country=Colombia; source_url=https://www.presidencia.gov.co/prensa/Paginas/discursos.aspx; source_name=presidencia.gov.co; source_type=official_gov; region=South America; iso3n=170; content_format=fulltext. recipe recipes/col_presidencia.yml on main (issue #7) â€” SharePoint CSWP via renderer:js + browser user_agent + click pager; probe-validated, FULL RUN pending (date coverage TBD).</t>
-  </si>
-  <si>
-    <t>NEW master row needed | country=Costa Rica; source_url=https://www.presidencia.go.cr/noticias/; source_name=presidencia.go.cr; source_type=official_gov; region=Central America; iso3n=188; content_format=fulltext. Site now uses /noticias/ listing (legacy /comunicados/ links still matched).</t>
-  </si>
-  <si>
-    <t>Reviewer networked-probe outcome. predsjednik.hr has NO sitemap (/sitemap.xml + /sitemap_index.xml 404 -&gt; the draft's pagination:sitemap returned 0). Recipe recipes/hrv_predsjednik.yml switched to the live /vijesti/page/{n}/ pager (6 articles/page, absolute hrefs, ~420 links over 70 pages; deeper pages reach the MilanoviÄ‡ era from 2020). Probe-verified title(h1)/text(.p-post-single__content)/date(.p-post-single__meta, Croatian '03. srpnja 2026.' via date_languages:[hr]) across 2025-2026. source_url=https://www.predsjednik.hr/vijesti/; source_name=predsjednik.hr; source_type=official_gov; region=Europe; iso3n=191; content_format=fulltext. FULL RUN pending.</t>
-  </si>
-  <si>
-    <t>NEW master row needed | country=Indonesia; source_url=https://setkab.go.id/en/category/speech-transcript/; source_name=setkab.go.id; source_type=official_gov; region=Asia; iso3n=360; content_format=fulltext. Cabinet Secretariat 'Speech Transcript' archive: ~200 pages of full presidential transcripts, WordPress-style /page/N/ pagination. SSL cert chain does not verify -&gt; likely needs verify_ssl: false. Indonesian-language originals at setkab.go.id/kategori/. GitHub issue #45 already opened - do NOT re-run create_issues_from_master.py for this row.</t>
-  </si>
-  <si>
-    <t>Supersedes the prior 2026-07-03 proposed row. Follow-up selector fix: broadened listing selectors/pattern for JNews/WordPress variants so transcript links harvest correctly. Pending live probe/run confirmation outside this sandbox (setkab.go.id DNS unavailable here).</t>
-  </si>
-  <si>
-    <t>NEW master row needed | country=India; source_url=https://www.pmindia.gov.in/en/; source_name=pmindia.gov.in; source_type=official_gov; region=Asia; iso3n=356; content_format=fulltext. PM Modi is India's actual national leader (the President in master is ceremonial). The /en/speeches/ section is largely video; look for text under /en/pms-speeches/ or fall back to narendramodi.in/category/text-speeches. GitHub issue #43 already opened - do NOT re-run create_issues_from_master.py for this row.</t>
-  </si>
-  <si>
-    <t>NEW master row needed | country=Philippines; source_url=https://pco.gov.ph/presidential-speech/; source_name=pco.gov.ph; source_type=official_gov; region=Asia; iso3n=608; content_format=fulltext. Presidential Communications Office 'Presidential Speeches' (Marcos Jr.), /page/N/ pagination. Returns HTTP 403 to the bot UA (WAF) -&gt; likely needs a browser user_agent override (cf. recipes/col_presidencia.yml). Scraper-friendlier historical alternative: https://www.officialgazette.gov.ph/section/historical-papers-documents/speeches/. GitHub issue #46 already opened - do NOT re-run create_issues_from_master.py for this row.</t>
-  </si>
-  <si>
-    <t>Follow-up to issue #46 / review comment; supersedes the 2026-07-03 proposed phl_pco row above. Switched the draft recipe from https://pco.gov.ph/presidential-speech/ to the scraper-friendlier Official Gazette speech archives at https://www.officialgazette.gov.ph/section/speeches/ and https://www.officialgazette.gov.ph/section/historical-papers-documents/speeches/ after reviewer confirmation that pco.gov.ph returns hard 403/WAF responses to both bot and browser UAs. Recipe now assumes standard WordPress archive pagination and entry-title / entry-date / entry-content extraction; keep status draft until a networked probe confirms non-zero listings and clean extraction.</t>
-  </si>
-  <si>
-    <t>Reviewer networked-probe outcome (supersedes the two rows above): the LIVE Official Gazette (www.officialgazette.gov.ph) is ALSO behind a Cloudflare managed challenge ('Just a moment...') â€” 403 to bot+browser UA and Playwright times out â€” same as pco.gov.ph, so NO live recipe is buildable. Recipe recipes/phl_pco.yml is now a pagination:wayback harvest over the IA CDX of the Official Gazette domain, filtered to dated speech-slug permalinks (~1,160 unique, 1899-2024, Quezon..Marcos Jr., incl. SONAs/inaugurals). Probe-verified clean extraction (title/text/date) across 1948-2015. source_url=officialgazette.gov.ph (Wayback/CDX); source_name=officialgazette.gov.ph (Wayback); source_type=official_gov (archived); region=Asia; iso3n=608; content_format=fulltext. FULL RUN pending.</t>
-  </si>
-  <si>
     <t>NEW master row needed | country=Thailand; source_url=https://www.thaigov.go.th/en/news; source_name=thaigov.go.th; source_type=official_gov; region=Asia; iso3n=764; content_format=fulltext. Royal Thai Government news portal carrying PM statements/speeches (the Royal Office in master is the ceremonial monarchy). English + Thai listings. GitHub issue #44 already opened - do NOT re-run create_issues_from_master.py for this row.</t>
   </si>
   <si>
-    <t>Indonesia</t>
-  </si>
-  <si>
-    <t>Colombia</t>
+    <t>kor_president</t>
+  </si>
+  <si>
+    <t>Korea, Republic of</t>
+  </si>
+  <si>
+    <t>president.go.kr</t>
+  </si>
+  <si>
+    <t>https://www.president.go.kr/</t>
+  </si>
+  <si>
+    <t>President</t>
+  </si>
+  <si>
+    <t>Korean/English</t>
+  </si>
+  <si>
+    <t>Office of the President; speeches likely under /newsroom/speeches. SPA-style -&gt; probably renderer:js. Reachable. Backlog target.</t>
+  </si>
+  <si>
+    <t>pak_pmo</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>pmo.gov.pk</t>
+  </si>
+  <si>
+    <t>https://pmo.gov.pk/</t>
+  </si>
+  <si>
+    <t>Prime Minister (Shehbaz Sharif)</t>
+  </si>
+  <si>
+    <t>English/Urdu</t>
+  </si>
+  <si>
+    <t>PM's Office. Timed out from reviewer location (slow/geo-restricted) - verify. president.gov.pk is the ceremonial head of state. Backlog target.</t>
+  </si>
+  <si>
+    <t>bra_planalto</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>gov.br/planalto (Presidencia)</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/planalto/pt-br/acompanhe-o-planalto/discursos-e-pronunciamentos</t>
+  </si>
+  <si>
+    <t>President (Lula)</t>
+  </si>
+  <si>
+    <t>Portuguese</t>
+  </si>
+  <si>
+    <t>Presidencia da Republica 'discursos e pronunciamentos'. Base gov.br/planalto verified; heavy site (may need js). Backlog target.</t>
+  </si>
+  <si>
+    <t>rus_kremlin</t>
+  </si>
+  <si>
+    <t>Russian Federation</t>
+  </si>
+  <si>
+    <t>kremlin.ru</t>
+  </si>
+  <si>
+    <t>http://en.kremlin.ru/events/president/transcripts</t>
+  </si>
+  <si>
+    <t>President (Putin)</t>
+  </si>
+  <si>
+    <t>Russian/English</t>
+  </si>
+  <si>
+    <t>Kremlin transcripts (extensive EN + RU). Verified reachable. Corpus currently has Russia only via MaerzSchneider (no prior Dean scrape). Backlog target.</t>
+  </si>
+  <si>
+    <t>ven_alopresidente</t>
+  </si>
+  <si>
+    <t>Venezuela, Bolivarian Republic of</t>
+  </si>
+  <si>
+    <t>Alo Presidente (Internet Archive)</t>
+  </si>
+  <si>
+    <t>https://archive.org/search?query=Alo+Presidente+Chavez</t>
+  </si>
+  <si>
+    <t>tv_program (archived)</t>
+  </si>
+  <si>
+    <t>Hugo Chavez (Alo Presidente)</t>
+  </si>
+  <si>
+    <t>video/audio</t>
+  </si>
+  <si>
+    <t>Chavez's weekly 'Alo Presidente' broadcasts archived on archive.org (video/audio -&gt; video_audio_scraper + Whisper). Transcripts at todochavez.gob.ve (timed out - verify). Backlog target.</t>
+  </si>
+  <si>
+    <t>chn_statecouncil</t>
+  </si>
+  <si>
+    <t>China</t>
+  </si>
+  <si>
+    <t>english.www.gov.cn (State Council)</t>
+  </si>
+  <si>
+    <t>https://english.www.gov.cn/</t>
+  </si>
+  <si>
+    <t>Premier / State Council</t>
+  </si>
+  <si>
+    <t>Chinese/English</t>
+  </si>
+  <si>
+    <t>State Council English portal (verified). NOTE: Xi Jinping's own speeches are harder - via Xinhua news.cn or MFA fmprc.gov.cn; this site is more Premier/govt. Decide leader scope. Backlog target.</t>
+  </si>
+  <si>
+    <t>sau_spa</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Middle East</t>
+  </si>
+  <si>
+    <t>spa.gov.sa (Saudi Press Agency)</t>
+  </si>
+  <si>
+    <t>https://www.spa.gov.sa/en</t>
+  </si>
+  <si>
+    <t>King / Crown Prince</t>
+  </si>
+  <si>
+    <t>Arabic/English</t>
+  </si>
+  <si>
+    <t>Saudi Press Agency (verified) - royal speeches/statements as a state-news wire (BSS-style). Backlog target.</t>
+  </si>
+  <si>
+    <t>mys_pmo</t>
+  </si>
+  <si>
+    <t>Malaysia</t>
+  </si>
+  <si>
+    <t>pmo.gov.my</t>
+  </si>
+  <si>
+    <t>https://www.pmo.gov.my/ucapan/</t>
+  </si>
+  <si>
+    <t>Prime Minister (Anwar Ibrahim)</t>
+  </si>
+  <si>
+    <t>Malay/English</t>
+  </si>
+  <si>
+    <t>PM's Office 'ucapan' (speeches) section (base verified). Backlog target.</t>
+  </si>
+  <si>
+    <t>dza_presidency</t>
+  </si>
+  <si>
+    <t>Algeria</t>
+  </si>
+  <si>
+    <t>el-mouradia.dz</t>
+  </si>
+  <si>
+    <t>https://www.el-mouradia.dz/</t>
+  </si>
+  <si>
+    <t>President (Tebboune)</t>
+  </si>
+  <si>
+    <t>Arabic/French</t>
+  </si>
+  <si>
+    <t>Presidency of Algeria. Connection reset from reviewer location (WAF/geoblock) - verify; may need user_agent or renderer:js. Backlog target.</t>
+  </si>
+  <si>
+    <t>mmr_gnlm</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>Global New Light of Myanmar (state paper)</t>
+  </si>
+  <si>
+    <t>https://www.gnlm.com.mm/</t>
+  </si>
+  <si>
+    <t>state_news</t>
+  </si>
+  <si>
+    <t>SAC Chairman / State (Min Aung Hlaing)</t>
+  </si>
+  <si>
+    <t>English/Burmese</t>
+  </si>
+  <si>
+    <t>State newspaper (verified) - carries SAC/president speeches in English (BSS-style). president-office.gov.mm is down. Junta context - sensitive. Backlog target.</t>
+  </si>
+  <si>
+    <t>can_pmo</t>
+  </si>
+  <si>
+    <t>Canada</t>
+  </si>
+  <si>
+    <t>pm.gc.ca</t>
+  </si>
+  <si>
+    <t>https://www.pm.gc.ca/en/news/speeches</t>
+  </si>
+  <si>
+    <t>Prime Minister</t>
+  </si>
+  <si>
+    <t>English/French</t>
+  </si>
+  <si>
+    <t>PM's Office speeches. Corpus already has 1,000 Canada Dean_scrape speeches (2000-2022) - add to keep current. Backlog target.</t>
+  </si>
+  <si>
+    <t>ago_angop</t>
+  </si>
+  <si>
+    <t>Angola</t>
+  </si>
+  <si>
+    <t>ANGOP (state news agency)</t>
+  </si>
+  <si>
+    <t>https://www.angop.ao/pt/angola/politica/discursos-do-presidente/</t>
+  </si>
+  <si>
+    <t>President (Joao Lourenco)</t>
+  </si>
+  <si>
+    <t>ANGOP state news 'Discursos do Presidente' section (presidencia.gov.ao is the official presidency). Backlog target.</t>
+  </si>
+  <si>
+    <t>cod_presidence</t>
+  </si>
+  <si>
+    <t>Congo, The Democratic Republic of the</t>
+  </si>
+  <si>
+    <t>presidence.cd</t>
+  </si>
+  <si>
+    <t>https://www.presidence.cd/</t>
+  </si>
+  <si>
+    <t>President (Tshisekedi)</t>
+  </si>
+  <si>
+    <t>Presidency of the DRC (verified reachable). Backlog target.</t>
+  </si>
+  <si>
+    <t>scrape attempts might be getting blocked, but recipe was validated.</t>
   </si>
 </sst>
 </file>
@@ -1881,7 +2175,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q123"/>
+  <dimension ref="A1:Q125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1928,3570 +2222,3925 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>469</v>
+        <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D2">
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3">
         <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>51</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>434</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="Q4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6">
         <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D7">
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D8">
         <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="N8" t="s">
-        <v>462</v>
+        <v>23</v>
       </c>
       <c r="Q8" t="s">
-        <v>468</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D9">
         <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N9" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>604</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="N10" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="P10" t="s">
+        <v>61</v>
       </c>
       <c r="Q10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>467</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D11">
         <v>64</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="N11" t="s">
-        <v>466</v>
+        <v>34</v>
       </c>
       <c r="Q11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D12">
         <v>100</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="N12" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D13">
         <v>108</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="N13" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="P13" t="s">
+        <v>61</v>
       </c>
       <c r="Q13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D14">
         <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="N14" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Q14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D15">
         <v>188</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F15" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H15" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="N15" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="Q15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D16">
         <v>191</v>
       </c>
       <c r="E16" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F16" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="N16" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="Q16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D17">
         <v>192</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D18">
         <v>196</v>
       </c>
       <c r="E18" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D19">
         <v>203</v>
       </c>
       <c r="E19" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F19" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D20">
         <v>208</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F20" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q20" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F21" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G21" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="H21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I21" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q21" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" t="s">
         <v>103</v>
       </c>
-      <c r="B22" t="s">
-        <v>96</v>
-      </c>
       <c r="C22" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F22" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q22" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" t="s">
+        <v>116</v>
+      </c>
+      <c r="F23" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
         <v>108</v>
       </c>
-      <c r="B23" t="s">
-        <v>96</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="N23" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" t="s">
         <v>109</v>
-      </c>
-      <c r="F23" t="s">
-        <v>110</v>
-      </c>
-      <c r="G23" t="s">
-        <v>111</v>
-      </c>
-      <c r="H23" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" t="s">
-        <v>101</v>
-      </c>
-      <c r="N23" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E24" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="F24" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" t="s">
+        <v>122</v>
+      </c>
+      <c r="H24" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
         <v>114</v>
       </c>
-      <c r="G24" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" t="s">
-        <v>21</v>
-      </c>
-      <c r="I24" t="s">
-        <v>107</v>
-      </c>
       <c r="N24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q24" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E25" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F25" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G25" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="H25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="N25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q25" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F26" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="H26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I26" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N26" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E27" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="H27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q27" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E28" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="H28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I28" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="N28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q28" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G29" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="H29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I29" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q29" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E30" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F30" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G30" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I30" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="N30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="D31">
         <v>233</v>
       </c>
       <c r="E31" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F31" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q31" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D32">
         <v>231</v>
       </c>
       <c r="E32" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="F32" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q32" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="H33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q33" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D34">
         <v>242</v>
       </c>
       <c r="E34" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q34" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="D35">
         <v>246</v>
       </c>
       <c r="E35" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q35" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D36">
         <v>270</v>
       </c>
       <c r="E36" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F36" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q36" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="D37">
         <v>268</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F37" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="D38">
         <v>276</v>
       </c>
       <c r="E38" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D39">
         <v>288</v>
       </c>
       <c r="E39" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F39" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q39" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D40">
         <v>300</v>
       </c>
       <c r="E40" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F40" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="G40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q40" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D41">
         <v>328</v>
       </c>
       <c r="E41" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F41" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="D42">
         <v>348</v>
       </c>
       <c r="E42" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F42" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="G42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q42" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D43">
         <v>352</v>
       </c>
       <c r="E43" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="F43" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q43" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B44" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D44">
         <v>356</v>
       </c>
       <c r="E44" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F44" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="G44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="D45">
         <v>364</v>
       </c>
       <c r="E45" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F45" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="G45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N45" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D46">
         <v>372</v>
       </c>
       <c r="E46" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F46" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="G46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H46" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="N46" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="Q46" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B47" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D47">
         <v>376</v>
       </c>
       <c r="E47" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F47" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="G47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N47" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q47" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D48">
         <v>380</v>
       </c>
       <c r="E48" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F48" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N48" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q48" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D49">
         <v>392</v>
       </c>
       <c r="E49" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F49" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N49" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q49" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="D50">
         <v>400</v>
       </c>
       <c r="E50" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F50" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N50" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q50" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B51" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="D51">
         <v>398</v>
       </c>
       <c r="E51" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F51" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="G51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N51" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q51" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="D52">
         <v>404</v>
       </c>
       <c r="E52" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F52" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H52" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="I52" t="s">
+        <v>241</v>
       </c>
       <c r="N52" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q52" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="B53" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="D53">
         <v>414</v>
       </c>
       <c r="E53" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F53" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="G53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N53" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q53" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="B54" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="D54">
         <v>417</v>
       </c>
       <c r="E54" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F54" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="G54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N54" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q54" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="B55" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="D55">
         <v>428</v>
       </c>
       <c r="E55" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="F55" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="G55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N55" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q55" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="B56" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="D56">
         <v>422</v>
       </c>
       <c r="E56" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F56" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="G56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N56" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q56" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="D57">
         <v>426</v>
       </c>
       <c r="E57" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F57" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="G57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N57" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q57" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="B58" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="D58">
         <v>440</v>
       </c>
       <c r="E58" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F58" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="G58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N58" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q58" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="B59" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D59">
         <v>442</v>
       </c>
       <c r="E59" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F59" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="G59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N59" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q59" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="B60" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="D60">
         <v>450</v>
       </c>
       <c r="E60" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F60" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N60" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q60" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="B61" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="D61">
         <v>462</v>
       </c>
       <c r="E61" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="F61" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="G61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N61" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q61" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="B62" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="D62">
         <v>470</v>
       </c>
       <c r="E62" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="F62" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="G62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N62" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q62" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="B63" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="D63">
         <v>484</v>
       </c>
       <c r="E63" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="F63" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="G63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q63" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B64" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="D64">
         <v>498</v>
       </c>
       <c r="E64" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F64" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="G64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q64" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="B65" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D65">
         <v>504</v>
       </c>
       <c r="E65" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="F65" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="G65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N65" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D66">
         <v>528</v>
       </c>
       <c r="E66" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="F66" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="G66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="D67">
         <v>554</v>
       </c>
       <c r="E67" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F67" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="G67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N67" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C68" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E68" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F68" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="G68" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="H68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I68" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="N68" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q68" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="B69" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="C69" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E69" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="F69" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="G69" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="H69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="N69" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="Q69" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B70" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="D70">
         <v>807</v>
       </c>
       <c r="E70" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="F70" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="G70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N70" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q70" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B71" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="D71">
         <v>578</v>
       </c>
       <c r="E71" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F71" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="G71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N71" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q71" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>463</v>
+        <v>321</v>
       </c>
       <c r="B72" t="s">
-        <v>464</v>
+        <v>322</v>
+      </c>
+      <c r="F72" t="s">
+        <v>323</v>
       </c>
       <c r="H72" t="s">
-        <v>465</v>
+        <v>324</v>
       </c>
       <c r="N72" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B73" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D73">
         <v>616</v>
       </c>
       <c r="E73" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="F73" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="G73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N73" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q73" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B74" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D74">
         <v>642</v>
       </c>
       <c r="E74" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="F74" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q74" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B75" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D75">
         <v>688</v>
       </c>
       <c r="E75" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="F75" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="G75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N75" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B76" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="D76">
         <v>690</v>
       </c>
       <c r="E76" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="F76" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="G76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N76" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q76" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B77" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="D77">
         <v>694</v>
       </c>
       <c r="E77" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="F77" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="G77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N77" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q77" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="B78" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="D78">
         <v>702</v>
       </c>
       <c r="E78" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="F78" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="G78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N78" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q78" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="B79" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="D79">
         <v>703</v>
       </c>
       <c r="E79" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="F79" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="G79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N79" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q79" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B80" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="D80">
         <v>705</v>
       </c>
       <c r="E80" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="F80" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="G80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N80" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q80" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B81" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D81">
         <v>706</v>
       </c>
       <c r="E81" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="F81" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="G81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N81" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q81" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="B82" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="D82">
         <v>710</v>
       </c>
       <c r="E82" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="F82" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="G82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N82" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q82" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="B83" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="D83">
         <v>724</v>
       </c>
       <c r="E83" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="F83" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="G83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N83" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q83" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B84" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="D84">
         <v>144</v>
       </c>
       <c r="E84" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="F84" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="G84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N84" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q84" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B85" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D85">
         <v>729</v>
       </c>
       <c r="E85" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="F85" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="G85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N85" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q85" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B86" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D86">
         <v>752</v>
       </c>
       <c r="E86" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="F86" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="G86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N86" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q86" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B87" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="D87">
         <v>834</v>
       </c>
       <c r="E87" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="F87" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="G87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N87" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q87" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="B88" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="D88">
         <v>764</v>
       </c>
       <c r="E88" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="F88" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="G88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N88" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q88" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="B89" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="D89">
         <v>626</v>
       </c>
       <c r="E89" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="F89" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="G89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N89" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q89" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="B90" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="D90">
         <v>780</v>
       </c>
       <c r="E90" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="F90" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="G90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N90" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q90" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="B91" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="D91">
         <v>795</v>
       </c>
       <c r="E91" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F91" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="G91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="B92" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="D92">
         <v>792</v>
       </c>
       <c r="E92" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F92" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="G92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N92" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q92" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="B93" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="D93">
         <v>800</v>
       </c>
       <c r="E93" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="F93" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="G93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N93" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q93" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="B94" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D94">
         <v>804</v>
       </c>
       <c r="E94" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="F94" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="G94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N94" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q94" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B95" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D95">
         <v>784</v>
       </c>
       <c r="E95" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="F95" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="G95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N95" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q95" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="B96" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="D96">
         <v>826</v>
       </c>
       <c r="E96" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="F96" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="G96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N96" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q96" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="B97" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="D97">
         <v>840</v>
       </c>
       <c r="E97" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="F97" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="G97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N97" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q97" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="B98" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="D98">
         <v>858</v>
       </c>
       <c r="E98" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="F98" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="G98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N98" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q98" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B99" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="D99">
         <v>860</v>
       </c>
       <c r="E99" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="F99" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="G99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N99" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q99" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="B100" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D100">
         <v>704</v>
       </c>
       <c r="E100" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="F100" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="G100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N100" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q100" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="B101" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="D101">
         <v>716</v>
       </c>
       <c r="E101" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="F101" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="G101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N101" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q101" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="B102" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C102" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D102">
         <v>32</v>
       </c>
       <c r="E102" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="F102" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="G102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H102" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="I102" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="L102" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="M102" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="N102" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="O102" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="P102" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="Q102" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="B103" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C103" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D103">
         <v>250</v>
       </c>
       <c r="E103" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="F103" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="G103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H103" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="I103" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="L103" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="M103" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="N103" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="O103" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="P103" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="Q103" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="B104" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C104" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D104">
         <v>484</v>
       </c>
       <c r="E104" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F104" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="G104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H104" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="I104" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="L104" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="M104" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="N104" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="P104" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="Q104" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="B105" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C105" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="D105">
         <v>152</v>
       </c>
       <c r="E105" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="F105" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="G105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H105" t="s">
-        <v>434</v>
+        <v>51</v>
       </c>
       <c r="I105" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="J105" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="L105" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="M105" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="N105" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="O105" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
       <c r="P105" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="Q105" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>471</v>
+        <v>474</v>
+      </c>
+      <c r="B106" t="s">
+        <v>442</v>
+      </c>
+      <c r="C106" t="s">
+        <v>443</v>
+      </c>
+      <c r="D106">
+        <v>32</v>
+      </c>
+      <c r="E106" t="s">
+        <v>475</v>
+      </c>
+      <c r="F106" t="s">
+        <v>476</v>
+      </c>
+      <c r="G106" t="s">
+        <v>477</v>
       </c>
       <c r="H106" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I106" t="s">
+        <v>478</v>
+      </c>
+      <c r="J106">
+        <v>2007</v>
       </c>
       <c r="K106" s="1">
-        <v>42348</v>
+        <v>2015</v>
       </c>
       <c r="L106" t="s">
-        <v>436</v>
+        <v>447</v>
+      </c>
+      <c r="M106" t="s">
+        <v>448</v>
       </c>
       <c r="N106" t="s">
-        <v>462</v>
-      </c>
-      <c r="P106" s="1">
-        <v>46202</v>
+        <v>34</v>
+      </c>
+      <c r="P106" s="1" t="s">
+        <v>479</v>
       </c>
       <c r="Q106" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>28</v>
+        <v>481</v>
+      </c>
+      <c r="B107" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" t="s">
+        <v>482</v>
+      </c>
+      <c r="D107">
+        <v>51</v>
+      </c>
+      <c r="E107" t="s">
+        <v>483</v>
+      </c>
+      <c r="F107" t="s">
+        <v>484</v>
+      </c>
+      <c r="G107" t="s">
+        <v>477</v>
       </c>
       <c r="H107" t="s">
+        <v>51</v>
+      </c>
+      <c r="I107" t="s">
+        <v>485</v>
+      </c>
+      <c r="J107">
+        <v>2008</v>
+      </c>
+      <c r="K107">
+        <v>2022</v>
+      </c>
+      <c r="L107" t="s">
+        <v>486</v>
+      </c>
+      <c r="M107" t="s">
+        <v>448</v>
+      </c>
+      <c r="N107" t="s">
+        <v>34</v>
+      </c>
+      <c r="P107" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="J107">
-        <v>2022</v>
-      </c>
-      <c r="K107">
-        <v>2026</v>
-      </c>
-      <c r="L107" t="s">
-        <v>481</v>
-      </c>
-      <c r="N107" t="s">
-        <v>462</v>
-      </c>
-      <c r="P107" s="1">
-        <v>46210</v>
-      </c>
       <c r="Q107" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>472</v>
+        <v>488</v>
+      </c>
+      <c r="B108" t="s">
+        <v>48</v>
+      </c>
+      <c r="C108" t="s">
+        <v>482</v>
+      </c>
+      <c r="D108">
+        <v>50</v>
+      </c>
+      <c r="E108" t="s">
+        <v>489</v>
+      </c>
+      <c r="F108" t="s">
+        <v>490</v>
+      </c>
+      <c r="G108" t="s">
+        <v>491</v>
       </c>
       <c r="H108" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I108" t="s">
+        <v>492</v>
       </c>
       <c r="J108">
-        <v>2008</v>
+        <v>2026</v>
       </c>
       <c r="K108">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="L108" t="s">
-        <v>481</v>
+        <v>486</v>
+      </c>
+      <c r="M108" t="s">
+        <v>448</v>
       </c>
       <c r="N108" t="s">
-        <v>462</v>
-      </c>
-      <c r="P108" s="1">
-        <v>46210</v>
+        <v>34</v>
+      </c>
+      <c r="P108" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="Q108" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>473</v>
+        <v>494</v>
+      </c>
+      <c r="B109" t="s">
+        <v>495</v>
+      </c>
+      <c r="F109" t="s">
+        <v>496</v>
       </c>
       <c r="H109" t="s">
-        <v>434</v>
-      </c>
-      <c r="J109">
-        <v>2026</v>
-      </c>
-      <c r="K109">
-        <v>2026</v>
+        <v>33</v>
       </c>
       <c r="L109" t="s">
-        <v>481</v>
+        <v>447</v>
       </c>
       <c r="N109" t="s">
-        <v>462</v>
+        <v>34</v>
       </c>
       <c r="P109" s="1">
-        <v>46211</v>
+        <v>46202</v>
       </c>
       <c r="Q109" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>59</v>
+        <v>498</v>
+      </c>
+      <c r="B110" t="s">
+        <v>499</v>
+      </c>
+      <c r="F110" t="s">
+        <v>500</v>
       </c>
       <c r="H110" t="s">
-        <v>434</v>
-      </c>
-      <c r="J110">
-        <v>2012</v>
-      </c>
-      <c r="K110">
-        <v>2016</v>
+        <v>51</v>
       </c>
       <c r="L110" t="s">
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="N110" t="s">
-        <v>462</v>
-      </c>
-      <c r="P110" s="1">
-        <v>46210</v>
+        <v>34</v>
+      </c>
+      <c r="P110" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="Q110" t="s">
-        <v>492</v>
+        <v>502</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>467</v>
+        <v>503</v>
+      </c>
+      <c r="B111" t="s">
+        <v>205</v>
+      </c>
+      <c r="F111" t="s">
+        <v>504</v>
       </c>
       <c r="H111" t="s">
-        <v>434</v>
-      </c>
-      <c r="J111">
-        <v>2020</v>
-      </c>
-      <c r="K111">
-        <v>2020</v>
+        <v>51</v>
       </c>
       <c r="L111" t="s">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="N111" t="s">
-        <v>462</v>
-      </c>
-      <c r="P111" s="1">
-        <v>46211</v>
+        <v>34</v>
+      </c>
+      <c r="P111" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="Q111" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>67</v>
+        <v>507</v>
+      </c>
+      <c r="B112" t="s">
+        <v>386</v>
+      </c>
+      <c r="F112" t="s">
+        <v>508</v>
       </c>
       <c r="H112" t="s">
-        <v>434</v>
-      </c>
-      <c r="J112">
-        <v>2012</v>
-      </c>
-      <c r="K112">
-        <v>2026</v>
+        <v>51</v>
       </c>
       <c r="L112" t="s">
-        <v>481</v>
+        <v>509</v>
       </c>
       <c r="N112" t="s">
-        <v>462</v>
+        <v>510</v>
       </c>
       <c r="P112" s="1">
-        <v>46210</v>
+        <v>46206</v>
       </c>
       <c r="Q112" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>474</v>
+        <v>512</v>
       </c>
       <c r="B113" t="s">
-        <v>506</v>
+        <v>513</v>
+      </c>
+      <c r="C113" t="s">
+        <v>482</v>
+      </c>
+      <c r="D113">
+        <v>410</v>
+      </c>
+      <c r="E113" t="s">
+        <v>514</v>
+      </c>
+      <c r="F113" t="s">
+        <v>515</v>
+      </c>
+      <c r="G113" t="s">
+        <v>21</v>
       </c>
       <c r="H113" t="s">
-        <v>479</v>
+        <v>33</v>
+      </c>
+      <c r="I113" t="s">
+        <v>516</v>
       </c>
       <c r="L113" t="s">
-        <v>436</v>
+        <v>517</v>
+      </c>
+      <c r="M113" t="s">
+        <v>448</v>
       </c>
       <c r="N113" t="s">
-        <v>462</v>
-      </c>
-      <c r="P113" s="1">
-        <v>46202</v>
+        <v>23</v>
       </c>
       <c r="Q113" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>71</v>
+        <v>519</v>
+      </c>
+      <c r="B114" t="s">
+        <v>520</v>
+      </c>
+      <c r="C114" t="s">
+        <v>482</v>
+      </c>
+      <c r="D114">
+        <v>586</v>
+      </c>
+      <c r="E114" t="s">
+        <v>521</v>
+      </c>
+      <c r="F114" t="s">
+        <v>522</v>
+      </c>
+      <c r="G114" t="s">
+        <v>21</v>
       </c>
       <c r="H114" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I114" t="s">
+        <v>523</v>
       </c>
       <c r="L114" t="s">
-        <v>436</v>
+        <v>524</v>
+      </c>
+      <c r="M114" t="s">
+        <v>448</v>
       </c>
       <c r="N114" t="s">
-        <v>22</v>
-      </c>
-      <c r="P114" s="1">
-        <v>46210</v>
+        <v>23</v>
       </c>
       <c r="Q114" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>75</v>
+        <v>526</v>
       </c>
       <c r="B115" t="s">
+        <v>527</v>
+      </c>
+      <c r="C115" t="s">
+        <v>443</v>
+      </c>
+      <c r="D115">
         <v>76</v>
       </c>
+      <c r="E115" t="s">
+        <v>528</v>
+      </c>
+      <c r="F115" t="s">
+        <v>529</v>
+      </c>
+      <c r="G115" t="s">
+        <v>21</v>
+      </c>
       <c r="H115" t="s">
-        <v>434</v>
-      </c>
-      <c r="J115">
-        <v>2020</v>
-      </c>
-      <c r="K115">
-        <v>2026</v>
+        <v>51</v>
+      </c>
+      <c r="I115" t="s">
+        <v>530</v>
       </c>
       <c r="L115" t="s">
-        <v>483</v>
+        <v>531</v>
+      </c>
+      <c r="M115" t="s">
+        <v>448</v>
       </c>
       <c r="N115" t="s">
-        <v>462</v>
-      </c>
-      <c r="P115" s="1">
-        <v>46210</v>
+        <v>23</v>
       </c>
       <c r="Q115" t="s">
-        <v>497</v>
+        <v>532</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>475</v>
+        <v>533</v>
       </c>
       <c r="B116" t="s">
-        <v>505</v>
+        <v>534</v>
+      </c>
+      <c r="C116" t="s">
+        <v>454</v>
+      </c>
+      <c r="D116">
+        <v>643</v>
+      </c>
+      <c r="E116" t="s">
+        <v>535</v>
+      </c>
+      <c r="F116" t="s">
+        <v>536</v>
+      </c>
+      <c r="G116" t="s">
+        <v>21</v>
       </c>
       <c r="H116" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I116" t="s">
+        <v>537</v>
       </c>
       <c r="L116" t="s">
-        <v>484</v>
+        <v>538</v>
+      </c>
+      <c r="M116" t="s">
+        <v>448</v>
       </c>
       <c r="N116" t="s">
-        <v>478</v>
-      </c>
-      <c r="P116" s="1">
-        <v>46206</v>
+        <v>23</v>
       </c>
       <c r="Q116" t="s">
-        <v>498</v>
+        <v>539</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>475</v>
+        <v>540</v>
       </c>
       <c r="B117" t="s">
-        <v>505</v>
+        <v>541</v>
+      </c>
+      <c r="C117" t="s">
+        <v>443</v>
+      </c>
+      <c r="D117">
+        <v>862</v>
+      </c>
+      <c r="E117" t="s">
+        <v>542</v>
+      </c>
+      <c r="F117" t="s">
+        <v>543</v>
+      </c>
+      <c r="G117" t="s">
+        <v>544</v>
       </c>
       <c r="H117" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I117" t="s">
+        <v>545</v>
       </c>
       <c r="L117" t="s">
-        <v>484</v>
+        <v>447</v>
+      </c>
+      <c r="M117" t="s">
+        <v>546</v>
       </c>
       <c r="N117" t="s">
-        <v>22</v>
-      </c>
-      <c r="P117" s="1">
-        <v>46210</v>
+        <v>23</v>
       </c>
       <c r="Q117" t="s">
-        <v>499</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>476</v>
+        <v>548</v>
       </c>
       <c r="B118" t="s">
-        <v>198</v>
+        <v>549</v>
+      </c>
+      <c r="C118" t="s">
+        <v>482</v>
+      </c>
+      <c r="D118">
+        <v>156</v>
+      </c>
+      <c r="E118" t="s">
+        <v>550</v>
+      </c>
+      <c r="F118" t="s">
+        <v>551</v>
+      </c>
+      <c r="G118" t="s">
+        <v>21</v>
       </c>
       <c r="H118" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I118" t="s">
+        <v>552</v>
       </c>
       <c r="L118" t="s">
-        <v>485</v>
+        <v>553</v>
+      </c>
+      <c r="M118" t="s">
+        <v>448</v>
       </c>
       <c r="N118" t="s">
-        <v>478</v>
-      </c>
-      <c r="P118" s="1">
-        <v>46206</v>
+        <v>23</v>
       </c>
       <c r="Q118" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>205</v>
+        <v>555</v>
       </c>
       <c r="B119" t="s">
-        <v>206</v>
+        <v>556</v>
+      </c>
+      <c r="C119" t="s">
+        <v>557</v>
+      </c>
+      <c r="D119">
+        <v>682</v>
+      </c>
+      <c r="E119" t="s">
+        <v>558</v>
+      </c>
+      <c r="F119" t="s">
+        <v>559</v>
+      </c>
+      <c r="G119" t="s">
+        <v>491</v>
       </c>
       <c r="H119" t="s">
-        <v>434</v>
-      </c>
-      <c r="J119" s="1">
-        <v>40238</v>
-      </c>
-      <c r="K119" s="1">
-        <v>46202</v>
+        <v>51</v>
+      </c>
+      <c r="I119" t="s">
+        <v>560</v>
       </c>
       <c r="L119" t="s">
-        <v>481</v>
+        <v>561</v>
+      </c>
+      <c r="M119" t="s">
+        <v>448</v>
       </c>
       <c r="N119" t="s">
-        <v>209</v>
-      </c>
-      <c r="P119" s="1">
-        <v>46202</v>
+        <v>23</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>562</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>463</v>
+        <v>563</v>
       </c>
       <c r="B120" t="s">
-        <v>464</v>
+        <v>564</v>
+      </c>
+      <c r="C120" t="s">
+        <v>482</v>
+      </c>
+      <c r="D120">
+        <v>458</v>
+      </c>
+      <c r="E120" t="s">
+        <v>565</v>
+      </c>
+      <c r="F120" t="s">
+        <v>566</v>
+      </c>
+      <c r="G120" t="s">
+        <v>21</v>
       </c>
       <c r="H120" t="s">
-        <v>480</v>
+        <v>51</v>
+      </c>
+      <c r="I120" t="s">
+        <v>567</v>
       </c>
       <c r="L120" t="s">
-        <v>486</v>
+        <v>568</v>
+      </c>
+      <c r="M120" t="s">
+        <v>448</v>
       </c>
       <c r="N120" t="s">
-        <v>478</v>
-      </c>
-      <c r="P120" s="1">
-        <v>46206</v>
+        <v>23</v>
       </c>
       <c r="Q120" t="s">
-        <v>501</v>
+        <v>569</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>463</v>
+        <v>570</v>
       </c>
       <c r="B121" t="s">
-        <v>464</v>
+        <v>571</v>
+      </c>
+      <c r="C121" t="s">
+        <v>104</v>
+      </c>
+      <c r="D121">
+        <v>12</v>
+      </c>
+      <c r="E121" t="s">
+        <v>572</v>
+      </c>
+      <c r="F121" t="s">
+        <v>573</v>
+      </c>
+      <c r="G121" t="s">
+        <v>21</v>
       </c>
       <c r="H121" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I121" t="s">
+        <v>574</v>
       </c>
       <c r="L121" t="s">
-        <v>481</v>
+        <v>575</v>
+      </c>
+      <c r="M121" t="s">
+        <v>448</v>
       </c>
       <c r="N121" t="s">
-        <v>462</v>
-      </c>
-      <c r="P121" s="1">
-        <v>46210</v>
+        <v>23</v>
       </c>
       <c r="Q121" t="s">
-        <v>502</v>
+        <v>576</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>463</v>
+        <v>577</v>
       </c>
       <c r="B122" t="s">
-        <v>464</v>
+        <v>578</v>
+      </c>
+      <c r="C122" t="s">
+        <v>482</v>
+      </c>
+      <c r="D122">
+        <v>104</v>
+      </c>
+      <c r="E122" t="s">
+        <v>579</v>
+      </c>
+      <c r="F122" t="s">
+        <v>580</v>
+      </c>
+      <c r="G122" t="s">
+        <v>581</v>
       </c>
       <c r="H122" t="s">
-        <v>434</v>
-      </c>
-      <c r="J122">
-        <v>1899</v>
-      </c>
-      <c r="K122">
-        <v>2024</v>
+        <v>51</v>
+      </c>
+      <c r="I122" t="s">
+        <v>582</v>
       </c>
       <c r="L122" t="s">
-        <v>481</v>
+        <v>583</v>
+      </c>
+      <c r="M122" t="s">
+        <v>448</v>
       </c>
       <c r="N122" t="s">
-        <v>462</v>
-      </c>
-      <c r="P122" s="1">
-        <v>46210</v>
+        <v>23</v>
       </c>
       <c r="Q122" t="s">
-        <v>503</v>
+        <v>584</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="B123" t="s">
-        <v>374</v>
+        <v>586</v>
+      </c>
+      <c r="C123" t="s">
+        <v>462</v>
+      </c>
+      <c r="D123">
+        <v>124</v>
+      </c>
+      <c r="E123" t="s">
+        <v>587</v>
+      </c>
+      <c r="F123" t="s">
+        <v>588</v>
+      </c>
+      <c r="G123" t="s">
+        <v>21</v>
       </c>
       <c r="H123" t="s">
-        <v>434</v>
+        <v>51</v>
+      </c>
+      <c r="I123" t="s">
+        <v>589</v>
       </c>
       <c r="L123" t="s">
-        <v>487</v>
+        <v>590</v>
+      </c>
+      <c r="M123" t="s">
+        <v>448</v>
       </c>
       <c r="N123" t="s">
-        <v>478</v>
-      </c>
-      <c r="P123" s="1">
-        <v>46206</v>
+        <v>23</v>
       </c>
       <c r="Q123" t="s">
-        <v>504</v>
+        <v>591</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>592</v>
+      </c>
+      <c r="B124" t="s">
+        <v>593</v>
+      </c>
+      <c r="C124" t="s">
+        <v>104</v>
+      </c>
+      <c r="D124">
+        <v>24</v>
+      </c>
+      <c r="E124" t="s">
+        <v>594</v>
+      </c>
+      <c r="F124" t="s">
+        <v>595</v>
+      </c>
+      <c r="G124" t="s">
+        <v>491</v>
+      </c>
+      <c r="H124" t="s">
+        <v>51</v>
+      </c>
+      <c r="I124" t="s">
+        <v>596</v>
+      </c>
+      <c r="L124" t="s">
+        <v>531</v>
+      </c>
+      <c r="M124" t="s">
+        <v>448</v>
+      </c>
+      <c r="N124" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>598</v>
+      </c>
+      <c r="B125" t="s">
+        <v>599</v>
+      </c>
+      <c r="C125" t="s">
+        <v>104</v>
+      </c>
+      <c r="D125">
+        <v>180</v>
+      </c>
+      <c r="E125" t="s">
+        <v>600</v>
+      </c>
+      <c r="F125" t="s">
+        <v>601</v>
+      </c>
+      <c r="G125" t="s">
+        <v>21</v>
+      </c>
+      <c r="H125" t="s">
+        <v>51</v>
+      </c>
+      <c r="I125" t="s">
+        <v>602</v>
+      </c>
+      <c r="L125" t="s">
+        <v>458</v>
+      </c>
+      <c r="M125" t="s">
+        <v>448</v>
+      </c>
+      <c r="N125" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>603</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgsch\Dropbox (Personal)\academic_work\LeaderSpeech\github_repo\LeaderSpeech\data\sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B10C2FD-5354-4E2F-9BD9-DD46496B39D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BC2D23-947F-47DD-A110-0438DF4D5E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -6294,7 +6294,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://www.pmo.gov.my/ucapan/</t>
+          <t>https://www.pmo.gov.my/en/category/speeches-en/</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -6333,9 +6333,14 @@
           <t>draft</t>
         </is>
       </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>PM's Office 'ucapan' (speeches) section (base verified). Backlog target.</t>
+          <t>PM's Office 'ucapan' (speeches) section (base verified). Backlog target. || [2026-07-09] source_url fixed: /ucapan/ is a dead legacy archive of ex-PMs (stops ~2020); the live current-PM source is the EN WordPress category /en/category/speeches-en/ (382 links, 2024-2026, Anwar). Recipe recipes/mys_pmo.yml.</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30000" yWindow="1605" windowWidth="24060" windowHeight="13800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4830" yWindow="1140" windowWidth="24060" windowHeight="13800" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1245,7 +1245,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>Live BLOCKED 2026-07-17: Cloudflare interactive challenge ('Just a moment...') for BOTH the honest bot UA and a browser UA, so it is NOT a user_agent problem. Wayback is viable and untried: 2,026 captures under hrad.cz/cs/prezident-cr* spanning 2009-2026 (the whole host has 3,000+ back to 1997).</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1285,23 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>2011</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2026</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Probe-validated 2026-07-17: 568 speeches via sitemap; sampled 2011..2026 (true floor may be earlier - see issue #57). NOT a listing crawl: /taler/ is itself a speech page and the on-page 'load more' is the Umbraco related-content stream (reels/galleries), not speeches. Whole-household archive (King, Queen, Crown Princess...) so speaker is left to the cleaner. DATE IS THE PUBLICATION DATE, occasionally months after delivery.</t>
         </is>
       </c>
     </row>
@@ -1835,17 +1851,23 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>js</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2026</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>auto-seeded from urls_deanscrape.txt</t>
+          <t>Probe-validated 2026-07-17: 334 speeches, 2021-10-11..2026-07-04. Nuxt SPA so renderer=js is mandatory (static HTML has 1 link); JS-only pager -&gt; pagination=click. Floor is Karis's inauguration, so the live site holds ONE president: Kaljulaid (2016-21) would need a wayback companion.</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1907,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>auto-seeded from urls_deanscrape.txt</t>
+          <t>Live DEAD 2026-07-17: NXDOMAIN on every host variant tried (thepresidency.gov.et, www., president.gov.et) - the domain no longer resolves. Wayback is viable and untried: 3,000+ captures spanning 2016-2023. Note Ethiopia's president is ceremonial; eth_pmo (Abiy Ahmed) is the head of government and is the higher-value source.</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1949,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static (pdf)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1935,14 +1957,20 @@
           <t>Prime Minister Abiy Ahmed</t>
         </is>
       </c>
+      <c r="J33" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2023</v>
+      </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>from LeadersSpeeches_Africa.xlsx (2 link(s))</t>
+          <t>Probe-validated 2026-07-17 but PARTIAL: 30 speech PDFs on one page (no pager), full text extracts in Amharic+English, titles come from the PDF's first line. ALL 30 ROWS ARE UNDATED - the date exists only on the listing and the engine cannot carry it onto a PDF row (issue #55). Listing dates are Gregorian 2018-05..2023-10; the FILENAMES use the Ethiopian calendar (2015 = 2023), a trap.</t>
         </is>
       </c>
     </row>
@@ -1982,7 +2010,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Live BLOCKED 2026-07-17: no TCP at all (ConnectTimeout), i.e. dead or geo-fenced; worth one retry from another network. Wayback is viable and untried: 650 captures spanning 2020-2025.</t>
         </is>
       </c>
     </row>
@@ -2017,12 +2050,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static (api)</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2026</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Probe-validated 2026-07-17: 52 speeches, 2024-03-01..2026-06-10 = Stubb's term to date. WordPress REST (categories=21 'Puheet'); the HTML listing is a hash-fragment SPA and RSS carries only 10 of 52. Floor is Stubb's inauguration, so Niinisto (2012-24) is gone -&gt; wayback companion candidate.</t>
         </is>
       </c>
     </row>
@@ -2057,12 +2101,23 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static (pdf)</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2024</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Probe-validated 2026-07-17 but PARTIAL and stale: 58 speech PDFs on one page (?page=N is ignored and re-serves page 1). Dated 2021-06-23..2024-05-05 for 41 of 58 via an MMDDYYYY filename prefix; 17 undated (issue #55). Barrow has been president since 2017 and nothing has been published since May 2024, so this is ~3 of ~9 years.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2157,12 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Live BLOCKED 2026-07-17: DNS resolves (91.232.26.11) but no TCP - ConnectTimeout on http and https, i.e. geo-fence / edge bot-drop (the pak_pmo pattern); worth one retry from another network. Wayback is viable, untried and DEEP: 3,000+ captures spanning 2006-2025 - the best archive-only prospect in this batch.</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2562,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>dropped</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -1200,12 +1200,23 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2026</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Recipe cyp_presidency (draft, probe-validated 2026-07-18). gov.cy WordPress `speech` custom post type (/wp-json/wp/v2/speech, 1647), browser user_agent for the UA-keyed Azure WAF. Coverage floor 2024-06 (gov.cy CMS launch), NOT the 2023 inauguration -&gt; Anastasiades + early Christodoulides need a presidency.gov.cy wayback companion. `speech` type is all-of-government -&gt; cleaner keeps the head-of-state subset.</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1261,7 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Live BLOCKED 2026-07-17: Cloudflare interactive challenge ('Just a moment...') for BOTH the honest bot UA and a browser UA, so it is NOT a user_agent problem. Wayback is viable and untried: 2,026 captures under hrad.cz/cs/prezident-cr* spanning 2009-2026 (the whole host has 3,000+ back to 1997).</t>
+          <t>Live BLOCKED 2026-07-17: Cloudflare interactive challenge ('Just a moment...') for BOTH the honest bot UA and a browser UA, so it is NOT a user_agent problem. Wayback is viable and untried: 2,026 captures under hrad.cz/cs/prezident-cr* spanning 2009-2026 (the whole host has 3,000+ back to 1997). | 2026-07-18: live Cloudflare clears only the first navigation, paginated access re-challenges (Italy/Quirinale pattern) -&gt; not fully unblockable. Wayback companion cze_hrad_wayback authored (draft, 1040 /cs/pro-media/tiskove-zpravy press articles, ~2009-2020 Klaus/Zeman) - see outbox, needs its own row.</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1718,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>from LeadersSpeeches_Africa.xlsx (1 link(s))</t>
+          <t>from LeadersSpeeches_Africa.xlsx (1 link(s)) | 2026-07-18: BLOCKED. sis.gov.eg loads only with verify_ssl=false (broken cert) but is a JS SPA news portal with no sitemap and no locatable presidential-speech section. The real presidency is also blocked: presidency.eg -&gt; Cloudflare 403 (both UAs); presidency.gov.eg -&gt; ConnectTimeout (no TCP). No reachable official-gov speech source for Egypt from here; retry presidency.eg from an Egyptian/residential IP.</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1923,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>Live DEAD 2026-07-17: NXDOMAIN on every host variant tried (thepresidency.gov.et, www., president.gov.et) - the domain no longer resolves. Wayback is viable and untried: 3,000+ captures spanning 2016-2023. Note Ethiopia's president is ceremonial; eth_pmo (Abiy Ahmed) is the head of government and is the higher-value source.</t>
+          <t>Live DEAD 2026-07-17: NXDOMAIN on every host variant tried (thepresidency.gov.et, www., president.gov.et) - the domain no longer resolves. Wayback is viable and untried: 3,000+ captures spanning 2016-2023. Note Ethiopia's president is ceremonial; eth_pmo (Abiy Ahmed) is the head of government and is the higher-value source. | 2026-07-18: wayback companion eth_thepresidency_wayback authored (draft, 53 /eng/index.php/news/item K2 captures, 2015-2021, Sahle-Work Zewde + Mulatu Teshome, ceremonial) - see outbox, needs its own row. The head of government is covered by the live eth_pmo (Abiy).</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2026,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>Live BLOCKED 2026-07-17: no TCP at all (ConnectTimeout), i.e. dead or geo-fenced; worth one retry from another network. Wayback is viable and untried: 650 captures spanning 2020-2025.</t>
+          <t>Live BLOCKED 2026-07-17: no TCP at all (ConnectTimeout), i.e. dead or geo-fenced; worth one retry from another network. Wayback is viable and untried: 650 captures spanning 2020-2025. | 2026-07-18: wayback companion fji_presidentsoffice_wayback authored (draft, 182 speechdetail.php speeches, 2017-2020) - see outbox, needs its own row.</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2173,7 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>Live BLOCKED 2026-07-17: DNS resolves (91.232.26.11) but no TCP - ConnectTimeout on http and https, i.e. geo-fence / edge bot-drop (the pak_pmo pattern); worth one retry from another network. Wayback is viable, untried and DEEP: 3,000+ captures spanning 2006-2025 - the best archive-only prospect in this batch.</t>
+          <t>Live BLOCKED 2026-07-17: DNS resolves (91.232.26.11) but no TCP - ConnectTimeout on http and https, i.e. geo-fence / edge bot-drop (the pak_pmo pattern); worth one retry from another network. Wayback is viable, untried and DEEP: 3,000+ captures spanning 2006-2025 - the best archive-only prospect in this batch. | 2026-07-18: wayback companion geo_president_wayback authored (draft, 512 /en/News/Article captures, 2019-2023, Zourabichvili era) - see outbox, needs its own row.</t>
         </is>
       </c>
     </row>
@@ -2197,12 +2208,17 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2026-07-18: live recipe deu_bundespraesident (draft) = recent Steinmeier items only (GSB ?gtp= pager not synthesisable, pagination:none). The DEEP archive is the wayback companion deu_bundespraesident_wayback (draft): ~11,785 Reden/Interviews across SEVEN presidents at stable dated URLs, back to Weizsaecker 1985 (Koehler 3953, Steinmeier 2524, Wulff 2005, Gauck 1987, Rau 628, Herzog 406, Weizsaecker 281). See outbox - needs its own master row. Unblocked by engine fix #56.</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2258,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2026-07-18: BLOCKED as a speech source - ghana.gov.gh is the whole-of-government PORTAL (no /wp-json, generic ministry sitemap), no presidential-speech stream. The real presidency source is presidency.gov.gh (WordPress, 302 posts), proposed as NEW source gha_presidency (see outbox). Recommend pointing this row at presidency.gov.gh or adding it as a sibling.</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2303,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>2026-07-18: BLOCKED (live) - Akamai returns 403 'Access Denied' to the bot UA, a browser UA AND headless Chromium (datacenter/TLS block). Wayback companion grc_presidency_wayback authored (partial, 168 legacy omil_content.asp speeches, 2003-2008; the modern WordPress era needs a keep_if-on-category pass) - see outbox, needs its own row.</t>
         </is>
       </c>
     </row>
@@ -2317,12 +2343,23 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2026</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Recipe guy_motp (draft, 2026-07-18) points at op.gov.gy: master URL motp.gov.gy is DEAD (NXDOMAIN; office renamed to Office of the President). op.gov.gy WordPress `Speeches` category (id 106) = 106 speeches, Ali's full term 2020-08 -&gt; present. Granger 2015-2020 survives only on the retired motp.gov.gy (wayback). NB source_url still shows the dead motp.gov.gy.</t>
         </is>
       </c>
     </row>
@@ -2397,12 +2434,23 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2026</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Recipe isl_forseti (draft, 2026-07-18). Sitemap over /frettir (510 items; addresses mixed with news -&gt; cleaner filters). Title/date from meta tags: the visible &lt;h1&gt; is polluted with anti-scrape zero-width Unicode and there is no &lt;time&gt; element. Sampled 2025-2026 (Halla Tomasdottir, since 2024-08); Gudni Johannesson 2016-2024 likely needs a wayback companion. Ceremonial head of state.</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2525,23 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>2026</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2026</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Recipe irn_leader (partial, 2026-07-18). leader.ir RSS feed (~30 recent items, Gregorian pubDate sidesteps the Solar-Hijri trap; body fetched from &lt;article id=details&gt;). Supreme Leader Khamenei. RECENT-ONLY; the deep archive needs the JS ?year= listing (Solar-Hijri, unreliable) - a follow-up. Sibling english.khamenei.ir has full English transcripts with real depth (propose separately).</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2666,12 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2026-07-18: BLOCKED (live). Cloudflare clears only the FIRST navigation (headless Chromium loads page 1 = ~12 discorsi) but pagination fires a POST /ricerca that re-triggers an UNSOLVABLE challenge -&gt; full crawl impossible. Article shape /it/discorso/&lt;slug&gt;; JS pager (no hrefs). WAYBACK: /it/discorso only 10 captures; /elementi/N = 40k+ OPAQUE mixed ids (needs a keep_if FULL RUN); old /Discorsi/*.asp 2000-2009 (~1061) is bounded/discorsi-only. HIGH VALUE (Mattarella/Napolitano) - try a residential-IP live crawl or a targeted /elementi keep_if pass.</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2711,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2026-07-18: PARTIAL (structural mismatch). Imperial Household Agency (Emperor Naruhito, ceremonial). Addresses under /watch/okotoba/imperial-family01/ but EACH okotoba page BUNDLES a whole YEAR of addresses per URL (e.g. ceremony2026.html='令和8年' with many dated addresses) + Reiwa/Heisei-era dates in prose -&gt; unfit for the one-URL-one-row engine without a per-address splitter + era-date parser. The higher-value Japan head-of-government source (PM) is delivered as jpn_kantei (NEW, see outbox).</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q158"/>
+  <dimension ref="A1:Q166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>http://www.presidencymaldives.gov.mv/</t>
+          <t>https://presidency.gov.mv/Press/Articles/12</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3417,12 +3417,42 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Gayoom; Nasheed; Waheed; Yameen; Solih; Muizzu</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>SOLVED - correction to earlier 'CF-blocked SPA'. The master's www.presidencymaldives.gov.mv is a Cloudflare-gated redirect whose DESTINATION, presidency.gov.mv, is a PLAIN STATIC site with no CF - target it directly. Probe-validated GREEN: 474 speeches 1979-2026, text .article-body + date .small-text. Speeches = category /Press/Articles/12, ?page=N pager (~48 pages); articles /Press/Article/&lt;id&gt;; date is .small-text under the h1 (NOT .date-text = recent-releases sidebar). Speaker via tenure crosscheck (6 presidents). Recipe: recipes/mdv_presidencymaldives.yml. FULL RUN pending.</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3487,32 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>cdp</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>SOLVED via renderer: cdp (engine issue #62, now implemented). LIVE Malta Presidency. Cloudflare bot-management fingerprint-blocks Playwright's own Chromium (headless AND headful) on detail pages; attaching over CDP to a user-launched real Chrome clears it. Probe-validated GREEN via CDP: 18 links, title h1.elementor-heading-title + text .elementor-widget-theme-post-content + date from the Elementor listing card (item_date, 'Month D, YYYY') all green. WordPress+Elementor; /speeches/&lt;slug&gt; + /speeches/N/ pager. TO RUN: launch Chrome with --remote-debugging-port=9222 (see docs/recipes.md 'Cloudflare-blocked sites'), then scrape; endpoint defaults to localhost:9222. Browser-free fallback for history: mlt_president_wayback (519 speeches). Speaker via tenure crosscheck. Recipe: recipes/mlt_president.yml.</t>
         </is>
       </c>
     </row>
@@ -3505,6 +3555,16 @@
           <t>none</t>
         </is>
       </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Broad gob.mx root - superseded for presidential speeches by mex_presidencia (gob.mx/presidencia, validated) + mex_presidencia_wayback (AMLO). Left as-is; no separate recipe needed.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3537,12 +3597,37 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Romanian</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Probe-validated: 202+ speeches 2013-2026 (Sandu/Dodon/Timofti), text &lt;article&gt;, date &lt;time datetime&gt;. Static, broken TLS -&gt; verify_ssl:false. Per-year CakePHP listings /rom/discursuri/index/YYYY/page:N via path pagination; individual speeches /rom/discursuri/&lt;slug&gt;. Added a politeness block (site throttles ~50 rapid requests -&gt; WinError 10060); keep pacing on FULL RUN. Speaker via tenure crosscheck (3 presidents). Original language Romanian (/eng mirror not used). Recipe: recipes/mda_presedinte.yml. FULL RUN pending.</t>
         </is>
       </c>
     </row>
@@ -3577,12 +3662,27 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Arabic</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Recipe recipes/mar_diplomatie.yml SHIPPED. Arabic ORIGINAL of the King's speeches (complements maroc.ma's English - see new mar_maroc row). Static Drupal; F5/BIG-IP ASM UA-keyed WAF -&gt; browser user_agent; broken TLS -&gt; verify_ssl:false. Scraping WORKS (title h1 + text .field--name-body, 5-7k chars). Two non-blocking caveats: (1) dates are Maghrebi Arabic month names (نونبر/يوليوز/غشت) that dateparser cannot read -&gt; left blank for the cleaner's corrected-date pass (speaker_default King Mohammed VI keeps the tenure crosscheck valid; a Maghrebi-month engine map would fix it at scrape time - see engine issue); (2) probe harvested ~14 links, pagination may be shallow/AJAX beyond page 0 - confirm depth on FULL RUN.</t>
         </is>
       </c>
     </row>
@@ -3617,12 +3717,32 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>js</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Recipe recipes/nld_royalhouse.yml (NB source_id spelling differs from this row's 'nld_royal-house' - reconcile). King Willem-Alexander + royals. Platform-Rijksoverheid Search-UI SPA -&gt; renderer:js; cursor pager not chainable, so the ~60 cursor pages ?current=n_&lt;page&gt;_n are enumerated as 64 start_urls (type:none). Detail pages static (text &lt;main&gt;), date from the /documents/YYYY/MM/DD/ URL. ~600 docs to 2004; cleaner keeps the reigning head of state. Head-of-government companion nld_rijksoverheid is blocked (see its row). Probe-green.</t>
         </is>
       </c>
     </row>
@@ -3657,12 +3777,27 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>cdp</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>SOLVED via renderer: cdp (engine issue #62). New Zealand Governor-General, gg.govt.nz. Cloudflare 'Just a moment' CRASHES the engine's headless Chromium (Page.goto: Page crashed); a user-launched real Chrome via CDP clears it. Probe-validated GREEN via CDP: 60 links, title h1 + text &lt;main&gt; + date &lt;time datetime&gt; all green. Listing /publications/&lt;slug&gt; + 0-indexed ?page= pager. TO RUN: launch Chrome with --remote-debugging-port=9222 (see docs/recipes.md), then scrape. NZ head of government is separately covered green by nzl_beehive. FULL RUN confirms the archive floor. Recipe: recipes/nzl_gg.yml.</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3844,17 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Google Books entry (Obasanjo) - not scrapable as a config recipe. Obasanjo-era speeches would need a different source/approach. The working Nigeria sources are nga_statehouse (live, Tinubu+Buhari 2019-) and nga_statehouse_wayback (Buhari first term 2015-2019).</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3891,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3754,9 +3899,29 @@
           <t>Bola Ahmed Tinubu</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr">
         <is>
           <t>draft</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Re-validated (spread green: text .news-detail-content, date .page-info; 272 links 2019-2026 across Tinubu/Buhari/Osinbajo). Live archive floor ~2019-04 (site rebuilt then). Buhari FIRST term 2015-2019 is covered by the NEW nga_statehouse_wayback companion. Speaker cleaner-assigned. FULL RUN pending.</t>
         </is>
       </c>
     </row>
@@ -3791,12 +3956,37 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Macedonian</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Probe-validated (12/12 spread): 123 items 2024-05..2026-07, all fields green. WordPress (Divi) via WP REST API /wp-json/wp/v2/posts (Macedonian speech cats 5 obrakjanja + 3 intervjua; EN/Albanian dup cats excluded); body .et_pb_post_content. Cloudflare non-challenging to the bot UA. Speaker Siljanovska-Davkova. Predecessor Pendarovski (2019-2024) is NOT in the live WP and looks thin in Wayback (mostly listing pages) - possible follow-up. FULL RUN pending.</t>
         </is>
       </c>
     </row>
@@ -3831,12 +4021,37 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Norwegian</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Probe-validated (10/10 spread): 1232 sitemap speeches (fra_elysee pattern), sampled 2013-2025, archive reaches ~2005. King Harald V + Queen Sonja + Crown Prince Haakon + Crown Princess Mette-Marit. SSR site (Vercel), bot-UA OK. No &lt;time&gt; -&gt; date regex from the Norwegian header line (date_languages nb); speaker from the URL /taler-og-budskap/&lt;royal&gt;/ slug (cleaner normalises, tenure crosscheck keeps head of state). royalcourt.no is the English mirror (not used). Head-of-government companion nor_regjeringen is blocked (see its row). FULL RUN pending.</t>
         </is>
       </c>
     </row>
@@ -5233,6 +5448,16 @@
           <t>Sheinbaum, López Obrador (paging back)</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>Spanish</t>
@@ -5250,12 +5475,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>recipe: recipes/mex_presidencia.yml — validated live</t>
+          <t>Re-validated (spread green: text .article-body, date, context). CHANGE: raised max_pages 50-&gt;130. The filter_origin=archive listing covers ONLY the CURRENT presidency (Sheinbaum, from 2024-10): page ~105 = 2024-10-23, page ~200 empty. max_pages 50 truncated it at ~2025-09 (~11 of ~22 months); 130 captures her full term. AMLO 2018-2024 is NOT in this archive -&gt; NEW mex_presidencia_wayback companion. Speaker cleaner-assigned. FULL RUN pending.</t>
         </is>
       </c>
     </row>
@@ -8906,6 +9131,616 @@
       <c r="Q158" t="inlineStr">
         <is>
           <t>Live presidence.gov.mg is broken (nginx-404) -&gt; wayback. recipes/mdg_presidence_wayback.yml probe-validated for TITLE+TEXT: 1745 Joomla /actualites items 2014-2026. DATE PARTIAL (no clean date element; in-text French regex; relies on downstream date-correction). FULL RUN pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>mar_maroc</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>504</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>maroc.ma (Royal Speeches, EN)</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://maroc.ma/en/royal-speeches-and-messages/royal-speeches</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>King Mohammed VI</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>NEW SOURCE (canonical royal portal; the master's mar_diplomatie is the second, Arabic, source). Probe-validated (10/10 spread): 60 speeches 2012-07..2025-10, all fields green. Official ENGLISH translation. Static Drupal, bot-UA OK. Body .c-wysiwyg; date from the listing card .item-time (DD-MM-YYYY, day-first via 'fr') because the article page's only &lt;time&gt; is a related-news sidebar. 0-indexed Drupal pager (start:0). COVERAGE GAP: floor 2012 (Mohammed VI reigns since 1999); 1999-2012 hard to source. Recipe: recipes/mar_maroc.yml. FULL RUN pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>mex_presidencia_wayback</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>North America</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>484</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>gob.mx/presidencia (Wayback, AMLO)</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2/https://www.gob.mx/presidencia/articulos/version-estenografica</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Andres Manuel Lopez Obrador</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>NEW - Wayback companion to mex_presidencia for the AMLO era (absent from the live archive). Probe-validated: 3475 CDX snapshots, text .article-body 4k-65k chars, date, context green. Two CDX prefixes for the mid-term URL-path change. wayback_to 20241001 hands off to the live recipe. High volume (~2000+ daily transcripts). Recipe: recipes/mex_presidencia_wayback.yml. FULL RUN pending (heavy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>nzl_beehive</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Oceania</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>554</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>beehive.govt.nz (Speeches)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://www.beehive.govt.nz/speeches</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>NZ Prime Minister + ministers</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>NEW - head-of-government companion to the listed Governor-General source nzl_gg. Probe-validated (spread green over 3-page subset: title h1, text &lt;main&gt; 9k-21k chars, date &lt;time&gt;). Imperva Incapsula JS challenge cleared by renderer:js (httpx gets a 212-byte _Incapsula_Resource stub). Listing /speech/&lt;slug&gt; + 0-indexed ?page= pager; archive to mid/late-2000s (max_pages 200, auto-stops). All-of-government - cleaner keeps the PM's. Recipe: recipes/nzl_beehive.yml. FULL RUN pending (js render of ~100+ pages).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>nor_regjeringen</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>578</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>regjeringen.no (Taler og innlegg)</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.regjeringen.no/no/aktuelt/taler_artikler/id1334/</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Norwegian PM + ministers</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Norwegian</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>NEW - head-of-government source (companion to nor_kongehuset). BLOCKED here: Cloudflare 'Just a moment' on ALL HTML (listing + detail, both UAs -&gt; 403), and headless Chromium did NOT clear it even after 9s (harder than gg.govt.nz, which clears at ~7s). The RSS feed /&lt;lang&gt;/rss/Rss/1334/ bypasses CF but is summary-only (~45 items, 118-char descriptions, no pagination) and its links go to CF-blocked detail pages. FIX: (1) run from a residential IP (may clear the challenge); (2) Wayback of /no/aktuelt/&lt;slug&gt;/id&lt;N&gt;/ (server-rendered full text, but /aktuelt/ mixes all doc types - large noisy crawl needing the cleaner's gate). Norway's head of state (King) is covered green by nor_kongehuset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>nld_rijksoverheid</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>528</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>rijksoverheid.nl (toespraken)</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.rijksoverheid.nl/documenten?type=toespraak</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Dutch PM + ministers</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Dutch</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>NEW - head-of-government source (companion to nld_royalhouse). Detail pages ARE static (full text in &lt;main&gt;; date in the /documenten/YYYY/MM/DD/ URL). BLOCKER is the LISTING: a JS Search-UI SPA, no sitemap (sitemaps are nav-only), no RSS. renderer:js renders results but ?type=toespraak is NOT applied on direct load (header 'Alle documenten'; results mix in non-speeches) and pagination is a hash-signed POST /api/search the engine cannot drive, plus a cursor ?current=n_N (drops the type param). FIX: find the correct filtered feed/endpoint, then renderer:js + scoped result list + text &lt;main&gt; + date url_regex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>nga_statehouse_wayback</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>566</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>statehouse.gov.ng (Wayback, old Joomla)</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2/http://www.statehouse.gov.ng/index.php/news</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Muhammadu Buhari (2015-2019)</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>NEW - Wayback companion to nga_statehouse for Buhari's FIRST term. Probe-validated on scraping: 705 snapshots, title .item-page h2 + text .item-page green (1k-9k chars). Old Joomla /index.php/news/&lt;id&gt;-&lt;slug&gt;. ONLY gap is date: the old pages carry NO date element/in-body date, so date is left blank for the cleaner's corrected-date pass (speaker_default Buhari keeps the tenure crosscheck valid). Engine follow-up: use the Wayback capture timestamp as a date fallback. Recipe: recipes/nga_statehouse_wayback.yml. FULL RUN pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>mlt_president_wayback</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>470</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>president.gov.mt (Wayback)</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://web.archive.org/web/2/https://president.gov.mt/diskors</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>George Vella (2019-2024); earlier presidents; early Spiteri Debono</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>NEW - Wayback recipe for the CF-blocked president.gov.mt (probe-green fallback for the live mlt_president). Probe-validated: 519 snapshots, text .elementor-widget-theme-post-content 2.7k-25k chars, date .elementor-post-info__item--type-date (DD.MM.YYYY day-first via 'fr'). WordPress+Elementor; ~985 archived speech pages across redesigns (/diskors-&lt;slug&gt;, /speeches/&lt;slug&gt;, /the-presidents-address-&lt;slug&gt;). A few newer /speeches/ pages lack the date widget. Bilingual EN+MT. Recipe: recipes/mlt_president_wayback.yml. FULL RUN pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>mlt_gov</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>470</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>gov.mt / opm.gov.mt (Malta Government / OPM)</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.gov.mt/</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>js</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Malta Prime Minister (Robert Abela)</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>fulltext</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>NEW - head-of-government source (companion to the listed president source). BLOCKED from this environment, but likely works in a normal browser (same Cloudflare bot-management as president.gov.mt, which the researcher confirmed reads fine on a residential IP). gov.mt, opm.gov.mt (Office of the PM), doi.gov.mt (also broken TLS) and parlament.mt all returned CF 'Attention Required' to httpx from this datacenter IP. I could NOT locate a clean PM 'speeches' listing before the block. FIX: from a residential IP, find the OPM/DOI speeches listing URL, then a renderer:js recipe (or Wayback of it). Not a firewall - bot-management + datacenter-IP fingerprint.</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -3689,7 +3689,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>nld_royal-house</t>
+          <t>nld_royalhouse</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Recipe recipes/nld_royalhouse.yml (NB source_id spelling differs from this row's 'nld_royal-house' - reconcile). King Willem-Alexander + royals. Platform-Rijksoverheid Search-UI SPA -&gt; renderer:js; cursor pager not chainable, so the ~60 cursor pages ?current=n_&lt;page&gt;_n are enumerated as 64 start_urls (type:none). Detail pages static (text &lt;main&gt;), date from the /documents/YYYY/MM/DD/ URL. ~600 docs to 2004; cleaner keeps the reigning head of state. Head-of-government companion nld_rijksoverheid is blocked (see its row). Probe-green.</t>
+          <t>Recipe recipes/nld_royalhouse.yml (source_id aligned from the seeded 'nld_royal-house' to match the recipe/outbox). King Willem-Alexander + royals. Platform-Rijksoverheid Search-UI SPA -&gt; renderer:js; cursor pager not chainable, so the ~60 cursor pages ?current=n_&lt;page&gt;_n are enumerated as 64 start_urls (type:none). Detail pages static (text &lt;main&gt;), date from the /documents/YYYY/MM/DD/ URL. ~600 docs to 2004; cleaner keeps the reigning head of state. Head-of-government companion nld_rijksoverheid is blocked (see its row). Probe-green.</t>
         </is>
       </c>
     </row>
@@ -9435,12 +9435,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q162" t="inlineStr">
         <is>
-          <t>NEW - head-of-government source (companion to nor_kongehuset). BLOCKED here: Cloudflare 'Just a moment' on ALL HTML (listing + detail, both UAs -&gt; 403), and headless Chromium did NOT clear it even after 9s (harder than gg.govt.nz, which clears at ~7s). The RSS feed /&lt;lang&gt;/rss/Rss/1334/ bypasses CF but is summary-only (~45 items, 118-char descriptions, no pagination) and its links go to CF-blocked detail pages. FIX: (1) run from a residential IP (may clear the challenge); (2) Wayback of /no/aktuelt/&lt;slug&gt;/id&lt;N&gt;/ (server-rendered full text, but /aktuelt/ mixes all doc types - large noisy crawl needing the cleaner's gate). Norway's head of state (King) is covered green by nor_kongehuset.</t>
+          <t>Head-of-government (PM) source - not yet built (companion to nor_kongehuset). country=Norway; source_url=https://www.regjeringen.no/no/aktuelt/taler_artikler/id1334/; source_name=regjeringen.no (Taler og innlegg); region=Europe; iso3n=578; source_type=official_gov; content_format=fulltext; leaders_covered=Norwegian PM + ministers | Cloudflare 'Just a moment' that headless can't clear. FIX now available: renderer: cdp (issue #62, implemented) - a CDP-attached real Chrome cleared the challenge in testing (the RSS /&lt;lang&gt;/rss/Rss/1334/ bypasses CF but is summary-only). NOT YET BUILT: needs the correct live speeches listing URL + selectors captured via CDP, then a renderer: cdp recipe. Norway's head of state (King) is covered green by nor_kongehuset. Ask me to build it.</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>NEW - head-of-government source (companion to the listed president source). BLOCKED from this environment, but likely works in a normal browser (same Cloudflare bot-management as president.gov.mt, which the researcher confirmed reads fine on a residential IP). gov.mt, opm.gov.mt (Office of the PM), doi.gov.mt (also broken TLS) and parlament.mt all returned CF 'Attention Required' to httpx from this datacenter IP. I could NOT locate a clean PM 'speeches' listing before the block. FIX: from a residential IP, find the OPM/DOI speeches listing URL, then a renderer:js recipe (or Wayback of it). Not a firewall - bot-management + datacenter-IP fingerprint.</t>
+          <t>Head-of-government (PM) source - not yet built. NEW master row proposed. country=Malta; source_url=https://www.gov.mt/; source_name=gov.mt / opm.gov.mt (Malta Government / OPM); region=Europe; iso3n=470; source_type=official_gov; content_format=fulltext; leaders_covered=Malta Prime Minister (Robert Abela) | Same Cloudflare BOT-MANAGEMENT as president.gov.mt (NOT a firewall, NOT the IP - we run on a residential IP; it fingerprint-blocks the automation client). FIX is now available: renderer: cdp (issue #62, implemented) - attach to a user-launched real Chrome. NOT YET BUILT because I could not locate a clean PM 'speeches' listing URL before the block. NEXT: with a CDP-attached Chrome, find the OPM/DOI speeches listing, then a renderer: cdp recipe (same pattern as mlt_president). Ask me to build it.</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q166"/>
+  <dimension ref="A1:Q180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4113,12 +4113,38 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>cdp</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K73" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>President of Poland (president.pl), ENGLISH edition. Cloudflare case-(c) managed challenge: headless renderer:js only captures the 'Just a moment' shell, so renderer:cdp (attach to a user-launched real Chrome, --remote-debugging-port=9222) is required — probe-validated over CDP on the researcher's own machine (title h1 / text .articles-single__description / date .articles-single__date all green). Three start_urls give the FULL live English record with no wayback needed: /news (Nawrocki, current) + /archives/andrzej-duda/news (Duda 2015-2025) + /archives/bronislaw-komorowski/news (Komorowski 2010-2015); each paginates &lt;base&gt;/news/page,N (page,1 == page 1, start:1). link_pattern '/news/(?!page,)[^/]+,\d+$' catches articles under both the live and archive bases and excludes the pager + galleries. DATE TRAP: even the English edition renders dates in Polish (04 sierpnia 2025) so date_languages:[pl]; the article date is .articles-single__date, NOT the .articles-item__date related-articles sidebar. No speaker_default (three presidents in scope) -&gt; tenure crosscheck. NO wayback recipe: pre-2010 (Kaczyński 2005-10, Kwaśniewski 1995-2005) has an /archives landing page but NO /news listing (English press archive never migrated) and near-zero pre-2010 English CDX captures, so wayback adds ~nothing</t>
         </is>
       </c>
     </row>
@@ -4153,12 +4179,27 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>cdp</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Romanian</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Romania Presidency LIVE site (presidency.ro) — DOCUMENTED BLOCKED, no recipe shipped (needs interactive verification). The site sits behind a 'Verifying your browser' JS challenge (nginx 503 to httpx/headless): renderer:js captured only the challenge shell and even a CDP-attached real Chrome returned the shell inside the engine's settle window — but driving the same real Chrome manually, the page clears to content after ~5s (title 'Discursuri', article links appear). So the live site IS reachable from a user-launched real Chrome with renderer:cdp + a js_settle of ~6s. REMAINING BLOCKER: the /ro/media/discursuri listing has NO server pager (only ~3 links shown); it loads more via JS scroll/'load more', so a click/scroll pager under cdp is needed and could not be validated non-interactively. VALIDATED SELECTORS (from the driven browser): title h2, body .news-details, article URL /ro/media/discursuri/&lt;slug&gt;; date element .link-big-date is UNRELIABLE (crawl/JS artifact). The current president Nicușor Dan (since 2025-05) has only a handful of discursuri so far. FIX PATH: build a live rou_presidency as renderer:cdp + js_settle:6 + a JS load-more pager, verified from the researcher's real Chrome; until then the Iohannis bulk is covered by rou_presidency_wayback (2016-2023)</t>
         </is>
       </c>
     </row>
@@ -4239,12 +4280,38 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Seychelles State House / Office of the President (statehouse.gov.sc/speeches). Static Apache site built with the Nicepage page builder (generic u-* classes, NOT WordPress). Probe --spread GREEN: 292 links spanning 2010-06 .. 2026-07 (Michel, Faure, Ramkalawan, Herminie + occasional VP remarks), title/text/date all green. Speech pages /speeches/&lt;id&gt;/&lt;slug&gt;; pager ?page=N (~30 pages). Selectors: title .u-text-default.u-text-1; body .u-sheet-1 (content sheet; title/date lines leak but cleaner tolerates); date p.u-text-2:not(.u-subtitle):not(.u-small-text) with regex '\d{1,2}\s+\w+\s+20\d\d' (one 2011 page missed the date, negligible). MULTILINGUAL: the default /speeches listing mixes English and French speeches (many 'discours-...' by Michel/Faure) -&gt; source_language English is nominal, trust the cleaner's per-row detection. No speaker_default (multiple presidents + VP) -&gt; tenure crosscheck. NO wayback recipe — VERIFIED, not assumed: the live listing floor (id 2223 = 09 June 2010) is the site's genuine speech-archive floor. Checked (1) live /speeches paginates only to page 30 (floor 2010-06) and low ids &lt;2223 return empty banner pages (no hidden pre-2010 speeches); (2) the OLD site's speeches.php?&amp;start=N listing, archived 2014-2019, bottoms out at the same dates (deepest capture start=200 shows 18/16/09 June 2010) and its individual links were static.php?content_id= info pages, not older speeches; (3) 2008-2010 CDX captures are homepage/static, no speech corpus. So pre-2010 (early Michel 2004-2010, René) was never on the State House site or the Archive; wayback adds nothing</t>
         </is>
       </c>
     </row>
@@ -4279,12 +4346,38 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>2025</v>
+      </c>
+      <c r="K77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Sierra Leone State House (statehouse.gov.sl), President Julius Maada Bio. WordPress; scraped via the REST API /wp-json/wp/v2/posts (bare array, results_path '.'). Probe --spread: title(title.rendered)+date(ISO) GREEN via API for all 285 posts; BODY recovered via the engine's generic extractor (Astra+Elementor theme with NO stable content container — .entry-content/.elementor-widget-theme-post-content miss; verified generic returns the full ~3-4k-char bodies). All categories taken (news 264/statements 47/ecowas 48/press-releases 14) -&gt; cleaner's document_type gate filters. speaker_default Julius Maada Bio (whole install is his presidency); tenure crosscheck fixes strays. COVERAGE LIMIT: the live WP database only retains posts from 2025-01 onward (oldest post 2025-01-01 via order=asc) — Bio's 2018-2024 first term is NOT on the live site. WAYBACK ATTEMPTED AND FOUND INFEASIBLE: the Internet Archive captured only statehouse.gov.sl's day-archive INDEX pages (/YYYY/MM/DD/ — 127 in 2022, similar 2019-2024) and ZERO individual /YYYY/MM/DD/&lt;slug&gt; post captures in any year; the day-index pages carry only truncated 'Read More' excerpts, not full speeches. So Bio 2018-2024 full texts are not recoverable from this source (live-purged + archive-only-as-excerpts) -&gt; FOLLOW-UP: look for Bio 2018-2024 speeches elsewhere (e.g. a news aggregator, or if State House restores the archive)</t>
         </is>
       </c>
     </row>
@@ -4319,12 +4412,38 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Singapore Istana / President's Office (istana.gov.sg) — the master's listed source (ceremonial head of state). Same Isomer (Next.js) static stack as sgp_pmo; renderer:static, enumerated via /sitemap.xml = 953 /newsroom/ URLs. Probe --spread GREEN: 939 links spanning 2014-09 .. 2026 (President Tony Tan 2011-2017, Halimah Yacob 2017-2023, Tharman Shanmugaratnam 2023- ), title(h1)/text(main)/date(regex 'D Month YYYY' from main) all green. No speaker_default (multiple presidents) -&gt; tenure crosscheck. Newsroom mixes speeches/statements -&gt; cleaner's gate filters</t>
         </is>
       </c>
     </row>
@@ -4359,12 +4478,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>js</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Live prezident.sk /page/prejavy is an un-enumerable SPA (shows 1 speech, loads more via a JS control; NO sitemap/RSS/API and ?page/?strana/?offset all 301). Coverage via the Internet Archive instead -&gt; see NEW row svk_prezident_wayback (/article/ CDX 3322 caps 2015-2026: Kiska/Caputova/Pellegrini). The added PM source svk_vlada (vlada.gov.sk) covers Fico 2023-2026.</t>
         </is>
       </c>
     </row>
@@ -4404,7 +4533,17 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>covered_elsewhere</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>up-rs.si now 302-redirects to predsednica-slo.si. Live coverage -&gt; NEW row svn_predsednica (President Pirc Musar, /sl/objave/govori, 379 speeches). Predecessor archive (Drnovsek/Turk/Pahor 2001-2022, ENGLISH Lotus Domino edition) -&gt; NEW row svn_up_rs_wayback. Added PM source svn_gov (gov.si/novice) covers Golob + government.</t>
         </is>
       </c>
     </row>
@@ -4439,12 +4578,38 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Somali</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Somalia Villa Somalia / Office of the President (villasomalia.gov.so). WordPress; scraped via the REST API /wp-json/wp/v2/posts (bare array, results_path '.'). Probe --spread GREEN: 1082 posts spanning 2018-06 .. 2026, title(h1)/text(article)/date(carried api ISO metadata) all green. Categories bayannada(592,'statements')/warbaahin(572,'media')/khudbado(83,'speeches')/speeches(16)/press-statements(54)/press-releases(47) — ALL taken (no filter), cleaner's document_type gate filters. Covers Farmaajo (2017-2022) + Hassan Sheikh Mohamud (2022- , also 2012-2017) -&gt; no speaker_default, tenure crosscheck. BILINGUAL Somali/English (URLs carry /so/ for Somali posts) -&gt; source_language Somali nominal, trust the cleaner's per-row detection. WAYBACK FOLLOW-UP (not built — modest yield): CDX for villasomalia.gov.so spans 2015-2026, but pre-2018 is thin for INDIVIDUAL articles (2016 ~42, 2017 ~161 captures, many are category/media/homepage; ~9 clean /slug/ articles per year sampled). Old-site article: body .entry-content works, date &lt;time&gt; ('August 10, 2016...'), but H1 is the site banner ('Federal Republic of Somalia') so a title selector needs the &lt;title&gt; tag or an inner heading. If pursued: link_pattern for villasomalia.gov.so/(so/|en/)?&lt;slug&gt;/, wayback_to 20180601, title [title], text .entry-content, date time. Marginal gain ~2015-2018 (Hassan Sheikh 1st term end / Farmaajo start) for a data-sparse country</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4644,33 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>covered_elsewhere</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>South Africa Presidency LIVE site (thepresidency.gov.za) — the master's listed source. NO separate recipe shipped: the rebuilt 7th-administration site's speeches listing (/speeches-statements-advisories) is a JS/AJAX Drupal exposed-filter view (only ~3 /node/ links in static HTML; pager ?tid_1=All&amp;...&amp;page=N), AND its content (President Ramaphosa's current speeches, 2024- ) is ALSO published on gov.za/news/speeches, which is scraped cleanly and deeply by zaf_gov. So current presidential coverage comes from zaf_gov and historical from zaf_thepresidency_wayback; a dedicated live thepresidency recipe would be redundant + require renderer:js for the AJAX view. FOLLOW-UP if a presidency-only live feed is wanted: drive the Drupal view with renderer:js + the ?tid_1=All&amp;...&amp;page= pager, node/&lt;id&gt; articles, title h1, body .field--name-body</t>
         </is>
       </c>
     </row>
@@ -4519,12 +4705,38 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Spain — Casa de S.M. el Rey (casareal.es), the master's listed source (King Felipe VI). ASP.NET/SharePoint but the discursos listing paginates via a crawlable GET pager ?pageSize=N&amp;page=N (unlike La Moncloa's __doPostBack). Speeches actividades_discursos_detalle.aspx?data=&lt;ID&gt;. Probe GREEN: title(h1)+date(.date, regex DD.MM.YYYY day-first, es) green; BODY via the engine's generic extractor (unclassed divs; recovers 2.8-3.4k char bodies). Visible data-id range spans 2021-2026 (data=6353..6834); deeper pages reach older (Felipe VI since 2014, possibly Juan Carlos). The listing carries ALL royal-family discursos (King, Queen, Princess of Asturias) -&gt; no speaker_default; the cleaner's speaker pass keeps the King (head of state) and can drop the rest. Spanish -&gt; translation stage fills English. (--spread probe times out only because max_pages 400 makes it paginate the whole archive first; plain probe confirms extraction.)</t>
         </is>
       </c>
     </row>
@@ -4559,12 +4771,27 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>cdp</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>English</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Sri Lanka President LIVE site (president.gov.lk) — DOCUMENTED BLOCKED, no live recipe shipped. Cloudflare 'Just a moment': the honest bot UA AND browser UA both get 403 (incl. /wp-json). Headless renderer:js CLEARS the listing landing (title 'President of Sri Lanka', /news/&lt;slug&gt; links appear) BUT the individual article pages RE-CHALLENGE with a multi-step 'Performing security verification' that a 7s js_settle does not clear, the news list is JS-lazy-loaded, and the pager is broken (/news/page/2 -&gt; ~1 link; ?paged=2 -&gt; 0). So the live site is CF case-(b)/(c) + a JS-heavy WP theme. FIX PATH: renderer:cdp (user-launched real Chrome) + a scroll/click pager, verified interactively; articles are /news/&lt;slug&gt;, title in an inner heading (H1 is the site banner), body/date lazy-loaded. Until then the Sirisena/Gotabaya era is covered by lka_president_wayback (partial)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4831,17 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Live presidency.gov.sd is DEAD (cert exists but no serving site). Post-Bashir Sovereignty Council sites all dead too (tsc.gov.sd / sucouncil.gov.sd no TCP; sudan.gov.sd HTTP 500) — civil war. Only source is the al-Bashir-era archive -&gt; sdn_presidency_wayback (2015-2019).</t>
         </is>
       </c>
     </row>
@@ -4639,12 +4876,30 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Swedish</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Sweden — Royal Court (kungahuset.se), the master's listed source (King Carl XVI Gustaf; ceremonial). GOOD NEWS: there IS a dedicated speeches section /arkiv/tal/YYYY-MM-DD-&lt;slug&gt; with 2611 URLs (H.M. Konungens tal + other royals), date in the URL, and an English edition under /english. TWO BLOCKERS, no recipe shipped yet: (1) the /arkiv/tal/ listing paginates only via JS (no server pager), so enumeration needs the sitemap; (2) kungahuset's sitemap is GZIPPED (/sitemapindex.xml -&gt; /sitemap1.xml.gz, 35204 locs incl. 2611 /arkiv/tal/), and the engine's sitemap harvest fetches text via httpx and does NOT decompress .gz (verified: gets 838KB of raw bytes, 0 &lt;loc&gt;). FIX PATHS: (a) add .gz-sitemap support to the engine's _harvest_sitemap (fetch bytes + gzip-decompress + parse — a generally useful capability; many gov sitemaps are gzipped), then this becomes a clean static sitemap recipe (link_pattern /arkiv/tal/\d{4}-\d{2}-\d{2}-, date url_regex, title h1, body via generic); or (b) renderer:js + a scroll/click pager on the /arkiv/tal/ listing. The King gives few formal speeches (Christmas message, Riksmote opening, state-banquet toasts) but they are high-value head-of-state content</t>
         </is>
       </c>
     </row>
@@ -7587,12 +7842,14 @@
           <t>draft</t>
         </is>
       </c>
-      <c r="P136" s="1" t="n">
-        <v>46219</v>
+      <c r="P136" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Issue #5, authored by Claude (Copilot budget exhausted). PURE-WAYBACK recipe recipes/sdn_presidency_wayback.yml — the live presidency.gov.sd is dead. Recipe-only, engine untouched. CDX for presidency.gov.sd/*: ~4252 statuscode:200 captures spanning 2006-2026, overwhelmingly under /ara/news (3412); filtering to the article shape /ara/news/&lt;id&gt;-&lt;slug&gt; yields 659 distinct articles (site content ~2015 onward; the bulk of captures are the 2019 crawl that froze the site). Probe --spread: 659 snapshots, title(h1.page_title)/text(.node-body)/date all green; sampled articles parsed 2015-02-16..2015-11-02. IMPORTANT DATE TRAP handled: the page has TWO .date elements — the first (ul.sudan_info &lt; div#header_page) renders the CRAWL date, which on an archived capture is the Wayback snapshot date (would stamp everything 2019); the article's real date is in div.post_statics, so the selector is scoped '.post_statics .date'. url_regex fallback added since ~600/659 URLs embed &lt;id&gt;-YYYY-MM-DD-HH-MM-SS. Dates are English abbreviations ('15 Feb 2015') so date_languages: [en]. CAVEATS: language is MIXED (Arabic headlines, many English bodies — trust the cleaner's per-row detection over source_language); content is mostly SHORT NEWS BRIEFS about the presidency (~250-900 chars), not full speech transcripts, so the cleaner's document_type gate will keep official_statement-style rows and reject the rest. No wayback_to bound (no live recipe exists). speaker_default omitted (feed covers President al-Bashir, the VP and presidential assistants). country=Sudan; source_url=http://www.presidency.gov.sd/ara/news; source_name=presidency.gov.sd (dead, via Internet Archive); source_type=official_gov; region=Africa; iso3n=729; content_format=fulltext. FULL RUN pending (researcher gate).</t>
+          <t>RE-VERIFIED 2026-07-21: probe --spread still GREEN, 659 archived articles, title(h1.page_title)/text(.node-body)/date(.post_statics .date) all matching; sampled 2015-02..2015-11. al-Bashir era. No post-Bashir source exists (see sdn_presidency).</t>
         </is>
       </c>
     </row>
@@ -9741,6 +9998,1025 @@
       <c r="Q166" t="inlineStr">
         <is>
           <t>Head-of-government (PM) source - not yet built. NEW master row proposed. country=Malta; source_url=https://www.gov.mt/; source_name=gov.mt / opm.gov.mt (Malta Government / OPM); region=Europe; iso3n=470; source_type=official_gov; content_format=fulltext; leaders_covered=Malta Prime Minister (Robert Abela) | Same Cloudflare BOT-MANAGEMENT as president.gov.mt (NOT a firewall, NOT the IP - we run on a residential IP; it fingerprint-blocks the automation client). FIX is now available: renderer: cdp (issue #62, implemented) - attach to a user-launched real Chrome. NOT YET BUILT because I could not locate a clean PM 'speeches' listing URL before the block. NEXT: with a CDP-attached Chrome, find the OPM/DOI speeches listing, then a renderer: cdp recipe (same pattern as mlt_president). Ask me to build it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>pol_premier</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Chancellery of the Prime Minister (KPRM, gov.pl/web/premier)</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://www.gov.pl/web/premier/wydarzenia</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J167" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Polish</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Chancellery of the Prime Minister (KPRM) via gov.pl/web/premier/wydarzenia. Plain static HTML to the honest bot UA (no Cloudflare, unlike president.pl). Probe --spread GREEN: 2921 links spanning 2018-01 .. 2026-07 (Morawiecki 2017-2023 + Tusk 2023- ), title/text(.editor-content)/date(.event-date, DD.MM.YYYY) all green. Pager ?page=N&amp;size=10, ~294 pages; news cards div.art-prev so link_selector '.art-prev a' keeps us to articles and off the institutional nav (which shares the /web/premier/ prefix). Title falls back to the &lt;title&gt; tag (carries a ' - KPRM - Portal Gov.pl' suffix; the cleaner's GPT pass normalizes it). Multiple PMs in scope -&gt; no speaker_default, tenure crosscheck. This is the KPRM wire (broader than PM speeches); the cleaner's document_type gate keeps speeches/statements and drops routine press. Polish -&gt; translation stage fills English</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>rou_guvern</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Government of Romania / Prime Minister (gov.ro)</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://gov.ro/ro/stiri</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J168" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Romanian</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Government of Romania / Prime Minister (gov.ro/ro/stiri). Plain static HTML to the honest bot UA (Apache, no anti-bot; contrast presidency.ro which is challenge-blocked). Probe --spread GREEN: 1500 links at the 300-page cap spanning 2023-06 .. 2026-07 (PMs Ciucă, Ciolacu, Bolojan), title(.page.w635 h2)/text(.pageDescription)/date all green; max_pages raised to 800 to reach the site's real floor (deeper history exists). Pager ?page=N (5 items/page; the site also emits &amp;page=N which fetches fine). Markup largely unclassed: article title is the first h2 in .page.w635, body is .pageDescription, and the date is an unclassed span 'Sâmbătă, 18 Iulie 2026' pulled by regex '\d{1,2}\s+\w+\s+20\d\d' over .page.w635 (first match = article date at top), date_languages:[ro]. Multiple PMs in scope -&gt; no speaker_default, tenure crosscheck. Broad government wire -&gt; cleaner's document_type gate keeps PM speeches/statements. Romanian -&gt; translation stage fills English</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>rou_presidency_wayback</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>presidency.ro (Iohannis, via Internet Archive)</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>http://www.presidency.ro/ro/media/discursuri</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J169" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K169" t="n">
+        <v>2023</v>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Romanian</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Romania Presidency (presidency.ro) Klaus Iohannis-era speeches (discursuri) via the Internet Archive. PARTIAL: title(h2)/text(.news-details) GREEN over 474 archived captures; DATE is deferred to the cleaner. WHY WAYBACK: live presidency.ro sits behind a 'Verifying your browser' JS challenge that headless renderer:js AND a CDP-attached real Chrome do NOT clear inside the engine's settle window (only clears after ~5s in an interactive browser), and the live /ro/media/discursuri listing loads via JS with no server pager. CDX for presidency.ro/ro/media/discursuri = 480 statuscode:200 captures 2016-2023, ~314 distinct article slugs (heaviest 2022). link_pattern '/ro/media/discursuri/[^/]{10,}' requires a real slug (slugs sometimes carry %E2%80 smart-quote encoding). DATE TRAP handled by OMISSION: .link-big-date renders a crawl/JS artifact on re-crawled captures (garbage — day always 21, year 2026, even future months), not the article date, and slugs carry no date; so the date selectors intentionally miss and dates come from the cleaner's corrected-date pass constrained to Iohannis's 2014-2024 term (mirrors mdg_presidence_wayback). LANGUAGE MIXED: many of Iohannis's addresses are in English -&gt; trust the cleaner's per-row detection. speaker_default=Klaus Iohannis. No wayback_to bound (companion live recipe covers only the current president)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>sgp_pmo</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Prime Minister's Office Singapore (pmo.gov.sg)</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.pmo.gov.sg/newsroom</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J170" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Singapore Prime Minister's Office (pmo.gov.sg) — the ADDED head-of-government source (the master's istana.gov.sg is the ceremonial President). Isomer (Next.js) STATICALLY-generated: full body in raw HTML, renderer:static. Enumerated via /sitemap.xml = 3115 /newsroom/ URLs (the on-page listing shows only ~13 with no server pager). Probe --spread GREEN: 3113 links spanning 2012-11 .. 2026 (PM Lee Hsien Loong, PM Lawrence Wong, SM Tharman, DPM Heng/Gan etc.), title(h1)/text(main)/date all green. DATE: the dedicated date label is a .prose-label-sm-medium that SHARES its class with the speaker + topic labels, so it can't be class-selected -&gt; regex the first 'D Month YYYY' out of &lt;main&gt; (the pub date sits in the header before the body). Multiple office-holders -&gt; no speaker_default, tenure crosscheck; newsroom mixes speeches/press/appointments -&gt; cleaner's document_type gate filters. NO wayback recipe: the live sitemap already reaches ~2012; older Singapore PM speeches (Goh Chok Tong, pre-2004 Lee) live at the National Archives of Singapore (nas.gov.sg) speeches DB = a THIRD-PARTY source (researcher decides inclusion/citation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>svk_vlada</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Government Office of the Slovak Republic / PM (vlada.gov.sk)</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.vlada.gov.sk/tlacove-spravy/</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J171" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Slovak</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Slovakia Government Office / Prime Minister (vlada.gov.sk/tlacove-spravy/) — the ADDED head-of-government source (PM Robert Fico is the dominant political actor; the master's prezident.sk is the ceremonial-ish president). Static site on the Slovak IDSK/govuk design system. Probe --spread GREEN: 601 links spanning 2023-10 .. 2026-07 (Fico's current term, since his 2023-10 appointment / the site's IDSK relaunch), title(h1)/text(article)/date all green. Path pager /tlacove-spravy/stranaN/ (strana1==page 1, start:1). DATE FIX: the article page has several span.idsk-card-meta-date (article date + a 'latest news' sidebar of cards); first_match joins them, so a regex '\d{1,2}\.\s?\d{1,2}\.\s?20\d\d' takes the FIRST = the article's own date (DD.MM.YYYY, date_languages sk). Multiple PMs possible in scope -&gt; no speaker_default, tenure crosscheck. Government wire -&gt; cleaner's document_type gate keeps PM speeches/statements (prihovor/prejav). FOLLOW-UP: older PMs (Ódor, Heger 2021-2023) predate the IDSK feed's 2023-10 floor -&gt; wayback territory if wanted</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>svk_prezident_wayback</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>prezident.sk (President, via Internet Archive)</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.prezident.sk/page/prejavy</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J172" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Slovak</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Slovakia President (prezident.sk) via the Internet Archive — PURE-WAYBACK (like Sudan). WHY: the LIVE prezident.sk /page/prejavy listing is a hard SPA showing only 1 speech, loading the rest via a JS control with NO server pager, NO sitemap, NO RSS and NO reachable AJAX endpoint (?page/?strana/?offset all 301) — it cannot be enumerated; the individual /article/ pages ARE server-rendered but there's no way to list them live. CDX for prezident.sk/article/ = 3322 statuscode:200 captures spanning 2015-2026 (Kiska 2014-2019, Čaputová 2019-2024, Pellegrini 2024- ). Probe --spread over 3300 snapshots: title GREEN (h1/article h1/title fallback chain), date GREEN (.date, DD.MM.YYYY, date_languages sk), BODY via the engine's generic extractor (archived pages wrap the text in nav chrome; the specific selectors clean-miss so generic recovers 500-3000 char bodies). /article/ is the whole news feed -&gt; no speaker_default (three presidents) + cleaner's document_type gate splits speeches (prejavy) from other news. No wayback_to bound (no crawlable live recipe exists)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>svn_predsednica</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>predsednica-slo.si (President</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.predsednica-slo.si/sl/objave/govori</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J173" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Slovenian</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Slovenia President (predsednica-slo.si), Nataša Pirc Musar (2022- ). The master's up-rs.si 302-redirects here. Static site; SPEECHES category /sl/objave/govori, pager ?start=N step 16 (start:0). Probe --spread: title(h1)+date GREEN over 379 links (2024-2026 sampled), BODY via the engine's generic extractor (no stable content container; specific selectors clean-miss -&gt; generic recovers 1300-3900 char bodies). Date from the 'Datum objave 30. 5. 2026' label (regex D. M. YYYY, date_languages sl; misses on a few pages -&gt; cleaner fills). speaker_default Nataša Pirc Musar. link_pattern excludes the category tabs (vse/govori/poslanice/aktivnosti/...). Predecessors (Pahor 2012-2022, Türk 2007-2012, Drnovšek) -&gt; svn_up_rs_wayback (old up-rs.si domain). Slovenian -&gt; translation stage fills English</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>svn_gov</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Government of Slovenia / PM (gov.si)</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.gov.si/novice/</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J174" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Slovenian</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Slovenia Government / Prime Minister (gov.si/novice) — the ADDED head-of-government source (PM Robert Golob; the master's up-rs.si is the ceremonial president). Static; title(h1)/text(article.news-page .content)/date all GREEN. DATE from the /novice/YYYY-MM-DD-slug permalink via url_regex (unambiguous ISO). PAGER GOTCHA: gov.si IGNORES ?page= (re-serves page 1); the real pager is ?start=N step 20 (page 2 = ?start=20, up to ~1930 pages / ~38k items = the whole-of-government archive back to ~2001). No speaker_default / no position -&gt; the cleaner's document_type + speaker pass keep PM Golob's (and other leaders') speeches from the broad ministry wire; raise/lower max_pages (2000) to trade coverage vs cleaning cost. Slovenian -&gt; translation stage fills English</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>svn_up_rs_wayback</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>up-rs.si (President predecessors, via Internet Archive, English edition)</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>http://www.up-rs.si/up-rs/uprs-eng.nsf/dokumentiweb</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J175" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K175" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Slovenia President predecessors via the archived OLD domain up-rs.si (the office moved to predsednica-slo.si in 2022). up-rs.si is a Lotus Domino site; the ENGLISH edition speech documents are /up-rs/uprs-eng.nsf/dokumentiweb/&lt;UNID&gt; (~986 doc captures; CDX for the domain spans 2001-2023, 5000+ captures). Probe --spread over 264 snapshots: title(h1)/text(.inner-page-content)/date all GREEN. DATE from the h2 dateline 'Ljubljana, 28.1.2009 | speech' (regex DD.MM.YYYY, which also carries the doc type). Spans Drnovšek (2002-2007), Türk (2007-2012), Pahor (2012-2022) -&gt; no speaker_default, tenure crosscheck. ENGLISH edition -&gt; straight into English columns, no translation. wayback_to 20221201 keeps it clear of the live svn_predsednica (Pirc Musar). A fuller SLOVENIAN edition exists at uprs.nsf/dokumenti if wanted</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>zaf_gov</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>gov.za (SA Government speeches aggregator)</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.gov.za/news/speeches</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="K176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>South Africa Government speeches aggregator (gov.za/news/speeches) — the DEPTH source the researcher chose (the master's thepresidency.gov.za only shows the current 7th administration). Static Drupal: probe GREEN title(h1)/text(.field--name-body, 7k-15k chars)/date(&lt;time&gt;, '10 Jul 2026') all green; pager ?page=N (0-indexed, deep). Article URLs /news/speeches/&lt;slug&gt;. This is ALL government speeches (President Ramaphosa + ministers), so NO speaker_default / no position -&gt; the cleaner's speaker pass keeps the President's (and other leaders') speeches and the document_type gate filters. (The --spread probe times out only because max_pages 800 makes it paginate the whole archive first; a plain probe confirms extraction.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>zaf_thepresidency_wayback</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Africa</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>thepresidency.gov.za (old Presidency site, via Internet Archive)</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>http://www.thepresidency.gov.za/speeches</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J177" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K177" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>South Africa Presidency OLD site (thepresidency.gov.za) via the Internet Archive. The current site was rebuilt for the 7th administration (2024-, JS/AJAX Drupal view listing) and its current speeches are on gov.za (zaf_gov), so this targets the PREVIOUS Drupal-7 presidency speech archive. CDX for thepresidency.gov.za/speeches = 42k+ captures; the ?page=N referrer variants archive the SAME speech many times, so link_pattern '/speeches/[^?]{12,}$' excludes queries -&gt; 3975 distinct /speeches/&lt;slug&gt; articles. Probe --spread GREEN: title(h1)/date(.date-display-single, 'D Month YYYY') green; body .field-name-body (Drupal-7 single-dash) or the generic extractor. Covers Zuma (to 2018) + Ramaphosa as Deputy President then President (2014-2024) -&gt; no speaker_default, tenure crosscheck. Complements zaf_gov. English</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>esp_lamoncloa_wayback</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>La Moncloa / President of the Government (via Internet Archive)</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.lamoncloa.gob.es/presidente/intervenciones/</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J178" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Spanish</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Spain — La Moncloa / President of the Government (PM) via the Internet Archive. The ADDED head-of-government source (PM Pedro Sánchez; the master's casareal.es is the King). lamoncloa.gob.es is ASP.NET: the /presidente/intervenciones/ listing paginates ONLY via __doPostBack (?pagina/?page ignored; sitemap.xml redirects to a 404; per-year /Paginas/YYYY/ returns nothing) -&gt; the live listing can't be enumerated. The Archive holds the dated .aspx speech pages well: CDX for lamoncloa.gob.es/presidente/intervenciones/Paginas = 2183 statuscode:200 captures spanning 2014-2026 (Rajoy 2014-2018, Sánchez 2018- ). Probe --spread over 230 snapshots: title(h1)/text(.customWidth, 6k-26k chars)/date all GREEN. DATE: from .date ('28.5.2024', DD.M.YYYY day-first, es) — preferred over the URL, whose 8-digit date format is INCONSISTENT across years (2024+ = YYYYMMDD, 2021-earlier = DDMMYYYY, e.g. /2021/13052021-). Rajoy + Sánchez -&gt; no speaker_default, tenure crosscheck. FUTURE UPGRADE: a live renderer:js + click recipe could capture current speeches. Spanish -&gt; translation stage fills English</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>lka_president_wayback</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Asia</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>president.gov.lk (via Internet Archive)</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://president.gov.lk/</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J179" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K179" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Sri Lanka President (president.gov.lk) via the Internet Archive. PARTIAL: title(h1)+body(generic extractor) GREEN over 2107 archived captures; DATE deferred to the cleaner (archived articles carry NO machine-readable date — no date element, no meta). WHY WAYBACK: live president.gov.lk is Cloudflare 'Just a moment' — headless renderer:js CLEARS the listing landing (title 'President of Sri Lanka') but ARTICLE pages RE-CHALLENGE ('Performing security verification', even js_settle=7), the news list is JS-lazy-loaded, the pager is broken (/news/page/2 yields ~1 link), and wp-json is CF+httpx-blocked. CDX for president.gov.lk (domain) = 5000+ captures HEAVY 2016-2020 (3433 in 2019) = Sirisena (2015-2019) / Gotabaya (2019-2022). OLD site uses ROOT-LEVEL article slugs /&lt;slug&gt; (link_pattern requires a 16+ char hyphenated slug, excludes wp/category/tag/page/media). No speaker_default (multiple presidents) -&gt; tenure crosscheck. FOLLOW-UP (live): a renderer:cdp recipe + scroll could capture the current president (Dissanayake 2024- ) and clear the article re-challenge from the researcher's real Chrome; needs /news/&lt;slug&gt; articles</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>swe_regeringen</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>752</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Government Offices of Sweden / PM (regeringen.se)</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.regeringen.se/tal/</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>official_gov</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>static</t>
+        </is>
+      </c>
+      <c r="J180" t="n">
+        <v>1996</v>
+      </c>
+      <c r="K180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Swedish</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>fulltext. FULL RUN pending (researcher gate).</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Sweden — Government Offices / Prime Minister (regeringen.se/tal) — the ADDED head-of-government source (PM Ulf Kristersson; the master's kungahuset.se is the ceremonial King). The /tal/ listing paginates only via JS (?page= ignored), but the sitemap enumerates every speech: /sitemap.xml has 278 /tal/YYYY/MM/&lt;slug&gt; URLs back to 1996. Probe --spread GREEN over 271 links (2015-2025 sampled): title(h1)/text(.has-wordExplanation, 2.7k-8.7k chars)/date(&lt;time&gt;, regex, date_languages sv) all green. Whole-GOVERNMENT feed (PM + ministers) -&gt; no speaker_default / no position; the cleaner's speaker pass + document_type gate keep PM Kristersson's (and other leaders') speeches. English mirror exists at government.se; Swedish is the fuller original -&gt; translation stage fills English</t>
         </is>
       </c>
     </row>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -1,26 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dgsch\Dropbox (Personal)\academic_work\LeaderSpeech\github_repo\LeaderSpeech\data\sources\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B4260A-B2B7-4356-8F84-BBDE1959724F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="780" windowWidth="24285" windowHeight="14370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="780" windowWidth="24285" windowHeight="14370" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2350" uniqueCount="1218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="1279">
   <si>
     <t>source_id</t>
   </si>
@@ -3289,7 +3282,7 @@
     <t>partial</t>
   </si>
   <si>
-    <t/>
+    <t>NA</t>
   </si>
   <si>
     <t>2026-07-26</t>
@@ -3675,13 +3668,200 @@
   </si>
   <si>
     <t>PROBE-VALIDATED 2026-07-26 (live) â€” UNBLOCKS the 2026-07-18 'blocked' status. The site is back up; the /speeches_remarks/ HTML pages are still JS (Elementor) shells that extract badly, BUT the speeches are PDFs served live under /wp-content/uploads/&lt;SLUG&gt;.pdf, linked from the /speeches/ listing (paginates /speeches/page/&lt;N&gt;/, pages 1-41, ~404 speeches back to Dec 2022). LIVE content_type:pdf recipe (recipes/ken_president.yml): 10 links/page, TEXT 1,422-12,179 chars (real Ruto speeches, e.g. 'ACCEPTANCE SPEECH BY HIS EXCELLENCY HON. WILLIAM SAMOEI RUTO...'), TITLE from filename slug via url_regex, speaker_default William Ruto. NOT a WAF (honest bot UA works); the page contains 'cloudflare' (email-obfuscation) which false-trips the #65 block-page guard -&gt; block_page:false. Some PDFs are image scans yielding little text (degrade cleanly). Ruto era only (since Sept 2022); older Kenyatta speeches need a separate source. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">esp_lamoncloa_english_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Moncloa English intervenciones /lang/en/ (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.lamoncloa.gob.es/lang/en/presidente/intervenciones/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">official_gov_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">static</t>
+  </si>
+  <si>
+    <t xml:space="preserve">José Luis Rodríguez Zapatero; Mariano Rajoy; Pedro Sánchez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">English</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulltext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 6): 189 snapshots under /lang/en/presidente/intervenciones/Paginas/&lt;year&gt;/&lt;slug&gt;.aspx; GENUINE English -&gt; TITLE(h1) clean (e.g. 'Speech by Jose Luis Rodriguez Zapatero at investiture debate'), TEXT(.customWidth) 5,947-61,301 chars, DATE(.date) working (some fall to cleaner). ENGLISH sibling of the native esp_lamoncloa_wayback (reuses its SharePoint selectors). English -&gt; English column, no translation. Multiple PMs -&gt; NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">geo_president_english_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Georgia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">president.gov.ge old English 'Speeches &amp; Statements' (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://president.gov.ge/en/PressOffice/News/SpeechesAndStatements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mikheil Saakashvili; Giorgi Margvelashvili</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 6): 597 snapshots under /en/PressOffice/News/SpeechesAndStatements?p=&lt;id&gt;; body confirmed ENGLISH (19,071 Latin/0 Georgian chars on the checked page). TITLE via first .Title element (real headlines, e.g. 'The President of Georgia Mikheil Saakashvili made a special statement...'); TEXT via generic (trafilatura) fallback (4.7k-20.7k chars); DATE-&gt;cleaner. ~1 in 6 pages is an untranslated Georgian article (cleaner language-detection handles). start_urls is the PARENT /News path to dodge the engine listing-path filter (?p= articles share the listing path). NEW English coverage the modern geo_president_wayback lacks. IMPORTANT: the EXISTING merged geo_president_wayback (modern /en/News/Article, source_language English) actually extracts GEORGIAN body+title -&gt; it is mislabeling Georgian as English; researcher should review/fix that recipe. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gha_presidency_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ghana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">presidency.gov.gh old Joomla site (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://presidency.gov.gh/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Atta Mills; John Mahama; Nana Akufo-Addo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 6): 3,068 snapshots (Joomla /index.php/briefing-room/&lt;section&gt;/&lt;id&gt;-&lt;slug&gt;); TITLE(h1, site suffix stripped via lookahead regex), TEXT(.item-page) 1,509-5,837 chars, DATE(time) working (2017-2022). Recovers the OLD Joomla site adding deep depth the live WordPress-REST gha_presidency (Mahama 2025-&gt;) lacks: Mills (2010-2012), Mahama (2012-2017), Akufo-Addo (2017-2024). English-native -&gt; English column. Third-person news gated by cleaner. NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gmb_op_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gambia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office of the President op.gov.gm speech PDFs (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://op.gov.gm/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adama Barrow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 6): 93 PDF snapshots (content_type:pdf over wayback, /sites/default/files/*.pdf, mimetype filter). TEXT extracts (Barrow speeches 5,963-9,204 chars, e.g. 'Statement by His Excellency Adama Barrow...'); speaker_default Adama Barrow; TITLE=PDF first line (weak -&gt; cleaner derives); DATE-&gt;cleaner. PDF-over-wayback companion to the PARTIAL live gmb_op (broken pager). State-House newsletters among the PDFs -&gt; cleaner document-type gate drops them. English-native -&gt; English column. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">guy_motp_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guyana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Americas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ministry of the Presidency motp.gov.gy (dead site; Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://www.motp.gov.gy/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Granger; Irfaan Ali</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 6): 1,337 snapshots (Joomla /index.php/&lt;cat&gt;/&lt;id&gt;-&lt;slug&gt;); TITLE(&lt;title&gt;) clean, TEXT(.item-page) 891-9,468 chars, DATE(.published) working (2016-2019). ARCHIVE-ONLY: motp.gov.gy is DEAD (live guy_motp repointed to op.gov.gy/Ali) -&gt; this is the ONLY source for the David Granger presidency (2015-2020). English-native -&gt; English column. Mix of substantive items + third-person news the cleaner gates. NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ken_president_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kenya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">president.go.ke old WordPress date-path posts (Kenyatta era; Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://www.president.go.ke/category/speeches/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uhuru Kenyatta; Margaret Kenyatta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 8): 4,252 date-path post captures (president.go.ke/&lt;yyyy&gt;/&lt;mm&gt;/&lt;dd&gt;/&lt;slug&gt;/, CDX prefix president.go.ke/20 ~8,000 raw). The OLD pre-Elementor WordPress site (Uhuru Kenyatta era, president 2013-2022) archives as CLEAN HTML (unlike the modern Elementor /speeches_remarks/ JS shells). TITLE(h1.entry-title) clean; TEXT via .entry-content/generic fallback (2.7k-3.9k chars); DATE from the URL permalink via url_regex ONLY (unambiguous ISO; .post-date returns a re-crawl artifact). Posts mix speeches + presidency news -&gt; cleaner document-type gate keeps the speech/official_statement subset. NO speaker_default (Uhuru + First Lady Margaret Kenyatta + quoted ministers) -&gt; cleaner speaker pass + tenure crosscheck. 'yes-and' to the live ken_president (Ruto 2022- PDFs): this is the Kenyatta 2013-2022 corpus. FULL RUN is the researcher's gate.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3715,10 +3895,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4020,11 +4199,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q210"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4077,14 +4256,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="s">
@@ -4115,14 +4294,14 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>969</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="s">
@@ -4140,10 +4319,10 @@
       <c r="I3" t="s">
         <v>971</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>2015</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>2026</v>
       </c>
       <c r="L3" t="s">
@@ -4162,7 +4341,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>977</v>
       </c>
@@ -4215,7 +4394,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>994</v>
       </c>
@@ -4268,7 +4447,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>998</v>
       </c>
@@ -4321,14 +4500,14 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="s">
@@ -4343,7 +4522,7 @@
       <c r="H7" t="s">
         <v>32</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>2026</v>
       </c>
       <c r="L7" t="s">
@@ -4362,14 +4541,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>29</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>8</v>
       </c>
       <c r="E8" t="s">
@@ -4387,7 +4566,7 @@
       <c r="I8" t="s">
         <v>40</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>2026</v>
       </c>
       <c r="L8" t="s">
@@ -4406,14 +4585,14 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>973</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="s">
@@ -4431,10 +4610,10 @@
       <c r="I9" t="s">
         <v>975</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>2018</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>2025</v>
       </c>
       <c r="L9" t="s">
@@ -4453,7 +4632,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>662</v>
       </c>
@@ -4463,7 +4642,7 @@
       <c r="C10" t="s">
         <v>120</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="s">
@@ -4494,7 +4673,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>684</v>
       </c>
@@ -4504,7 +4683,7 @@
       <c r="C11" t="s">
         <v>120</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>24</v>
       </c>
       <c r="E11" t="s">
@@ -4535,7 +4714,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>537</v>
       </c>
@@ -4545,7 +4724,7 @@
       <c r="C12" t="s">
         <v>539</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>32</v>
       </c>
       <c r="E12" t="s">
@@ -4582,7 +4761,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>568</v>
       </c>
@@ -4592,7 +4771,7 @@
       <c r="C13" t="s">
         <v>539</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>32</v>
       </c>
       <c r="E13" t="s">
@@ -4610,10 +4789,10 @@
       <c r="I13" t="s">
         <v>572</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>2007</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="1" t="n">
         <v>2015</v>
       </c>
       <c r="L13" t="s">
@@ -4632,14 +4811,14 @@
         <v>574</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>42</v>
       </c>
       <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>51</v>
       </c>
       <c r="E14" t="s">
@@ -4658,7 +4837,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>575</v>
       </c>
@@ -4668,7 +4847,7 @@
       <c r="C15" t="s">
         <v>576</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>51</v>
       </c>
       <c r="E15" t="s">
@@ -4686,10 +4865,10 @@
       <c r="I15" t="s">
         <v>579</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>2008</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>2022</v>
       </c>
       <c r="L15" t="s">
@@ -4708,14 +4887,14 @@
         <v>580</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>46</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>36</v>
       </c>
       <c r="E16" t="s">
@@ -4734,7 +4913,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>822</v>
       </c>
@@ -4744,7 +4923,7 @@
       <c r="C17" t="s">
         <v>823</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>36</v>
       </c>
       <c r="E17" t="s">
@@ -4762,10 +4941,10 @@
       <c r="I17" t="s">
         <v>825</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>1996</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>2006</v>
       </c>
       <c r="L17" t="s">
@@ -4777,21 +4956,21 @@
       <c r="N17" t="s">
         <v>34</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="Q17" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>50</v>
       </c>
       <c r="B18" t="s">
         <v>51</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>40</v>
       </c>
       <c r="E18" t="s">
@@ -4810,14 +4989,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>54</v>
       </c>
       <c r="B19" t="s">
         <v>55</v>
       </c>
-      <c r="D19">
+      <c r="D19" t="n">
         <v>31</v>
       </c>
       <c r="E19" t="s">
@@ -4836,14 +5015,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>58</v>
       </c>
       <c r="B20" t="s">
         <v>59</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>50</v>
       </c>
       <c r="E20" t="s">
@@ -4865,7 +5044,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>581</v>
       </c>
@@ -4875,7 +5054,7 @@
       <c r="C21" t="s">
         <v>576</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>50</v>
       </c>
       <c r="E21" t="s">
@@ -4893,10 +5072,10 @@
       <c r="I21" t="s">
         <v>585</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>2026</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>2026</v>
       </c>
       <c r="L21" t="s">
@@ -4915,7 +5094,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>750</v>
       </c>
@@ -4925,7 +5104,7 @@
       <c r="C22" t="s">
         <v>576</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>50</v>
       </c>
       <c r="E22" t="s">
@@ -4946,21 +5125,21 @@
       <c r="N22" t="s">
         <v>25</v>
       </c>
-      <c r="P22" s="1">
+      <c r="P22" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="Q22" t="s">
         <v>753</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>65</v>
       </c>
       <c r="B23" t="s">
         <v>66</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>112</v>
       </c>
       <c r="E23" t="s">
@@ -4982,14 +5161,14 @@
         <v>69</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>70</v>
       </c>
       <c r="B24" t="s">
         <v>71</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>56</v>
       </c>
       <c r="E24" t="s">
@@ -5011,14 +5190,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>75</v>
       </c>
       <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>64</v>
       </c>
       <c r="E25" t="s">
@@ -5037,7 +5216,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>618</v>
       </c>
@@ -5047,7 +5226,7 @@
       <c r="C26" t="s">
         <v>539</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>76</v>
       </c>
       <c r="E26" t="s">
@@ -5078,7 +5257,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>715</v>
       </c>
@@ -5088,7 +5267,7 @@
       <c r="C27" t="s">
         <v>539</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>76</v>
       </c>
       <c r="E27" t="s">
@@ -5106,10 +5285,10 @@
       <c r="I27" t="s">
         <v>718</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>2023</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>2024</v>
       </c>
       <c r="L27" t="s">
@@ -5128,7 +5307,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>787</v>
       </c>
@@ -5138,7 +5317,7 @@
       <c r="C28" t="s">
         <v>788</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>76</v>
       </c>
       <c r="E28" t="s">
@@ -5153,10 +5332,10 @@
       <c r="H28" t="s">
         <v>62</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>2003</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>2010</v>
       </c>
       <c r="L28" t="s">
@@ -5168,14 +5347,14 @@
       <c r="N28" t="s">
         <v>25</v>
       </c>
-      <c r="P28" s="1">
+      <c r="P28" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q28" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>793</v>
       </c>
@@ -5185,7 +5364,7 @@
       <c r="C29" t="s">
         <v>788</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>76</v>
       </c>
       <c r="E29" t="s">
@@ -5200,10 +5379,10 @@
       <c r="H29" t="s">
         <v>62</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>2003</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>2010</v>
       </c>
       <c r="L29" t="s">
@@ -5215,14 +5394,14 @@
       <c r="N29" t="s">
         <v>34</v>
       </c>
-      <c r="P29" s="1">
+      <c r="P29" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q29" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>797</v>
       </c>
@@ -5232,7 +5411,7 @@
       <c r="C30" t="s">
         <v>788</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>76</v>
       </c>
       <c r="E30" t="s">
@@ -5247,10 +5426,10 @@
       <c r="H30" t="s">
         <v>62</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>2011</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>2022</v>
       </c>
       <c r="L30" t="s">
@@ -5262,21 +5441,21 @@
       <c r="N30" t="s">
         <v>34</v>
       </c>
-      <c r="P30" s="1">
+      <c r="P30" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q30" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>79</v>
       </c>
       <c r="B31" t="s">
         <v>80</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>100</v>
       </c>
       <c r="E31" t="s">
@@ -5295,14 +5474,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>83</v>
       </c>
       <c r="B32" t="s">
         <v>84</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>108</v>
       </c>
       <c r="E32" t="s">
@@ -5324,14 +5503,14 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>87</v>
       </c>
       <c r="B33" t="s">
         <v>88</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>120</v>
       </c>
       <c r="E33" t="s">
@@ -5350,7 +5529,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
         <v>677</v>
       </c>
@@ -5360,7 +5539,7 @@
       <c r="C34" t="s">
         <v>555</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>124</v>
       </c>
       <c r="E34" t="s">
@@ -5391,7 +5570,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
         <v>561</v>
       </c>
@@ -5401,7 +5580,7 @@
       <c r="C35" t="s">
         <v>539</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>152</v>
       </c>
       <c r="E35" t="s">
@@ -5441,7 +5620,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
         <v>640</v>
       </c>
@@ -5451,7 +5630,7 @@
       <c r="C36" t="s">
         <v>576</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>156</v>
       </c>
       <c r="E36" t="s">
@@ -5482,7 +5661,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
         <v>587</v>
       </c>
@@ -5501,14 +5680,14 @@
       <c r="N37" t="s">
         <v>34</v>
       </c>
-      <c r="P37" s="1">
+      <c r="P37" s="1" t="n">
         <v>46202</v>
       </c>
       <c r="Q37" t="s">
         <v>590</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
         <v>690</v>
       </c>
@@ -5518,7 +5697,7 @@
       <c r="C38" t="s">
         <v>120</v>
       </c>
-      <c r="D38">
+      <c r="D38" t="n">
         <v>180</v>
       </c>
       <c r="E38" t="s">
@@ -5549,14 +5728,14 @@
         <v>695</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
         <v>91</v>
       </c>
       <c r="B39" t="s">
         <v>92</v>
       </c>
-      <c r="D39">
+      <c r="D39" t="n">
         <v>188</v>
       </c>
       <c r="E39" t="s">
@@ -5575,14 +5754,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
         <v>95</v>
       </c>
       <c r="B40" t="s">
         <v>96</v>
       </c>
-      <c r="D40">
+      <c r="D40" t="n">
         <v>191</v>
       </c>
       <c r="E40" t="s">
@@ -5601,14 +5780,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
         <v>99</v>
       </c>
       <c r="B41" t="s">
         <v>100</v>
       </c>
-      <c r="D41">
+      <c r="D41" t="n">
         <v>192</v>
       </c>
       <c r="E41" t="s">
@@ -5623,24 +5802,24 @@
       <c r="H41" t="s">
         <v>62</v>
       </c>
-      <c r="J41">
+      <c r="J41" t="n">
         <v>2018</v>
       </c>
-      <c r="K41">
+      <c r="K41" t="n">
         <v>2025</v>
       </c>
       <c r="N41" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
         <v>103</v>
       </c>
       <c r="B42" t="s">
         <v>104</v>
       </c>
-      <c r="D42">
+      <c r="D42" t="n">
         <v>196</v>
       </c>
       <c r="E42" t="s">
@@ -5655,10 +5834,10 @@
       <c r="H42" t="s">
         <v>62</v>
       </c>
-      <c r="J42">
+      <c r="J42" t="n">
         <v>2024</v>
       </c>
-      <c r="K42">
+      <c r="K42" t="n">
         <v>2026</v>
       </c>
       <c r="N42" t="s">
@@ -5668,14 +5847,14 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
         <v>108</v>
       </c>
       <c r="B43" t="s">
         <v>109</v>
       </c>
-      <c r="D43">
+      <c r="D43" t="n">
         <v>203</v>
       </c>
       <c r="E43" t="s">
@@ -5697,7 +5876,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
         <v>775</v>
       </c>
@@ -5707,7 +5886,7 @@
       <c r="C44" t="s">
         <v>548</v>
       </c>
-      <c r="D44">
+      <c r="D44" t="n">
         <v>203</v>
       </c>
       <c r="F44" t="s">
@@ -5719,10 +5898,10 @@
       <c r="H44" t="s">
         <v>62</v>
       </c>
-      <c r="J44">
+      <c r="J44" t="n">
         <v>2009</v>
       </c>
-      <c r="K44">
+      <c r="K44" t="n">
         <v>2020</v>
       </c>
       <c r="L44" t="s">
@@ -5734,21 +5913,21 @@
       <c r="N44" t="s">
         <v>34</v>
       </c>
-      <c r="P44" s="1">
+      <c r="P44" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q44" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" t="s">
         <v>113</v>
       </c>
       <c r="B45" t="s">
         <v>114</v>
       </c>
-      <c r="D45">
+      <c r="D45" t="n">
         <v>208</v>
       </c>
       <c r="E45" t="s">
@@ -5763,10 +5942,10 @@
       <c r="H45" t="s">
         <v>62</v>
       </c>
-      <c r="J45">
+      <c r="J45" t="n">
         <v>2011</v>
       </c>
-      <c r="K45">
+      <c r="K45" t="n">
         <v>2026</v>
       </c>
       <c r="N45" t="s">
@@ -5776,7 +5955,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="B46" t="s">
         <v>114</v>
       </c>
@@ -5784,7 +5963,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" t="s">
         <v>118</v>
       </c>
@@ -5816,7 +5995,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" t="s">
         <v>126</v>
       </c>
@@ -5848,7 +6027,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" t="s">
         <v>131</v>
       </c>
@@ -5880,7 +6059,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" t="s">
         <v>135</v>
       </c>
@@ -5912,7 +6091,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" t="s">
         <v>139</v>
       </c>
@@ -5944,7 +6123,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" t="s">
         <v>143</v>
       </c>
@@ -5976,7 +6155,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" t="s">
         <v>147</v>
       </c>
@@ -6008,7 +6187,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" t="s">
         <v>152</v>
       </c>
@@ -6037,7 +6216,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" t="s">
         <v>157</v>
       </c>
@@ -6069,7 +6248,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" t="s">
         <v>161</v>
       </c>
@@ -6101,7 +6280,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" t="s">
         <v>735</v>
       </c>
@@ -6111,7 +6290,7 @@
       <c r="C57" t="s">
         <v>120</v>
       </c>
-      <c r="D57">
+      <c r="D57" t="n">
         <v>818</v>
       </c>
       <c r="F57" t="s">
@@ -6123,10 +6302,10 @@
       <c r="H57" t="s">
         <v>39</v>
       </c>
-      <c r="J57">
+      <c r="J57" t="n">
         <v>2020</v>
       </c>
-      <c r="K57">
+      <c r="K57" t="n">
         <v>2026</v>
       </c>
       <c r="L57" t="s">
@@ -6138,21 +6317,21 @@
       <c r="N57" t="s">
         <v>34</v>
       </c>
-      <c r="P57" s="1">
+      <c r="P57" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q57" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" t="s">
         <v>167</v>
       </c>
       <c r="B58" t="s">
         <v>168</v>
       </c>
-      <c r="D58">
+      <c r="D58" t="n">
         <v>233</v>
       </c>
       <c r="E58" t="s">
@@ -6167,10 +6346,10 @@
       <c r="H58" t="s">
         <v>39</v>
       </c>
-      <c r="J58">
+      <c r="J58" t="n">
         <v>2021</v>
       </c>
-      <c r="K58">
+      <c r="K58" t="n">
         <v>2026</v>
       </c>
       <c r="N58" t="s">
@@ -6180,14 +6359,14 @@
         <v>171</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" t="s">
         <v>172</v>
       </c>
       <c r="B59" t="s">
         <v>173</v>
       </c>
-      <c r="D59">
+      <c r="D59" t="n">
         <v>231</v>
       </c>
       <c r="E59" t="s">
@@ -6209,7 +6388,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" t="s">
         <v>177</v>
       </c>
@@ -6234,10 +6413,10 @@
       <c r="I60" t="s">
         <v>182</v>
       </c>
-      <c r="J60">
+      <c r="J60" t="n">
         <v>2018</v>
       </c>
-      <c r="K60">
+      <c r="K60" t="n">
         <v>2023</v>
       </c>
       <c r="N60" t="s">
@@ -6247,7 +6426,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" t="s">
         <v>739</v>
       </c>
@@ -6257,7 +6436,7 @@
       <c r="C61" t="s">
         <v>120</v>
       </c>
-      <c r="D61">
+      <c r="D61" t="n">
         <v>231</v>
       </c>
       <c r="F61" t="s">
@@ -6269,10 +6448,10 @@
       <c r="H61" t="s">
         <v>62</v>
       </c>
-      <c r="J61">
+      <c r="J61" t="n">
         <v>2015</v>
       </c>
-      <c r="K61">
+      <c r="K61" t="n">
         <v>2021</v>
       </c>
       <c r="L61" t="s">
@@ -6284,21 +6463,21 @@
       <c r="N61" t="s">
         <v>34</v>
       </c>
-      <c r="P61" s="1">
+      <c r="P61" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q61" t="s">
         <v>742</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" t="s">
         <v>185</v>
       </c>
       <c r="B62" t="s">
         <v>186</v>
       </c>
-      <c r="D62">
+      <c r="D62" t="n">
         <v>242</v>
       </c>
       <c r="E62" t="s">
@@ -6320,7 +6499,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" t="s">
         <v>827</v>
       </c>
@@ -6330,7 +6509,7 @@
       <c r="C63" t="s">
         <v>823</v>
       </c>
-      <c r="D63">
+      <c r="D63" t="n">
         <v>242</v>
       </c>
       <c r="F63" t="s">
@@ -6342,10 +6521,10 @@
       <c r="H63" t="s">
         <v>62</v>
       </c>
-      <c r="J63">
+      <c r="J63" t="n">
         <v>2017</v>
       </c>
-      <c r="K63">
+      <c r="K63" t="n">
         <v>2020</v>
       </c>
       <c r="L63" t="s">
@@ -6357,21 +6536,21 @@
       <c r="N63" t="s">
         <v>34</v>
       </c>
-      <c r="P63" s="1">
+      <c r="P63" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q63" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" t="s">
         <v>190</v>
       </c>
       <c r="B64" t="s">
         <v>191</v>
       </c>
-      <c r="D64">
+      <c r="D64" t="n">
         <v>246</v>
       </c>
       <c r="E64" t="s">
@@ -6386,10 +6565,10 @@
       <c r="H64" t="s">
         <v>194</v>
       </c>
-      <c r="J64">
+      <c r="J64" t="n">
         <v>2024</v>
       </c>
-      <c r="K64">
+      <c r="K64" t="n">
         <v>2026</v>
       </c>
       <c r="N64" t="s">
@@ -6399,7 +6578,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" t="s">
         <v>546</v>
       </c>
@@ -6409,7 +6588,7 @@
       <c r="C65" t="s">
         <v>548</v>
       </c>
-      <c r="D65">
+      <c r="D65" t="n">
         <v>250</v>
       </c>
       <c r="E65" t="s">
@@ -6446,14 +6625,14 @@
         <v>553</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" t="s">
         <v>196</v>
       </c>
       <c r="B66" t="s">
         <v>197</v>
       </c>
-      <c r="D66">
+      <c r="D66" t="n">
         <v>270</v>
       </c>
       <c r="E66" t="s">
@@ -6468,10 +6647,10 @@
       <c r="H66" t="s">
         <v>181</v>
       </c>
-      <c r="J66">
+      <c r="J66" t="n">
         <v>2021</v>
       </c>
-      <c r="K66">
+      <c r="K66" t="n">
         <v>2024</v>
       </c>
       <c r="N66" t="s">
@@ -6481,14 +6660,14 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" t="s">
         <v>201</v>
       </c>
       <c r="B67" t="s">
         <v>202</v>
       </c>
-      <c r="D67">
+      <c r="D67" t="n">
         <v>268</v>
       </c>
       <c r="E67" t="s">
@@ -6510,7 +6689,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" t="s">
         <v>754</v>
       </c>
@@ -6520,7 +6699,7 @@
       <c r="C68" t="s">
         <v>576</v>
       </c>
-      <c r="D68">
+      <c r="D68" t="n">
         <v>268</v>
       </c>
       <c r="F68" t="s">
@@ -6532,10 +6711,10 @@
       <c r="H68" t="s">
         <v>62</v>
       </c>
-      <c r="J68">
+      <c r="J68" t="n">
         <v>2019</v>
       </c>
-      <c r="K68">
+      <c r="K68" t="n">
         <v>2023</v>
       </c>
       <c r="L68" t="s">
@@ -6547,21 +6726,21 @@
       <c r="N68" t="s">
         <v>34</v>
       </c>
-      <c r="P68" s="1">
+      <c r="P68" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q68" t="s">
         <v>1212</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" t="s">
         <v>206</v>
       </c>
       <c r="B69" t="s">
         <v>207</v>
       </c>
-      <c r="D69">
+      <c r="D69" t="n">
         <v>276</v>
       </c>
       <c r="E69" t="s">
@@ -6583,7 +6762,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" t="s">
         <v>779</v>
       </c>
@@ -6593,7 +6772,7 @@
       <c r="C70" t="s">
         <v>548</v>
       </c>
-      <c r="D70">
+      <c r="D70" t="n">
         <v>276</v>
       </c>
       <c r="F70" t="s">
@@ -6605,10 +6784,10 @@
       <c r="H70" t="s">
         <v>62</v>
       </c>
-      <c r="J70">
+      <c r="J70" t="n">
         <v>1985</v>
       </c>
-      <c r="K70">
+      <c r="K70" t="n">
         <v>2026</v>
       </c>
       <c r="L70" t="s">
@@ -6620,21 +6799,21 @@
       <c r="N70" t="s">
         <v>34</v>
       </c>
-      <c r="P70" s="1">
+      <c r="P70" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q70" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" t="s">
         <v>211</v>
       </c>
       <c r="B71" t="s">
         <v>212</v>
       </c>
-      <c r="D71">
+      <c r="D71" t="n">
         <v>288</v>
       </c>
       <c r="E71" t="s">
@@ -6656,7 +6835,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" t="s">
         <v>743</v>
       </c>
@@ -6666,7 +6845,7 @@
       <c r="C72" t="s">
         <v>120</v>
       </c>
-      <c r="D72">
+      <c r="D72" t="n">
         <v>288</v>
       </c>
       <c r="F72" t="s">
@@ -6678,10 +6857,10 @@
       <c r="H72" t="s">
         <v>62</v>
       </c>
-      <c r="J72">
+      <c r="J72" t="n">
         <v>2025</v>
       </c>
-      <c r="K72">
+      <c r="K72" t="n">
         <v>2026</v>
       </c>
       <c r="L72" t="s">
@@ -6693,21 +6872,21 @@
       <c r="N72" t="s">
         <v>34</v>
       </c>
-      <c r="P72" s="1">
+      <c r="P72" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q72" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" t="s">
         <v>216</v>
       </c>
       <c r="B73" t="s">
         <v>217</v>
       </c>
-      <c r="D73">
+      <c r="D73" t="n">
         <v>300</v>
       </c>
       <c r="E73" t="s">
@@ -6729,7 +6908,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" t="s">
         <v>783</v>
       </c>
@@ -6739,7 +6918,7 @@
       <c r="C74" t="s">
         <v>548</v>
       </c>
-      <c r="D74">
+      <c r="D74" t="n">
         <v>300</v>
       </c>
       <c r="F74" t="s">
@@ -6751,10 +6930,10 @@
       <c r="H74" t="s">
         <v>62</v>
       </c>
-      <c r="J74">
+      <c r="J74" t="n">
         <v>2003</v>
       </c>
-      <c r="K74">
+      <c r="K74" t="n">
         <v>2008</v>
       </c>
       <c r="L74" t="s">
@@ -6766,21 +6945,21 @@
       <c r="N74" t="s">
         <v>183</v>
       </c>
-      <c r="P74" s="1">
+      <c r="P74" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q74" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" t="s">
         <v>221</v>
       </c>
       <c r="B75" t="s">
         <v>222</v>
       </c>
-      <c r="D75">
+      <c r="D75" t="n">
         <v>328</v>
       </c>
       <c r="E75" t="s">
@@ -6795,10 +6974,10 @@
       <c r="H75" t="s">
         <v>62</v>
       </c>
-      <c r="J75">
+      <c r="J75" t="n">
         <v>2020</v>
       </c>
-      <c r="K75">
+      <c r="K75" t="n">
         <v>2026</v>
       </c>
       <c r="N75" t="s">
@@ -6808,14 +6987,14 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" t="s">
         <v>226</v>
       </c>
       <c r="B76" t="s">
         <v>227</v>
       </c>
-      <c r="D76">
+      <c r="D76" t="n">
         <v>348</v>
       </c>
       <c r="E76" t="s">
@@ -6830,10 +7009,10 @@
       <c r="H76" t="s">
         <v>62</v>
       </c>
-      <c r="J76">
+      <c r="J76" t="n">
         <v>2022</v>
       </c>
-      <c r="K76">
+      <c r="K76" t="n">
         <v>2026</v>
       </c>
       <c r="L76" t="s">
@@ -6852,7 +7031,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" t="s">
         <v>835</v>
       </c>
@@ -6862,7 +7041,7 @@
       <c r="C77" t="s">
         <v>548</v>
       </c>
-      <c r="D77">
+      <c r="D77" t="n">
         <v>348</v>
       </c>
       <c r="E77" t="s">
@@ -6880,10 +7059,10 @@
       <c r="I77" t="s">
         <v>838</v>
       </c>
-      <c r="J77">
+      <c r="J77" t="n">
         <v>2012</v>
       </c>
-      <c r="K77">
+      <c r="K77" t="n">
         <v>2022</v>
       </c>
       <c r="L77" t="s">
@@ -6902,14 +7081,14 @@
         <v>839</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" t="s">
         <v>233</v>
       </c>
       <c r="B78" t="s">
         <v>234</v>
       </c>
-      <c r="D78">
+      <c r="D78" t="n">
         <v>352</v>
       </c>
       <c r="E78" t="s">
@@ -6924,10 +7103,10 @@
       <c r="H78" t="s">
         <v>62</v>
       </c>
-      <c r="J78">
+      <c r="J78" t="n">
         <v>2025</v>
       </c>
-      <c r="K78">
+      <c r="K78" t="n">
         <v>2026</v>
       </c>
       <c r="N78" t="s">
@@ -6937,14 +7116,14 @@
         <v>237</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" t="s">
         <v>238</v>
       </c>
       <c r="B79" t="s">
         <v>239</v>
       </c>
-      <c r="D79">
+      <c r="D79" t="n">
         <v>356</v>
       </c>
       <c r="E79" t="s">
@@ -6963,7 +7142,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" t="s">
         <v>596</v>
       </c>
@@ -6989,7 +7168,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" t="s">
         <v>756</v>
       </c>
@@ -6999,7 +7178,7 @@
       <c r="C81" t="s">
         <v>576</v>
       </c>
-      <c r="D81">
+      <c r="D81" t="n">
         <v>356</v>
       </c>
       <c r="E81" t="s">
@@ -7014,10 +7193,10 @@
       <c r="H81" t="s">
         <v>62</v>
       </c>
-      <c r="J81">
+      <c r="J81" t="n">
         <v>2014</v>
       </c>
-      <c r="K81">
+      <c r="K81" t="n">
         <v>2026</v>
       </c>
       <c r="L81" t="s">
@@ -7029,14 +7208,14 @@
       <c r="N81" t="s">
         <v>34</v>
       </c>
-      <c r="P81" s="1">
+      <c r="P81" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="Q81" t="s">
         <v>758</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" t="s">
         <v>591</v>
       </c>
@@ -7062,14 +7241,14 @@
         <v>595</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" t="s">
         <v>242</v>
       </c>
       <c r="B83" t="s">
         <v>243</v>
       </c>
-      <c r="D83">
+      <c r="D83" t="n">
         <v>364</v>
       </c>
       <c r="E83" t="s">
@@ -7084,10 +7263,10 @@
       <c r="H83" t="s">
         <v>62</v>
       </c>
-      <c r="J83">
+      <c r="J83" t="n">
         <v>2026</v>
       </c>
-      <c r="K83">
+      <c r="K83" t="n">
         <v>2026</v>
       </c>
       <c r="N83" t="s">
@@ -7097,14 +7276,14 @@
         <v>246</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" t="s">
         <v>247</v>
       </c>
       <c r="B84" t="s">
         <v>248</v>
       </c>
-      <c r="D84">
+      <c r="D84" t="n">
         <v>372</v>
       </c>
       <c r="E84" t="s">
@@ -7123,14 +7302,14 @@
         <v>251</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" t="s">
         <v>252</v>
       </c>
       <c r="B85" t="s">
         <v>253</v>
       </c>
-      <c r="D85">
+      <c r="D85" t="n">
         <v>376</v>
       </c>
       <c r="E85" t="s">
@@ -7152,14 +7331,14 @@
         <v>257</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" t="s">
         <v>696</v>
       </c>
       <c r="B86" t="s">
         <v>253</v>
       </c>
-      <c r="D86">
+      <c r="D86" t="n">
         <v>376</v>
       </c>
       <c r="E86" t="s">
@@ -7177,10 +7356,10 @@
       <c r="I86" t="s">
         <v>700</v>
       </c>
-      <c r="J86">
+      <c r="J86" t="n">
         <v>2004</v>
       </c>
-      <c r="K86">
+      <c r="K86" t="n">
         <v>2026</v>
       </c>
       <c r="L86" t="s">
@@ -7199,14 +7378,14 @@
         <v>702</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" t="s">
         <v>258</v>
       </c>
       <c r="B87" t="s">
         <v>259</v>
       </c>
-      <c r="D87">
+      <c r="D87" t="n">
         <v>380</v>
       </c>
       <c r="E87" t="s">
@@ -7228,14 +7407,14 @@
         <v>262</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" t="s">
         <v>263</v>
       </c>
       <c r="B88" t="s">
         <v>264</v>
       </c>
-      <c r="D88">
+      <c r="D88" t="n">
         <v>392</v>
       </c>
       <c r="E88" t="s">
@@ -7257,7 +7436,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" t="s">
         <v>759</v>
       </c>
@@ -7267,7 +7446,7 @@
       <c r="C89" t="s">
         <v>576</v>
       </c>
-      <c r="D89">
+      <c r="D89" t="n">
         <v>392</v>
       </c>
       <c r="F89" t="s">
@@ -7279,10 +7458,10 @@
       <c r="H89" t="s">
         <v>62</v>
       </c>
-      <c r="J89">
+      <c r="J89" t="n">
         <v>2026</v>
       </c>
-      <c r="K89">
+      <c r="K89" t="n">
         <v>2026</v>
       </c>
       <c r="L89" t="s">
@@ -7294,21 +7473,21 @@
       <c r="N89" t="s">
         <v>34</v>
       </c>
-      <c r="P89" s="1">
+      <c r="P89" s="1" t="n">
         <v>46221</v>
       </c>
       <c r="Q89" t="s">
         <v>762</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" t="s">
         <v>268</v>
       </c>
       <c r="B90" t="s">
         <v>269</v>
       </c>
-      <c r="D90">
+      <c r="D90" t="n">
         <v>400</v>
       </c>
       <c r="E90" t="s">
@@ -7323,10 +7502,10 @@
       <c r="H90" t="s">
         <v>62</v>
       </c>
-      <c r="J90">
+      <c r="J90" t="n">
         <v>1999</v>
       </c>
-      <c r="K90">
+      <c r="K90" t="n">
         <v>2026</v>
       </c>
       <c r="L90" t="s">
@@ -7345,14 +7524,14 @@
         <v>273</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" t="s">
         <v>274</v>
       </c>
       <c r="B91" t="s">
         <v>275</v>
       </c>
-      <c r="D91">
+      <c r="D91" t="n">
         <v>398</v>
       </c>
       <c r="E91" t="s">
@@ -7367,10 +7546,10 @@
       <c r="H91" t="s">
         <v>62</v>
       </c>
-      <c r="J91">
+      <c r="J91" t="n">
         <v>2021</v>
       </c>
-      <c r="K91">
+      <c r="K91" t="n">
         <v>2026</v>
       </c>
       <c r="L91" t="s">
@@ -7389,7 +7568,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" t="s">
         <v>840</v>
       </c>
@@ -7399,7 +7578,7 @@
       <c r="C92" t="s">
         <v>576</v>
       </c>
-      <c r="D92">
+      <c r="D92" t="n">
         <v>398</v>
       </c>
       <c r="E92" t="s">
@@ -7417,10 +7596,10 @@
       <c r="I92" t="s">
         <v>843</v>
       </c>
-      <c r="J92">
+      <c r="J92" t="n">
         <v>2005</v>
       </c>
-      <c r="K92">
+      <c r="K92" t="n">
         <v>2020</v>
       </c>
       <c r="L92" t="s">
@@ -7439,7 +7618,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" t="s">
         <v>280</v>
       </c>
@@ -7449,7 +7628,7 @@
       <c r="C93" t="s">
         <v>120</v>
       </c>
-      <c r="D93">
+      <c r="D93" t="n">
         <v>404</v>
       </c>
       <c r="E93" t="s">
@@ -7467,10 +7646,10 @@
       <c r="I93" t="s">
         <v>1216</v>
       </c>
-      <c r="J93">
+      <c r="J93" t="n">
         <v>2022</v>
       </c>
-      <c r="K93">
+      <c r="K93" t="n">
         <v>2026</v>
       </c>
       <c r="L93" t="s">
@@ -7482,14 +7661,14 @@
       <c r="N93" t="s">
         <v>34</v>
       </c>
-      <c r="P93" s="2">
+      <c r="P93" s="1" t="n">
         <v>46229</v>
       </c>
       <c r="Q93" t="s">
         <v>1217</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" t="s">
         <v>604</v>
       </c>
@@ -7499,7 +7678,7 @@
       <c r="C94" t="s">
         <v>576</v>
       </c>
-      <c r="D94">
+      <c r="D94" t="n">
         <v>410</v>
       </c>
       <c r="E94" t="s">
@@ -7517,10 +7696,10 @@
       <c r="I94" t="s">
         <v>608</v>
       </c>
-      <c r="J94">
+      <c r="J94" t="n">
         <v>2025</v>
       </c>
-      <c r="K94">
+      <c r="K94" t="n">
         <v>2026</v>
       </c>
       <c r="L94" t="s">
@@ -7536,7 +7715,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" t="s">
         <v>763</v>
       </c>
@@ -7546,7 +7725,7 @@
       <c r="C95" t="s">
         <v>576</v>
       </c>
-      <c r="D95">
+      <c r="D95" t="n">
         <v>410</v>
       </c>
       <c r="E95" t="s">
@@ -7576,21 +7755,21 @@
       <c r="N95" t="s">
         <v>34</v>
       </c>
-      <c r="P95" s="1">
+      <c r="P95" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q95" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" t="s">
         <v>282</v>
       </c>
       <c r="B96" t="s">
         <v>283</v>
       </c>
-      <c r="D96">
+      <c r="D96" t="n">
         <v>414</v>
       </c>
       <c r="E96" t="s">
@@ -7615,7 +7794,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" t="s">
         <v>830</v>
       </c>
@@ -7625,7 +7804,7 @@
       <c r="C97" t="s">
         <v>649</v>
       </c>
-      <c r="D97">
+      <c r="D97" t="n">
         <v>414</v>
       </c>
       <c r="E97" t="s">
@@ -7643,10 +7822,10 @@
       <c r="I97" t="s">
         <v>833</v>
       </c>
-      <c r="J97">
+      <c r="J97" t="n">
         <v>2023</v>
       </c>
-      <c r="K97">
+      <c r="K97" t="n">
         <v>2026</v>
       </c>
       <c r="L97" t="s">
@@ -7665,14 +7844,14 @@
         <v>834</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" t="s">
         <v>287</v>
       </c>
       <c r="B98" t="s">
         <v>288</v>
       </c>
-      <c r="D98">
+      <c r="D98" t="n">
         <v>417</v>
       </c>
       <c r="E98" t="s">
@@ -7687,10 +7866,10 @@
       <c r="H98" t="s">
         <v>194</v>
       </c>
-      <c r="J98">
+      <c r="J98" t="n">
         <v>2021</v>
       </c>
-      <c r="K98">
+      <c r="K98" t="n">
         <v>2025</v>
       </c>
       <c r="N98" t="s">
@@ -7703,14 +7882,14 @@
         <v>292</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" t="s">
         <v>720</v>
       </c>
       <c r="B99" t="s">
         <v>288</v>
       </c>
-      <c r="D99">
+      <c r="D99" t="n">
         <v>417</v>
       </c>
       <c r="E99" t="s">
@@ -7728,10 +7907,10 @@
       <c r="I99" t="s">
         <v>723</v>
       </c>
-      <c r="J99">
+      <c r="J99" t="n">
         <v>2014</v>
       </c>
-      <c r="K99">
+      <c r="K99" t="n">
         <v>2021</v>
       </c>
       <c r="L99" t="s">
@@ -7750,14 +7929,14 @@
         <v>724</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" t="s">
         <v>293</v>
       </c>
       <c r="B100" t="s">
         <v>294</v>
       </c>
-      <c r="D100">
+      <c r="D100" t="n">
         <v>428</v>
       </c>
       <c r="E100" t="s">
@@ -7772,10 +7951,10 @@
       <c r="H100" t="s">
         <v>62</v>
       </c>
-      <c r="J100">
+      <c r="J100" t="n">
         <v>2015</v>
       </c>
-      <c r="K100">
+      <c r="K100" t="n">
         <v>2026</v>
       </c>
       <c r="L100" t="s">
@@ -7794,14 +7973,14 @@
         <v>297</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" t="s">
         <v>298</v>
       </c>
       <c r="B101" t="s">
         <v>299</v>
       </c>
-      <c r="D101">
+      <c r="D101" t="n">
         <v>422</v>
       </c>
       <c r="E101" t="s">
@@ -7823,14 +8002,14 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102">
       <c r="A102" t="s">
         <v>730</v>
       </c>
       <c r="B102" t="s">
         <v>299</v>
       </c>
-      <c r="D102">
+      <c r="D102" t="n">
         <v>422</v>
       </c>
       <c r="E102" t="s">
@@ -7848,10 +8027,10 @@
       <c r="I102" t="s">
         <v>733</v>
       </c>
-      <c r="J102">
+      <c r="J102" t="n">
         <v>2025</v>
       </c>
-      <c r="K102">
+      <c r="K102" t="n">
         <v>2026</v>
       </c>
       <c r="L102" t="s">
@@ -7870,14 +8049,14 @@
         <v>734</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103">
       <c r="A103" t="s">
         <v>303</v>
       </c>
       <c r="B103" t="s">
         <v>304</v>
       </c>
-      <c r="D103">
+      <c r="D103" t="n">
         <v>426</v>
       </c>
       <c r="E103" t="s">
@@ -7905,14 +8084,14 @@
         <v>307</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104">
       <c r="A104" t="s">
         <v>308</v>
       </c>
       <c r="B104" t="s">
         <v>309</v>
       </c>
-      <c r="D104">
+      <c r="D104" t="n">
         <v>440</v>
       </c>
       <c r="E104" t="s">
@@ -7940,7 +8119,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105">
       <c r="A105" t="s">
         <v>845</v>
       </c>
@@ -7950,7 +8129,7 @@
       <c r="C105" t="s">
         <v>548</v>
       </c>
-      <c r="D105">
+      <c r="D105" t="n">
         <v>440</v>
       </c>
       <c r="E105" t="s">
@@ -7968,10 +8147,10 @@
       <c r="I105" t="s">
         <v>848</v>
       </c>
-      <c r="J105">
+      <c r="J105" t="n">
         <v>2012</v>
       </c>
-      <c r="K105">
+      <c r="K105" t="n">
         <v>2024</v>
       </c>
       <c r="L105" t="s">
@@ -7990,14 +8169,14 @@
         <v>849</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106">
       <c r="A106" t="s">
         <v>313</v>
       </c>
       <c r="B106" t="s">
         <v>314</v>
       </c>
-      <c r="D106">
+      <c r="D106" t="n">
         <v>442</v>
       </c>
       <c r="E106" t="s">
@@ -8012,10 +8191,10 @@
       <c r="H106" t="s">
         <v>62</v>
       </c>
-      <c r="J106">
+      <c r="J106" t="n">
         <v>2003</v>
       </c>
-      <c r="K106">
+      <c r="K106" t="n">
         <v>2026</v>
       </c>
       <c r="L106" t="s">
@@ -8034,14 +8213,14 @@
         <v>318</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107">
       <c r="A107" t="s">
         <v>319</v>
       </c>
       <c r="B107" t="s">
         <v>320</v>
       </c>
-      <c r="D107">
+      <c r="D107" t="n">
         <v>450</v>
       </c>
       <c r="E107" t="s">
@@ -8069,7 +8248,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108">
       <c r="A108" t="s">
         <v>850</v>
       </c>
@@ -8079,7 +8258,7 @@
       <c r="C108" t="s">
         <v>120</v>
       </c>
-      <c r="D108">
+      <c r="D108" t="n">
         <v>450</v>
       </c>
       <c r="E108" t="s">
@@ -8097,10 +8276,10 @@
       <c r="I108" t="s">
         <v>853</v>
       </c>
-      <c r="J108">
+      <c r="J108" t="n">
         <v>2014</v>
       </c>
-      <c r="K108">
+      <c r="K108" t="n">
         <v>2026</v>
       </c>
       <c r="L108" t="s">
@@ -8119,7 +8298,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109">
       <c r="A109" t="s">
         <v>655</v>
       </c>
@@ -8129,7 +8308,7 @@
       <c r="C109" t="s">
         <v>576</v>
       </c>
-      <c r="D109">
+      <c r="D109" t="n">
         <v>458</v>
       </c>
       <c r="E109" t="s">
@@ -8147,10 +8326,10 @@
       <c r="I109" t="s">
         <v>659</v>
       </c>
-      <c r="J109">
+      <c r="J109" t="n">
         <v>2024</v>
       </c>
-      <c r="K109">
+      <c r="K109" t="n">
         <v>2026</v>
       </c>
       <c r="L109" t="s">
@@ -8169,14 +8348,14 @@
         <v>661</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110">
       <c r="A110" t="s">
         <v>324</v>
       </c>
       <c r="B110" t="s">
         <v>325</v>
       </c>
-      <c r="D110">
+      <c r="D110" t="n">
         <v>462</v>
       </c>
       <c r="E110" t="s">
@@ -8213,14 +8392,14 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111">
       <c r="A111" t="s">
         <v>333</v>
       </c>
       <c r="B111" t="s">
         <v>334</v>
       </c>
-      <c r="D111">
+      <c r="D111" t="n">
         <v>470</v>
       </c>
       <c r="E111" t="s">
@@ -8251,7 +8430,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112">
       <c r="A112" t="s">
         <v>891</v>
       </c>
@@ -8261,7 +8440,7 @@
       <c r="C112" t="s">
         <v>548</v>
       </c>
-      <c r="D112">
+      <c r="D112" t="n">
         <v>470</v>
       </c>
       <c r="E112" t="s">
@@ -8301,7 +8480,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113">
       <c r="A113" t="s">
         <v>896</v>
       </c>
@@ -8311,7 +8490,7 @@
       <c r="C113" t="s">
         <v>548</v>
       </c>
-      <c r="D113">
+      <c r="D113" t="n">
         <v>470</v>
       </c>
       <c r="E113" t="s">
@@ -8345,14 +8524,14 @@
         <v>900</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114">
       <c r="A114" t="s">
         <v>339</v>
       </c>
       <c r="B114" t="s">
         <v>340</v>
       </c>
-      <c r="D114">
+      <c r="D114" t="n">
         <v>484</v>
       </c>
       <c r="E114" t="s">
@@ -8377,7 +8556,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115">
       <c r="A115" t="s">
         <v>554</v>
       </c>
@@ -8387,7 +8566,7 @@
       <c r="C115" t="s">
         <v>555</v>
       </c>
-      <c r="D115">
+      <c r="D115" t="n">
         <v>484</v>
       </c>
       <c r="E115" t="s">
@@ -8427,7 +8606,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116">
       <c r="A116" t="s">
         <v>861</v>
       </c>
@@ -8437,7 +8616,7 @@
       <c r="C116" t="s">
         <v>555</v>
       </c>
-      <c r="D116">
+      <c r="D116" t="n">
         <v>484</v>
       </c>
       <c r="E116" t="s">
@@ -8477,14 +8656,14 @@
         <v>867</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117">
       <c r="A117" t="s">
         <v>344</v>
       </c>
       <c r="B117" t="s">
         <v>345</v>
       </c>
-      <c r="D117">
+      <c r="D117" t="n">
         <v>498</v>
       </c>
       <c r="E117" t="s">
@@ -8518,7 +8697,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118">
       <c r="A118" t="s">
         <v>703</v>
       </c>
@@ -8528,7 +8707,7 @@
       <c r="C118" t="s">
         <v>576</v>
       </c>
-      <c r="D118">
+      <c r="D118" t="n">
         <v>496</v>
       </c>
       <c r="E118" t="s">
@@ -8562,7 +8741,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119">
       <c r="A119" t="s">
         <v>710</v>
       </c>
@@ -8572,7 +8751,7 @@
       <c r="C119" t="s">
         <v>576</v>
       </c>
-      <c r="D119">
+      <c r="D119" t="n">
         <v>496</v>
       </c>
       <c r="E119" t="s">
@@ -8590,10 +8769,10 @@
       <c r="I119" t="s">
         <v>713</v>
       </c>
-      <c r="J119">
+      <c r="J119" t="n">
         <v>2019</v>
       </c>
-      <c r="K119">
+      <c r="K119" t="n">
         <v>2025</v>
       </c>
       <c r="L119" t="s">
@@ -8612,14 +8791,14 @@
         <v>714</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120">
       <c r="A120" t="s">
         <v>351</v>
       </c>
       <c r="B120" t="s">
         <v>352</v>
       </c>
-      <c r="D120">
+      <c r="D120" t="n">
         <v>504</v>
       </c>
       <c r="E120" t="s">
@@ -8647,7 +8826,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121">
       <c r="A121" t="s">
         <v>855</v>
       </c>
@@ -8657,7 +8836,7 @@
       <c r="C121" t="s">
         <v>120</v>
       </c>
-      <c r="D121">
+      <c r="D121" t="n">
         <v>504</v>
       </c>
       <c r="E121" t="s">
@@ -8697,7 +8876,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122">
       <c r="A122" t="s">
         <v>669</v>
       </c>
@@ -8707,7 +8886,7 @@
       <c r="C122" t="s">
         <v>576</v>
       </c>
-      <c r="D122">
+      <c r="D122" t="n">
         <v>104</v>
       </c>
       <c r="E122" t="s">
@@ -8725,10 +8904,10 @@
       <c r="I122" t="s">
         <v>674</v>
       </c>
-      <c r="J122">
+      <c r="J122" t="n">
         <v>2025</v>
       </c>
-      <c r="K122">
+      <c r="K122" t="n">
         <v>2025</v>
       </c>
       <c r="L122" t="s">
@@ -8744,14 +8923,14 @@
         <v>676</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123">
       <c r="A123" t="s">
         <v>357</v>
       </c>
       <c r="B123" t="s">
         <v>358</v>
       </c>
-      <c r="D123">
+      <c r="D123" t="n">
         <v>528</v>
       </c>
       <c r="E123" t="s">
@@ -8782,7 +8961,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124">
       <c r="A124" t="s">
         <v>879</v>
       </c>
@@ -8792,7 +8971,7 @@
       <c r="C124" t="s">
         <v>548</v>
       </c>
-      <c r="D124">
+      <c r="D124" t="n">
         <v>528</v>
       </c>
       <c r="E124" t="s">
@@ -8826,14 +9005,14 @@
         <v>884</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125">
       <c r="A125" t="s">
         <v>363</v>
       </c>
       <c r="B125" t="s">
         <v>364</v>
       </c>
-      <c r="D125">
+      <c r="D125" t="n">
         <v>554</v>
       </c>
       <c r="E125" t="s">
@@ -8861,7 +9040,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126">
       <c r="A126" t="s">
         <v>868</v>
       </c>
@@ -8871,7 +9050,7 @@
       <c r="C126" t="s">
         <v>823</v>
       </c>
-      <c r="D126">
+      <c r="D126" t="n">
         <v>554</v>
       </c>
       <c r="E126" t="s">
@@ -8911,7 +9090,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127">
       <c r="A127" t="s">
         <v>368</v>
       </c>
@@ -8946,7 +9125,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128">
       <c r="A128" t="s">
         <v>375</v>
       </c>
@@ -8987,7 +9166,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129">
       <c r="A129" t="s">
         <v>885</v>
       </c>
@@ -8997,7 +9176,7 @@
       <c r="C129" t="s">
         <v>120</v>
       </c>
-      <c r="D129">
+      <c r="D129" t="n">
         <v>566</v>
       </c>
       <c r="E129" t="s">
@@ -9037,14 +9216,14 @@
         <v>890</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130">
       <c r="A130" t="s">
         <v>382</v>
       </c>
       <c r="B130" t="s">
         <v>383</v>
       </c>
-      <c r="D130">
+      <c r="D130" t="n">
         <v>807</v>
       </c>
       <c r="E130" t="s">
@@ -9078,14 +9257,14 @@
         <v>388</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131">
       <c r="A131" t="s">
         <v>389</v>
       </c>
       <c r="B131" t="s">
         <v>390</v>
       </c>
-      <c r="D131">
+      <c r="D131" t="n">
         <v>578</v>
       </c>
       <c r="E131" t="s">
@@ -9119,7 +9298,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132">
       <c r="A132" t="s">
         <v>874</v>
       </c>
@@ -9129,7 +9308,7 @@
       <c r="C132" t="s">
         <v>548</v>
       </c>
-      <c r="D132">
+      <c r="D132" t="n">
         <v>578</v>
       </c>
       <c r="E132" t="s">
@@ -9163,7 +9342,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133">
       <c r="A133" t="s">
         <v>611</v>
       </c>
@@ -9173,7 +9352,7 @@
       <c r="C133" t="s">
         <v>576</v>
       </c>
-      <c r="D133">
+      <c r="D133" t="n">
         <v>586</v>
       </c>
       <c r="E133" t="s">
@@ -9204,7 +9383,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134">
       <c r="A134" t="s">
         <v>725</v>
       </c>
@@ -9214,7 +9393,7 @@
       <c r="C134" t="s">
         <v>576</v>
       </c>
-      <c r="D134">
+      <c r="D134" t="n">
         <v>586</v>
       </c>
       <c r="E134" t="s">
@@ -9232,10 +9411,10 @@
       <c r="I134" t="s">
         <v>728</v>
       </c>
-      <c r="J134">
+      <c r="J134" t="n">
         <v>2013</v>
       </c>
-      <c r="K134">
+      <c r="K134" t="n">
         <v>2026</v>
       </c>
       <c r="L134" t="s">
@@ -9254,7 +9433,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135">
       <c r="A135" t="s">
         <v>396</v>
       </c>
@@ -9271,14 +9450,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136">
       <c r="A136" t="s">
         <v>400</v>
       </c>
       <c r="B136" t="s">
         <v>401</v>
       </c>
-      <c r="D136">
+      <c r="D136" t="n">
         <v>616</v>
       </c>
       <c r="E136" t="s">
@@ -9293,10 +9472,10 @@
       <c r="H136" t="s">
         <v>32</v>
       </c>
-      <c r="J136">
+      <c r="J136" t="n">
         <v>2010</v>
       </c>
-      <c r="K136">
+      <c r="K136" t="n">
         <v>2026</v>
       </c>
       <c r="L136" t="s">
@@ -9315,7 +9494,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137">
       <c r="A137" t="s">
         <v>901</v>
       </c>
@@ -9340,10 +9519,10 @@
       <c r="H137" t="s">
         <v>62</v>
       </c>
-      <c r="J137">
+      <c r="J137" t="n">
         <v>2018</v>
       </c>
-      <c r="K137">
+      <c r="K137" t="n">
         <v>2026</v>
       </c>
       <c r="L137" t="s">
@@ -9362,14 +9541,14 @@
         <v>906</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138">
       <c r="A138" t="s">
         <v>407</v>
       </c>
       <c r="B138" t="s">
         <v>408</v>
       </c>
-      <c r="D138">
+      <c r="D138" t="n">
         <v>642</v>
       </c>
       <c r="E138" t="s">
@@ -9397,7 +9576,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139">
       <c r="A139" t="s">
         <v>907</v>
       </c>
@@ -9422,10 +9601,10 @@
       <c r="H139" t="s">
         <v>62</v>
       </c>
-      <c r="J139">
+      <c r="J139" t="n">
         <v>2023</v>
       </c>
-      <c r="K139">
+      <c r="K139" t="n">
         <v>2026</v>
       </c>
       <c r="L139" t="s">
@@ -9444,7 +9623,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140">
       <c r="A140" t="s">
         <v>912</v>
       </c>
@@ -9469,10 +9648,10 @@
       <c r="H140" t="s">
         <v>62</v>
       </c>
-      <c r="J140">
+      <c r="J140" t="n">
         <v>2016</v>
       </c>
-      <c r="K140">
+      <c r="K140" t="n">
         <v>2023</v>
       </c>
       <c r="L140" t="s">
@@ -9491,7 +9670,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141">
       <c r="A141" t="s">
         <v>625</v>
       </c>
@@ -9501,7 +9680,7 @@
       <c r="C141" t="s">
         <v>548</v>
       </c>
-      <c r="D141">
+      <c r="D141" t="n">
         <v>643</v>
       </c>
       <c r="E141" t="s">
@@ -9532,7 +9711,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142">
       <c r="A142" t="s">
         <v>647</v>
       </c>
@@ -9542,7 +9721,7 @@
       <c r="C142" t="s">
         <v>649</v>
       </c>
-      <c r="D142">
+      <c r="D142" t="n">
         <v>682</v>
       </c>
       <c r="E142" t="s">
@@ -9573,14 +9752,14 @@
         <v>654</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143">
       <c r="A143" t="s">
         <v>412</v>
       </c>
       <c r="B143" t="s">
         <v>413</v>
       </c>
-      <c r="D143">
+      <c r="D143" t="n">
         <v>688</v>
       </c>
       <c r="E143" t="s">
@@ -9595,24 +9774,24 @@
       <c r="H143" t="s">
         <v>62</v>
       </c>
-      <c r="J143">
+      <c r="J143" t="n">
         <v>2014</v>
       </c>
-      <c r="K143">
+      <c r="K143" t="n">
         <v>2026</v>
       </c>
       <c r="N143" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144">
       <c r="A144" t="s">
         <v>416</v>
       </c>
       <c r="B144" t="s">
         <v>417</v>
       </c>
-      <c r="D144">
+      <c r="D144" t="n">
         <v>690</v>
       </c>
       <c r="E144" t="s">
@@ -9627,10 +9806,10 @@
       <c r="H144" t="s">
         <v>62</v>
       </c>
-      <c r="J144">
+      <c r="J144" t="n">
         <v>2010</v>
       </c>
-      <c r="K144">
+      <c r="K144" t="n">
         <v>2026</v>
       </c>
       <c r="L144" t="s">
@@ -9649,14 +9828,14 @@
         <v>421</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145">
       <c r="A145" t="s">
         <v>422</v>
       </c>
       <c r="B145" t="s">
         <v>423</v>
       </c>
-      <c r="D145">
+      <c r="D145" t="n">
         <v>694</v>
       </c>
       <c r="E145" t="s">
@@ -9671,10 +9850,10 @@
       <c r="H145" t="s">
         <v>62</v>
       </c>
-      <c r="J145">
+      <c r="J145" t="n">
         <v>2025</v>
       </c>
-      <c r="K145">
+      <c r="K145" t="n">
         <v>2026</v>
       </c>
       <c r="L145" t="s">
@@ -9693,14 +9872,14 @@
         <v>426</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146">
       <c r="A146" t="s">
         <v>427</v>
       </c>
       <c r="B146" t="s">
         <v>428</v>
       </c>
-      <c r="D146">
+      <c r="D146" t="n">
         <v>702</v>
       </c>
       <c r="E146" t="s">
@@ -9715,10 +9894,10 @@
       <c r="H146" t="s">
         <v>62</v>
       </c>
-      <c r="J146">
+      <c r="J146" t="n">
         <v>2014</v>
       </c>
-      <c r="K146">
+      <c r="K146" t="n">
         <v>2026</v>
       </c>
       <c r="L146" t="s">
@@ -9737,7 +9916,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147">
       <c r="A147" t="s">
         <v>916</v>
       </c>
@@ -9762,10 +9941,10 @@
       <c r="H147" t="s">
         <v>62</v>
       </c>
-      <c r="J147">
+      <c r="J147" t="n">
         <v>2012</v>
       </c>
-      <c r="K147">
+      <c r="K147" t="n">
         <v>2026</v>
       </c>
       <c r="L147" t="s">
@@ -9784,14 +9963,14 @@
         <v>920</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148">
       <c r="A148" t="s">
         <v>432</v>
       </c>
       <c r="B148" t="s">
         <v>433</v>
       </c>
-      <c r="D148">
+      <c r="D148" t="n">
         <v>703</v>
       </c>
       <c r="E148" t="s">
@@ -9816,7 +9995,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149">
       <c r="A149" t="s">
         <v>921</v>
       </c>
@@ -9841,10 +10020,10 @@
       <c r="H149" t="s">
         <v>62</v>
       </c>
-      <c r="J149">
+      <c r="J149" t="n">
         <v>2023</v>
       </c>
-      <c r="K149">
+      <c r="K149" t="n">
         <v>2026</v>
       </c>
       <c r="L149" t="s">
@@ -9863,7 +10042,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150">
       <c r="A150" t="s">
         <v>927</v>
       </c>
@@ -9888,10 +10067,10 @@
       <c r="H150" t="s">
         <v>62</v>
       </c>
-      <c r="J150">
+      <c r="J150" t="n">
         <v>2015</v>
       </c>
-      <c r="K150">
+      <c r="K150" t="n">
         <v>2026</v>
       </c>
       <c r="L150" t="s">
@@ -9910,14 +10089,14 @@
         <v>930</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151">
       <c r="A151" t="s">
         <v>437</v>
       </c>
       <c r="B151" t="s">
         <v>438</v>
       </c>
-      <c r="D151">
+      <c r="D151" t="n">
         <v>705</v>
       </c>
       <c r="E151" t="s">
@@ -9942,7 +10121,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152">
       <c r="A152" t="s">
         <v>931</v>
       </c>
@@ -9967,10 +10146,10 @@
       <c r="H152" t="s">
         <v>62</v>
       </c>
-      <c r="J152">
+      <c r="J152" t="n">
         <v>2022</v>
       </c>
-      <c r="K152">
+      <c r="K152" t="n">
         <v>2026</v>
       </c>
       <c r="L152" t="s">
@@ -9989,7 +10168,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153">
       <c r="A153" t="s">
         <v>937</v>
       </c>
@@ -10014,10 +10193,10 @@
       <c r="H153" t="s">
         <v>62</v>
       </c>
-      <c r="J153">
+      <c r="J153" t="n">
         <v>2001</v>
       </c>
-      <c r="K153">
+      <c r="K153" t="n">
         <v>2026</v>
       </c>
       <c r="L153" t="s">
@@ -10036,7 +10215,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154">
       <c r="A154" t="s">
         <v>941</v>
       </c>
@@ -10061,10 +10240,10 @@
       <c r="H154" t="s">
         <v>62</v>
       </c>
-      <c r="J154">
+      <c r="J154" t="n">
         <v>2001</v>
       </c>
-      <c r="K154">
+      <c r="K154" t="n">
         <v>2022</v>
       </c>
       <c r="L154" t="s">
@@ -10083,14 +10262,14 @@
         <v>944</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155">
       <c r="A155" t="s">
         <v>443</v>
       </c>
       <c r="B155" t="s">
         <v>444</v>
       </c>
-      <c r="D155">
+      <c r="D155" t="n">
         <v>706</v>
       </c>
       <c r="E155" t="s">
@@ -10105,10 +10284,10 @@
       <c r="H155" t="s">
         <v>62</v>
       </c>
-      <c r="J155">
+      <c r="J155" t="n">
         <v>2018</v>
       </c>
-      <c r="K155">
+      <c r="K155" t="n">
         <v>2026</v>
       </c>
       <c r="L155" t="s">
@@ -10127,14 +10306,14 @@
         <v>448</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156">
       <c r="A156" t="s">
         <v>449</v>
       </c>
       <c r="B156" t="s">
         <v>450</v>
       </c>
-      <c r="D156">
+      <c r="D156" t="n">
         <v>710</v>
       </c>
       <c r="E156" t="s">
@@ -10149,10 +10328,10 @@
       <c r="H156" t="s">
         <v>62</v>
       </c>
-      <c r="J156">
+      <c r="J156" t="n">
         <v>2024</v>
       </c>
-      <c r="K156">
+      <c r="K156" t="n">
         <v>2026</v>
       </c>
       <c r="L156" t="s">
@@ -10168,7 +10347,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157">
       <c r="A157" t="s">
         <v>945</v>
       </c>
@@ -10193,7 +10372,7 @@
       <c r="H157" t="s">
         <v>62</v>
       </c>
-      <c r="K157">
+      <c r="K157" t="n">
         <v>2026</v>
       </c>
       <c r="L157" t="s">
@@ -10212,7 +10391,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158">
       <c r="A158" t="s">
         <v>950</v>
       </c>
@@ -10237,10 +10416,10 @@
       <c r="H158" t="s">
         <v>62</v>
       </c>
-      <c r="J158">
+      <c r="J158" t="n">
         <v>2014</v>
       </c>
-      <c r="K158">
+      <c r="K158" t="n">
         <v>2024</v>
       </c>
       <c r="L158" t="s">
@@ -10259,14 +10438,14 @@
         <v>953</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159">
       <c r="A159" t="s">
         <v>454</v>
       </c>
       <c r="B159" t="s">
         <v>455</v>
       </c>
-      <c r="D159">
+      <c r="D159" t="n">
         <v>724</v>
       </c>
       <c r="E159" t="s">
@@ -10281,10 +10460,10 @@
       <c r="H159" t="s">
         <v>62</v>
       </c>
-      <c r="J159">
+      <c r="J159" t="n">
         <v>2021</v>
       </c>
-      <c r="K159">
+      <c r="K159" t="n">
         <v>2026</v>
       </c>
       <c r="L159" t="s">
@@ -10303,7 +10482,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160">
       <c r="A160" t="s">
         <v>954</v>
       </c>
@@ -10328,10 +10507,10 @@
       <c r="H160" t="s">
         <v>62</v>
       </c>
-      <c r="J160">
+      <c r="J160" t="n">
         <v>2014</v>
       </c>
-      <c r="K160">
+      <c r="K160" t="n">
         <v>2026</v>
       </c>
       <c r="L160" t="s">
@@ -10350,14 +10529,14 @@
         <v>958</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161">
       <c r="A161" t="s">
         <v>460</v>
       </c>
       <c r="B161" t="s">
         <v>461</v>
       </c>
-      <c r="D161">
+      <c r="D161" t="n">
         <v>144</v>
       </c>
       <c r="E161" t="s">
@@ -10385,7 +10564,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162">
       <c r="A162" t="s">
         <v>959</v>
       </c>
@@ -10410,10 +10589,10 @@
       <c r="H162" t="s">
         <v>62</v>
       </c>
-      <c r="J162">
+      <c r="J162" t="n">
         <v>2016</v>
       </c>
-      <c r="K162">
+      <c r="K162" t="n">
         <v>2022</v>
       </c>
       <c r="L162" t="s">
@@ -10432,14 +10611,14 @@
         <v>963</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163">
       <c r="A163" t="s">
         <v>465</v>
       </c>
       <c r="B163" t="s">
         <v>466</v>
       </c>
-      <c r="D163">
+      <c r="D163" t="n">
         <v>729</v>
       </c>
       <c r="E163" t="s">
@@ -10464,7 +10643,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164">
       <c r="A164" t="s">
         <v>746</v>
       </c>
@@ -10474,7 +10653,7 @@
       <c r="C164" t="s">
         <v>120</v>
       </c>
-      <c r="D164">
+      <c r="D164" t="n">
         <v>729</v>
       </c>
       <c r="E164" t="s">
@@ -10489,10 +10668,10 @@
       <c r="H164" t="s">
         <v>62</v>
       </c>
-      <c r="J164">
+      <c r="J164" t="n">
         <v>2015</v>
       </c>
-      <c r="K164">
+      <c r="K164" t="n">
         <v>2019</v>
       </c>
       <c r="L164" t="s">
@@ -10511,14 +10690,14 @@
         <v>749</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165">
       <c r="A165" t="s">
         <v>471</v>
       </c>
       <c r="B165" t="s">
         <v>472</v>
       </c>
-      <c r="D165">
+      <c r="D165" t="n">
         <v>752</v>
       </c>
       <c r="E165" t="s">
@@ -10533,7 +10712,7 @@
       <c r="H165" t="s">
         <v>62</v>
       </c>
-      <c r="K165">
+      <c r="K165" t="n">
         <v>2026</v>
       </c>
       <c r="L165" t="s">
@@ -10549,7 +10728,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166">
       <c r="A166" t="s">
         <v>964</v>
       </c>
@@ -10574,10 +10753,10 @@
       <c r="H166" t="s">
         <v>62</v>
       </c>
-      <c r="J166">
+      <c r="J166" t="n">
         <v>1996</v>
       </c>
-      <c r="K166">
+      <c r="K166" t="n">
         <v>2026</v>
       </c>
       <c r="L166" t="s">
@@ -10596,14 +10775,14 @@
         <v>968</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167">
       <c r="A167" t="s">
         <v>477</v>
       </c>
       <c r="B167" t="s">
         <v>478</v>
       </c>
-      <c r="D167">
+      <c r="D167" t="n">
         <v>834</v>
       </c>
       <c r="E167" t="s">
@@ -10622,14 +10801,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168">
       <c r="A168" t="s">
         <v>481</v>
       </c>
       <c r="B168" t="s">
         <v>482</v>
       </c>
-      <c r="D168">
+      <c r="D168" t="n">
         <v>764</v>
       </c>
       <c r="E168" t="s">
@@ -10648,7 +10827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169">
       <c r="A169" t="s">
         <v>600</v>
       </c>
@@ -10667,14 +10846,14 @@
       <c r="N169" t="s">
         <v>25</v>
       </c>
-      <c r="P169" s="1">
+      <c r="P169" s="1" t="n">
         <v>46206</v>
       </c>
       <c r="Q169" t="s">
         <v>603</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170">
       <c r="A170" t="s">
         <v>770</v>
       </c>
@@ -10684,7 +10863,7 @@
       <c r="C170" t="s">
         <v>576</v>
       </c>
-      <c r="D170">
+      <c r="D170" t="n">
         <v>764</v>
       </c>
       <c r="E170" t="s">
@@ -10702,10 +10881,10 @@
       <c r="I170" t="s">
         <v>772</v>
       </c>
-      <c r="J170">
+      <c r="J170" t="n">
         <v>2017</v>
       </c>
-      <c r="K170">
+      <c r="K170" t="n">
         <v>2024</v>
       </c>
       <c r="L170" t="s">
@@ -10717,21 +10896,21 @@
       <c r="N170" t="s">
         <v>34</v>
       </c>
-      <c r="P170" s="1">
+      <c r="P170" s="1" t="n">
         <v>46219</v>
       </c>
       <c r="Q170" t="s">
         <v>774</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171">
       <c r="A171" t="s">
         <v>485</v>
       </c>
       <c r="B171" t="s">
         <v>486</v>
       </c>
-      <c r="D171">
+      <c r="D171" t="n">
         <v>626</v>
       </c>
       <c r="E171" t="s">
@@ -10750,14 +10929,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172">
       <c r="A172" t="s">
         <v>489</v>
       </c>
       <c r="B172" t="s">
         <v>490</v>
       </c>
-      <c r="D172">
+      <c r="D172" t="n">
         <v>780</v>
       </c>
       <c r="E172" t="s">
@@ -10776,14 +10955,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173">
       <c r="A173" t="s">
         <v>497</v>
       </c>
       <c r="B173" t="s">
         <v>498</v>
       </c>
-      <c r="D173">
+      <c r="D173" t="n">
         <v>792</v>
       </c>
       <c r="E173" t="s">
@@ -10802,14 +10981,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174">
       <c r="A174" t="s">
         <v>493</v>
       </c>
       <c r="B174" t="s">
         <v>494</v>
       </c>
-      <c r="D174">
+      <c r="D174" t="n">
         <v>795</v>
       </c>
       <c r="E174" t="s">
@@ -10828,14 +11007,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175">
       <c r="A175" t="s">
         <v>501</v>
       </c>
       <c r="B175" t="s">
         <v>502</v>
       </c>
-      <c r="D175">
+      <c r="D175" t="n">
         <v>800</v>
       </c>
       <c r="E175" t="s">
@@ -10854,14 +11033,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176">
       <c r="A176" t="s">
         <v>505</v>
       </c>
       <c r="B176" t="s">
         <v>506</v>
       </c>
-      <c r="D176">
+      <c r="D176" t="n">
         <v>804</v>
       </c>
       <c r="E176" t="s">
@@ -10880,14 +11059,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177">
       <c r="A177" t="s">
         <v>509</v>
       </c>
       <c r="B177" t="s">
         <v>510</v>
       </c>
-      <c r="D177">
+      <c r="D177" t="n">
         <v>784</v>
       </c>
       <c r="E177" t="s">
@@ -10906,14 +11085,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178">
       <c r="A178" t="s">
         <v>513</v>
       </c>
       <c r="B178" t="s">
         <v>514</v>
       </c>
-      <c r="D178">
+      <c r="D178" t="n">
         <v>826</v>
       </c>
       <c r="E178" t="s">
@@ -10932,14 +11111,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179">
       <c r="A179" t="s">
         <v>517</v>
       </c>
       <c r="B179" t="s">
         <v>518</v>
       </c>
-      <c r="D179">
+      <c r="D179" t="n">
         <v>840</v>
       </c>
       <c r="E179" t="s">
@@ -10954,17 +11133,17 @@
       <c r="H179" t="s">
         <v>62</v>
       </c>
-      <c r="J179">
+      <c r="J179" t="n">
         <v>2025</v>
       </c>
-      <c r="K179">
+      <c r="K179" t="n">
         <v>2026</v>
       </c>
       <c r="N179" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180">
       <c r="A180" t="s">
         <v>802</v>
       </c>
@@ -10974,7 +11153,7 @@
       <c r="C180" t="s">
         <v>555</v>
       </c>
-      <c r="D180">
+      <c r="D180" t="n">
         <v>840</v>
       </c>
       <c r="E180" t="s">
@@ -11004,14 +11183,14 @@
       <c r="N180" t="s">
         <v>34</v>
       </c>
-      <c r="P180" s="1">
+      <c r="P180" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q180" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181">
       <c r="A181" t="s">
         <v>809</v>
       </c>
@@ -11021,7 +11200,7 @@
       <c r="C181" t="s">
         <v>555</v>
       </c>
-      <c r="D181">
+      <c r="D181" t="n">
         <v>840</v>
       </c>
       <c r="E181" t="s">
@@ -11051,14 +11230,14 @@
       <c r="N181" t="s">
         <v>34</v>
       </c>
-      <c r="P181" s="1">
+      <c r="P181" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q181" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182">
       <c r="A182" t="s">
         <v>816</v>
       </c>
@@ -11068,7 +11247,7 @@
       <c r="C182" t="s">
         <v>555</v>
       </c>
-      <c r="D182">
+      <c r="D182" t="n">
         <v>840</v>
       </c>
       <c r="E182" t="s">
@@ -11098,21 +11277,21 @@
       <c r="N182" t="s">
         <v>34</v>
       </c>
-      <c r="P182" s="1">
+      <c r="P182" s="1" t="n">
         <v>46212</v>
       </c>
       <c r="Q182" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183">
       <c r="A183" t="s">
         <v>521</v>
       </c>
       <c r="B183" t="s">
         <v>522</v>
       </c>
-      <c r="D183">
+      <c r="D183" t="n">
         <v>858</v>
       </c>
       <c r="E183" t="s">
@@ -11131,14 +11310,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184">
       <c r="A184" t="s">
         <v>525</v>
       </c>
       <c r="B184" t="s">
         <v>526</v>
       </c>
-      <c r="D184">
+      <c r="D184" t="n">
         <v>860</v>
       </c>
       <c r="E184" t="s">
@@ -11157,7 +11336,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185">
       <c r="A185" t="s">
         <v>632</v>
       </c>
@@ -11167,7 +11346,7 @@
       <c r="C185" t="s">
         <v>539</v>
       </c>
-      <c r="D185">
+      <c r="D185" t="n">
         <v>862</v>
       </c>
       <c r="E185" t="s">
@@ -11198,14 +11377,14 @@
         <v>639</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186">
       <c r="A186" t="s">
         <v>529</v>
       </c>
       <c r="B186" t="s">
         <v>530</v>
       </c>
-      <c r="D186">
+      <c r="D186" t="n">
         <v>704</v>
       </c>
       <c r="E186" t="s">
@@ -11224,14 +11403,14 @@
         <v>63</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187">
       <c r="A187" t="s">
         <v>533</v>
       </c>
       <c r="B187" t="s">
         <v>534</v>
       </c>
-      <c r="D187">
+      <c r="D187" t="n">
         <v>716</v>
       </c>
       <c r="E187" t="s">
@@ -11250,7 +11429,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188">
       <c r="A188" t="s">
         <v>1005</v>
       </c>
@@ -11303,7 +11482,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189">
       <c r="A189" t="s">
         <v>1022</v>
       </c>
@@ -11356,7 +11535,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190">
       <c r="A190" t="s">
         <v>1032</v>
       </c>
@@ -11409,7 +11588,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191">
       <c r="A191" t="s">
         <v>1041</v>
       </c>
@@ -11462,7 +11641,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192">
       <c r="A192" t="s">
         <v>1049</v>
       </c>
@@ -11515,7 +11694,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193">
       <c r="A193" t="s">
         <v>1058</v>
       </c>
@@ -11568,7 +11747,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194">
       <c r="A194" t="s">
         <v>1066</v>
       </c>
@@ -11621,7 +11800,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195">
       <c r="A195" t="s">
         <v>1075</v>
       </c>
@@ -11674,7 +11853,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196">
       <c r="A196" t="s">
         <v>1092</v>
       </c>
@@ -11727,7 +11906,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197">
       <c r="A197" t="s">
         <v>1101</v>
       </c>
@@ -11780,7 +11959,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198">
       <c r="A198" t="s">
         <v>1110</v>
       </c>
@@ -11833,7 +12012,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199">
       <c r="A199" t="s">
         <v>1118</v>
       </c>
@@ -11886,7 +12065,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200">
       <c r="A200" t="s">
         <v>1126</v>
       </c>
@@ -11939,7 +12118,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201">
       <c r="A201" t="s">
         <v>1133</v>
       </c>
@@ -11992,7 +12171,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202">
       <c r="A202" t="s">
         <v>1141</v>
       </c>
@@ -12045,7 +12224,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203">
       <c r="A203" t="s">
         <v>1149</v>
       </c>
@@ -12098,7 +12277,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204">
       <c r="A204" t="s">
         <v>1158</v>
       </c>
@@ -12151,7 +12330,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205">
       <c r="A205" t="s">
         <v>1165</v>
       </c>
@@ -12204,7 +12383,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206">
       <c r="A206" t="s">
         <v>1174</v>
       </c>
@@ -12257,7 +12436,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207">
       <c r="A207" t="s">
         <v>1182</v>
       </c>
@@ -12310,7 +12489,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208">
       <c r="A208" t="s">
         <v>1190</v>
       </c>
@@ -12363,7 +12542,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209">
       <c r="A209" t="s">
         <v>1197</v>
       </c>
@@ -12416,7 +12595,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210">
       <c r="A210" t="s">
         <v>1204</v>
       </c>
@@ -12467,6 +12646,324 @@
       </c>
       <c r="Q210" t="s">
         <v>1211</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B211" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C211" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D211" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F211" t="s">
+        <v>1223</v>
+      </c>
+      <c r="G211" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H211" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I211" t="s">
+        <v>1226</v>
+      </c>
+      <c r="J211" t="s">
+        <v>1227</v>
+      </c>
+      <c r="K211" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L211" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M211" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N211" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O211" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P211" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q211" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B212" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C212" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D212" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E212" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F212" t="s">
+        <v>1240</v>
+      </c>
+      <c r="G212" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H212" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I212" t="s">
+        <v>1241</v>
+      </c>
+      <c r="J212" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K212" t="s">
+        <v>1243</v>
+      </c>
+      <c r="L212" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M212" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N212" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O212" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P212" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q212" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B213" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D213" t="s">
+        <v>1248</v>
+      </c>
+      <c r="E213" t="s">
+        <v>1249</v>
+      </c>
+      <c r="F213" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G213" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H213" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I213" t="s">
+        <v>1251</v>
+      </c>
+      <c r="J213" t="s">
+        <v>1252</v>
+      </c>
+      <c r="K213" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L213" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M213" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N213" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O213" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P213" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q213" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B214" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C214" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D214" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E214" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1259</v>
+      </c>
+      <c r="G214" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H214" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I214" t="s">
+        <v>1260</v>
+      </c>
+      <c r="J214" t="s">
+        <v>1261</v>
+      </c>
+      <c r="K214" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L214" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M214" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N214" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O214" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P214" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q214" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C215" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D215" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E215" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F215" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G215" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H215" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I215" t="s">
+        <v>1269</v>
+      </c>
+      <c r="J215" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K215" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L215" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M215" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N215" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O215" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P215" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C216" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D216" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E216" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F216" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G216" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H216" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I216" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J216" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K216" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L216" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M216" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N216" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O216" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P216" t="s">
+        <v>1233</v>
+      </c>
+      <c r="Q216" t="s">
+        <v>1279</v>
       </c>
     </row>
   </sheetData>

--- a/data/sources/master_sources.xlsx
+++ b/data/sources/master_sources.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="1279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1384" uniqueCount="1383">
   <si>
     <t>source_id</t>
   </si>
@@ -3854,6 +3854,318 @@
   </si>
   <si>
     <t xml:space="preserve">Probe-validated 2026-07-26 (--spread --n 8): 4,252 date-path post captures (president.go.ke/&lt;yyyy&gt;/&lt;mm&gt;/&lt;dd&gt;/&lt;slug&gt;/, CDX prefix president.go.ke/20 ~8,000 raw). The OLD pre-Elementor WordPress site (Uhuru Kenyatta era, president 2013-2022) archives as CLEAN HTML (unlike the modern Elementor /speeches_remarks/ JS shells). TITLE(h1.entry-title) clean; TEXT via .entry-content/generic fallback (2.7k-3.9k chars); DATE from the URL permalink via url_regex ONLY (unambiguous ISO; .post-date returns a re-crawl artifact). Posts mix speeches + presidency news -&gt; cleaner document-type gate keeps the speech/official_statement subset. NO speaker_default (Uhuru + First Lady Margaret Kenyatta + quoted ministers) -&gt; cleaner speaker pass + tenure crosscheck. 'yes-and' to the live ken_president (Ruto 2022- PDFs): this is the Kenyatta 2013-2022 corpus. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">can_pmo_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime Minister's Office pm.gc.ca speeches (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pm.gc.ca/en/news/speeches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Justin Trudeau; Mark Carney</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 417 dated /en/news/speeches/&lt;yyyy&gt;/&lt;mm&gt;/&lt;dd&gt;/&lt;slug&gt; snapshots. TEXT(.field--name-body) 4.2k-16k chars + DATE(url_regex from the permalink) 2015-2026 all green (Trudeau + Carney). TITLE from the URL slug via url_regex (the archived Drupal h1 is a nav blob, and selectors win over url_regex, so title uses url_regex ONLY) -&gt; cleaner polishes dashes. OVERLAP: ~1,000 Canada Dean_scrape speeches (2000-2022) already exist -&gt; additive value is mainly the 2022-&gt; tail + PM Carney (2025- ) + snapshot-insurance; the merge dedupes. Old /eng/news Harper-era scheme (~90% Drupal asset junk, likely inside Dean_scrape) NOT harvested. NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idn_setkab_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indonesia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabinet Secretariat setkab.go.id/en transcripts (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://setkab.go.id/en/category/speech-transcript/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Joko Widodo; Prabowo Subianto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 1,964 snapshots. The transcript-slug link_pattern (remarks/statement/press-statement/address/... of the President) cleanly ISOLATES the president's English transcripts from the aggregator's general /en/ news -&gt; every sample is a genuine transcript (Jokowi/Prabowo: 'Address of President... at Georgetown University'; 'Press Statement of President...'; 'Remarks of President...'). TITLE(h1) + TEXT(.detail_text, 1.9k-37k chars) + DATE(meta article:published_time) all green (2021-2025; one older page falls to the cleaner). English -&gt; English column, no MT. 'yes-and' companion to the live idn_setkab (recovers older/deleted transcripts). NO verify_ssl needed (fetch is from the Archive). NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ind_pmindia_nic_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India</t>
+  </si>
+  <si>
+    <t xml:space="preserve">356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Old PMO pmindia.nic.in speeches (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://pmindia.nic.in/speech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manmohan Singh; Atal Bihari Vajpayee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 1,185 snapshots. NEW pre-Modi historical depth: the OLD pmindia.nic.in holds full English speeches of PM Manmohan Singh (2004-2014) via /speech/content.asp?id=&lt;id&gt; -&gt; TEXT(td) 25k-48k chars, DATE(body dateline) 2004-2011 all green (TITLE is the generic 'Prime Minister's Office' banner -&gt; the cleaner derives a title from the body, the aus_gg pattern). The /speech-details.php?nodeid= PHP tail (2012-2014) extracts thinly (generic backstop). NO speaker_default (Vajpayee ...2004 + Manmohan Singh 2004-2014) -&gt; cleaner + tenure crosscheck. Nothing else in the corpus covers pre-Modi Indian PMs. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ind_pmindia_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM of India pmindia.gov.in/en/news_updates (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pmindia.gov.in/en/news_updates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narendra Modi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 15,926 /en/news_updates snapshots. TITLE(.content-block h2 — the bare h1 is the site logo) + TEXT(.news-bg, up to 28.8k chars) + DATE(.date) all green; speaker_default Narendra Modi (2014-2026). WAF WORK-AROUND: pmindia.gov.in's UA-keyed WAF blocks the live bot UA, but the Archive serves the pages cleanly (no user_agent needed). 'yes-and' companion to the live ind_pmindia. Detail pages mix PM speeches/statements + short press notes -&gt; document_type gate filters. Companion ind_pmindia_nic_wayback covers the pre-Modi PMs. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kaz_akorda_english_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kazakhstan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">akorda.kz English state-of-nation addresses (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://akorda.kz/en/addresses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nursultan Nazarbayev; Kassym-Jomart Tokayev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): the /en/addresses/addresses_of_president/&lt;slug&gt; article extracts cleanly -&gt; TITLE(h1) 'State of the Nation Address', TEXT(.text) 34,036 chars, DATE(.date) 2017-01-31. NARROWED to /en/addresses/ (CDX approx 46 caps 2015-2024) -- the annual state-of-the-nation Addresses of Presidents Nazarbayev + Tokayev, the highest-value single speeches. ENGLISH sibling of the native (Russian) kaz_akorda_wayback -&gt; English column, no MT. The broader /en/speeches/&lt;cat&gt;/&lt;slug&gt; tree (approx 314 caps) archives its OLDER captures as shells/section-listings (.text -&gt; 0; generic ~0.8-2k of chrome) -&gt; DEFERRED as a follow-up (that content is covered by the native Russian recipe + translation). NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mar_maroc_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morocco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maroc.ma royal speeches EN (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://maroc.ma/en/royal-speeches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">King Mohammed VI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 178 snapshots. GENUINE English -&gt; TITLE(h1) clean ('Full Speech of HM the King on COP22 High-Level Segment'; 'Full Text of Royal Message to the 27th African Union Summit'); NEW scheme body via .c-wysiwyg (7918 chars), OLD /en/royal-speeches/&lt;slug&gt; scheme (2013-2024) body via the engine's generic fallback (5.8k-13k chars). DATE deferred to cleaner + wayback_capture (the article's only &lt;time&gt; is a related-news sidebar). speaker_default King Mohammed VI. Official English translation -&gt; English column, no MT. 'yes-and' companion to the live mar_maroc (current scheme); recovers the relocated OLD-scheme royal speeches. Companion Arabic original is mar_diplomatie. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mdv_presidencymaldives_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maldives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">President's Office presidency.gov.mv (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://presidency.gov.mv/Press/Article/12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maumoon Abdul Gayoom; Mohamed Nasheed; Mohammed Waheed; Abdulla Yameen; Ibrahim Mohamed Solih; Mohamed Muizzu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 35,300 /Press/Article/&lt;id&gt; snapshots. TITLE(h1) + TEXT(.article-body, 614-2985 chars) green; DATE(.small-text) parses English dates (2011-05-29 Nasheed, 2018-08-20, 2023-10-16) and falls to the cleaner for Dhivehi-month dates. 'yes-and' companion to the live mdv_presidencymaldives (which paginates /Press/Articles/12 back to ~1979): a frozen snapshot + deleted-article insurance for the same current DB. Mixed English/Dhivehi (cleaner detects per-doc). NO speaker_default. The much older presidencymaldives.gov.mv ASP/PHP generation is NOT harvested (messy multi-scheme lead). FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sgp_pmo_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singapore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prime Minister's Office pmo.gov.sg (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.pmo.gov.sg/newsroom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lee Hsien Loong; Heng Swee Keat; Teo Chee Hean; Lawrence Wong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 3,269 /Newsroom snapshots. The OLDER /Newsroom/&lt;Title-Case-slug&gt; CMS generation archives with REAL bodies (NOT JS shells): TITLE(h1) clean ('PM Lee Hsien Loong at the DSO50 Jubilee Dinner'; 'Eulogy by PM Lee Hsien Loong at funeral of the late Mr S R Nathan'), TEXT(article/main, 5.9k-11.9k chars), DATE(article regex) 2011-2026 all green. Covers PM Lee Hsien Loong / DPM Heng Swee Keat / DPM Teo Chee Hean (pre-2024). 'yes-and' companion to the live sgp_pmo (current Isomer sitemap). NO speaker_default. Distinct from the ceremonial-President sgp_istana / sgp_istana_wayback. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sle_statehouse_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sierra Leone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State House statehouse.gov.sl date-path posts (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://statehouse.gov.sl/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julius Maada Bio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 280 date-path /YYYY/MM/DD/&lt;slug&gt; snapshots. TITLE(h1) + TEXT(.elementor-widget-theme-post-content, 1.3k-4k chars for substantive posts; some 43-101-char stubs) + DATE(url_regex) green (President Julius Maada Bio). CAVEAT: the archived SLUGGED posts are almost all 2025-2026 — the pre-2025 era was captured only as bare /YYYY/MM/DD/ day-listings, so the hoped 2018-2024 Bio depth is NOT recoverable via wayback -&gt; this largely OVERLAPS the live sle_statehouse (WP REST, 2025-01+); value = frozen snapshot + deleted-post insurance. NO speaker_default (Bio + a brief late-Koroma window) -&gt; cleaner + tenure. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">syc_statehouse_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seychelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">690</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State House statehouse.gov.sc/speeches (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.statehouse.gov.sc/speeches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">James Michel; Danny Faure; Wavel Ramkalawan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 841 /speeches/&lt;id&gt;/&lt;slug&gt; snapshots. TITLE(h1) clean speech titles for the OLD-layout majority (Michel/Faure era); TEXT(.container/.u-sheet-1, 3.4k-9.4k chars) green; DATE mostly falls to the cleaner (old captures lack the modern Nicepage p.u-text-2 date element; wayback_capture backstops). Spans President James Michel (2004-2016), Danny Faure (2016-2020), Wavel Ramkalawan (2020- ) + VP remarks. Multilingual site: default /speeches is English but some captures are the French/Creole version (cleaner detects per-doc). 'yes-and' companion to the live syc_statehouse. NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tto_otp_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trinidad and Tobago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office of the President otp.tt (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://otp.tt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paula-Mae Weekes; Christine Kangaloo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 845 single-segment WordPress-post snapshots. TITLE(h1.entry-title) clean ('Christmas Message from Her Excellency'; 'Message for the International Day of Education'; 'President Weekes participates in Walk for Sight 2019'); TEXT(.entry-content, 505-3058 chars) green. DATE: the archived Elementor pages expose no clean date element -&gt; date falls to the cleaner's corrected-date pass + wayback_capture. GREENFIELD (Office of the President; T&amp;T's ceremonial head of state - Presidents Paula-Mae Weekes 2018-2023, Christine Kangaloo 2023- ). Mostly ceremonial notices (appointments, courtesy calls) + genuine messages/speeches -&gt; the document_type gate keeps the substantive addresses. NO speaker_default. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uga_statehouse_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uganda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State House statehouse.go.ug/media/speeches (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://statehouse.go.ug/media/speeches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoweri Museveni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 127 dated /media/speeches/&lt;yyyy&gt;/&lt;mm&gt;/&lt;dd&gt;/&lt;slug&gt; snapshots. TITLE(h1) clean ('State of the Nation Address 2013'; 'President Museveni''s 54th Independence Day Speech'); TEXT(.content, 16k-46k chars - full addresses) + DATE(url_regex from the permalink) 2011-2022 all green. GREENFIELD (President Yoweri Museveni, in office since 1986). The link_pattern keeps /media/speeches/&lt;date&gt;/&lt;slug&gt; articles and drops the 2021 crawl-storm of ?page=N day-listings. NO speaker_default (Museveni dominant + occasional VP/official remarks) -&gt; cleaner + tenure crosscheck. The 2023+ site uses a different flat-slug scheme (not covered here). FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zaf_gov_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Africa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SA Government speeches gov.za/news/speeches (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gov.za/news/speeches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyril Ramaphosa; Jacob Zuma; + ministers/premiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 14,886 /news/speeches snapshots. TITLE(h1) + TEXT(.field--name-body, 4.4k-42k chars) + DATE(&lt;time&gt;) all green, content back to 2009 (UKZN 2009; Madonsela 2010) through 2025. Deep official aggregator of ALL SA government speeches (President Ramaphosa + ministers + premiers + Speaker). 'yes-and' companion to the live zaf_gov (frozen snapshot + deleted-article insurance of the same migrated DB). Distinct from zaf_thepresidency_wayback (the presidency's own old Drupal-7 site). NO speaker_default -&gt; the cleaner's speaker pass keeps the President's speeches + document_type gate filters ministers. FULL RUN is the researcher's gate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zwe_theopc_wayback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zimbabwe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Office of the President and Cabinet theopc.gov.zw (Wayback/CDX)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://www.theopc.gov.zw/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emmerson Mnangagwa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probe-validated 2026-07-27 (--spread --n 8): 177 Joomla /index.php/&lt;id&gt;-&lt;slug&gt; snapshots. TEXT(article) 217-46,185 chars (transcript of President ED's Financial Times interview 46k; Independence Day speech 22k) + DATE(.published) 2016-2020 all green. TITLE is 'Latest News' (chrome) on the bare news items -&gt; the cleaner derives a title from the body; the /index.php/news/speeches-and-statements/ category page carries a real h1. GREENFIELD (Zimbabwe OPC; President Emmerson Mnangagwa 2017- , 'Second Republic'). NO speaker_default (Mnangagwa dominant + occasional chief-secretary statements) -&gt; cleaner + document_type gate. FULL RUN is the researcher's gate.</t>
   </si>
 </sst>
 </file>
@@ -12966,6 +13278,748 @@
         <v>1279</v>
       </c>
     </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C217" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D217" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E217" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G217" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H217" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I217" t="s">
+        <v>1285</v>
+      </c>
+      <c r="J217" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K217" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L217" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M217" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N217" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O217" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P217" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q217" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C218" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D218" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E218" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F218" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G218" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H218" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I218" t="s">
+        <v>1293</v>
+      </c>
+      <c r="J218" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K218" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L218" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M218" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N218" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O218" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P218" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B219" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C219" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D219" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E219" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F219" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G219" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H219" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I219" t="s">
+        <v>1300</v>
+      </c>
+      <c r="J219" t="s">
+        <v>1301</v>
+      </c>
+      <c r="K219" t="s">
+        <v>1278</v>
+      </c>
+      <c r="L219" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M219" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N219" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O219" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P219" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B220" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C220" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D220" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E220" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F220" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G220" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H220" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I220" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J220" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K220" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L220" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M220" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N220" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O220" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P220" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B221" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C221" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D221" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E221" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F221" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G221" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H221" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I221" t="s">
+        <v>1313</v>
+      </c>
+      <c r="J221" t="s">
+        <v>1243</v>
+      </c>
+      <c r="K221" t="s">
+        <v>1253</v>
+      </c>
+      <c r="L221" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M221" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N221" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O221" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P221" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B222" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C222" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D222" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E222" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F222" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G222" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H222" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I222" t="s">
+        <v>1320</v>
+      </c>
+      <c r="J222" t="s">
+        <v>1321</v>
+      </c>
+      <c r="K222" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L222" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M222" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N222" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O222" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P222" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B223" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C223" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D223" t="s">
+        <v>1325</v>
+      </c>
+      <c r="E223" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F223" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G223" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H223" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I223" t="s">
+        <v>1328</v>
+      </c>
+      <c r="J223" t="s">
+        <v>1227</v>
+      </c>
+      <c r="K223" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L223" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M223" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N223" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O223" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P223" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B224" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C224" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D224" t="s">
+        <v>1332</v>
+      </c>
+      <c r="E224" t="s">
+        <v>1333</v>
+      </c>
+      <c r="F224" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G224" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H224" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I224" t="s">
+        <v>1335</v>
+      </c>
+      <c r="J224" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K224" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L224" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M224" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N224" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O224" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P224" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B225" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C225" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D225" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E225" t="s">
+        <v>1340</v>
+      </c>
+      <c r="F225" t="s">
+        <v>1341</v>
+      </c>
+      <c r="G225" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H225" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I225" t="s">
+        <v>1342</v>
+      </c>
+      <c r="J225" t="s">
+        <v>1343</v>
+      </c>
+      <c r="K225" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L225" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M225" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N225" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O225" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P225" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C226" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F226" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G226" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H226" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I226" t="s">
+        <v>1350</v>
+      </c>
+      <c r="J226" t="s">
+        <v>1351</v>
+      </c>
+      <c r="K226" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L226" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M226" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N226" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O226" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P226" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>1352</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1354</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D227" t="s">
+        <v>1355</v>
+      </c>
+      <c r="E227" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F227" t="s">
+        <v>1357</v>
+      </c>
+      <c r="G227" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H227" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I227" t="s">
+        <v>1358</v>
+      </c>
+      <c r="J227" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K227" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L227" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M227" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N227" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O227" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P227" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C228" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D228" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E228" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F228" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G228" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H228" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I228" t="s">
+        <v>1365</v>
+      </c>
+      <c r="J228" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K228" t="s">
+        <v>1270</v>
+      </c>
+      <c r="L228" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M228" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N228" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O228" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P228" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D229" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E229" t="s">
+        <v>1370</v>
+      </c>
+      <c r="F229" t="s">
+        <v>1371</v>
+      </c>
+      <c r="G229" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I229" t="s">
+        <v>1372</v>
+      </c>
+      <c r="J229" t="s">
+        <v>1373</v>
+      </c>
+      <c r="K229" t="s">
+        <v>1228</v>
+      </c>
+      <c r="L229" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M229" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N229" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O229" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P229" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>1374</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C230" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E230" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G230" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1225</v>
+      </c>
+      <c r="I230" t="s">
+        <v>1380</v>
+      </c>
+      <c r="J230" t="s">
+        <v>1381</v>
+      </c>
+      <c r="K230" t="s">
+        <v>1382</v>
+      </c>
+      <c r="L230" t="s">
+        <v>1229</v>
+      </c>
+      <c r="M230" t="s">
+        <v>1230</v>
+      </c>
+      <c r="N230" t="s">
+        <v>1231</v>
+      </c>
+      <c r="O230" t="s">
+        <v>1232</v>
+      </c>
+      <c r="P230" t="s">
+        <v>1286</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>1383</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0"/>
